--- a/Excel/PetTupoConfig.xlsx
+++ b/Excel/PetTupoConfig.xlsx
@@ -1,51 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GitWeiJing2022\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{164642F1-3596-4379-AB8F-49C501B74E69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11775"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PetTupoProto" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>作者</author>
     <author>Admin</author>
   </authors>
   <commentList>
-    <comment ref="K3" authorId="0">
+    <comment ref="K3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>作者:
 10.生命值
@@ -97,14 +85,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="L3" authorId="0">
+    <comment ref="L3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>作者:
 10.生命值
@@ -156,13 +144,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="M3" authorId="1">
+    <comment ref="M3" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Admin:</t>
@@ -171,6 +160,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -193,7 +183,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="313">
   <si>
     <t>c</t>
   </si>
@@ -279,15 +269,6 @@
     <t>Attack Training Level 20</t>
   </si>
   <si>
-    <t>25000</t>
-  </si>
-  <si>
-    <t>10000163;1200</t>
-  </si>
-  <si>
-    <t>100403;4800</t>
-  </si>
-  <si>
     <t>生命修炼0级</t>
   </si>
   <si>
@@ -300,9 +281,6 @@
     <t>Life Training Level 20</t>
   </si>
   <si>
-    <t>100203;28800</t>
-  </si>
-  <si>
     <t>防御修炼0级</t>
   </si>
   <si>
@@ -315,9 +293,6 @@
     <t>Defense Training Level 20</t>
   </si>
   <si>
-    <t>100603;4800</t>
-  </si>
-  <si>
     <t>法防修炼0级</t>
   </si>
   <si>
@@ -330,20 +305,831 @@
     <t>Magic Defense Training Level 20</t>
   </si>
   <si>
-    <t>100803;4800</t>
+    <t>攻击修炼1级</t>
+  </si>
+  <si>
+    <t>Attack Training Level 1</t>
+  </si>
+  <si>
+    <t>攻击修炼2级</t>
+  </si>
+  <si>
+    <t>Attack Training Level 2</t>
+  </si>
+  <si>
+    <t>攻击修炼3级</t>
+  </si>
+  <si>
+    <t>Attack Training Level 3</t>
+  </si>
+  <si>
+    <t>攻击修炼4级</t>
+  </si>
+  <si>
+    <t>Attack Training Level 4</t>
+  </si>
+  <si>
+    <t>攻击修炼5级</t>
+  </si>
+  <si>
+    <t>Attack Training Level 5</t>
+  </si>
+  <si>
+    <t>攻击修炼6级</t>
+  </si>
+  <si>
+    <t>Attack Training Level 6</t>
+  </si>
+  <si>
+    <t>攻击修炼7级</t>
+  </si>
+  <si>
+    <t>Attack Training Level 7</t>
+  </si>
+  <si>
+    <t>攻击修炼8级</t>
+  </si>
+  <si>
+    <t>Attack Training Level 8</t>
+  </si>
+  <si>
+    <t>攻击修炼9级</t>
+  </si>
+  <si>
+    <t>Attack Training Level 9</t>
+  </si>
+  <si>
+    <t>攻击修炼10级</t>
+  </si>
+  <si>
+    <t>Attack Training Level 10</t>
+  </si>
+  <si>
+    <t>攻击修炼11级</t>
+  </si>
+  <si>
+    <t>Attack Training Level 11</t>
+  </si>
+  <si>
+    <t>攻击修炼12级</t>
+  </si>
+  <si>
+    <t>Attack Training Level 12</t>
+  </si>
+  <si>
+    <t>攻击修炼13级</t>
+  </si>
+  <si>
+    <t>Attack Training Level 13</t>
+  </si>
+  <si>
+    <t>攻击修炼14级</t>
+  </si>
+  <si>
+    <t>Attack Training Level 14</t>
+  </si>
+  <si>
+    <t>攻击修炼15级</t>
+  </si>
+  <si>
+    <t>Attack Training Level 15</t>
+  </si>
+  <si>
+    <t>攻击修炼16级</t>
+  </si>
+  <si>
+    <t>Attack Training Level 16</t>
+  </si>
+  <si>
+    <t>攻击修炼17级</t>
+  </si>
+  <si>
+    <t>Attack Training Level 17</t>
+  </si>
+  <si>
+    <t>攻击修炼18级</t>
+  </si>
+  <si>
+    <t>Attack Training Level 18</t>
+  </si>
+  <si>
+    <t>攻击修炼19级</t>
+  </si>
+  <si>
+    <t>Attack Training Level 19</t>
+  </si>
+  <si>
+    <t>0</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>1;1000000@10000168;10</t>
+  </si>
+  <si>
+    <t>1;2000000@10000168;20</t>
+  </si>
+  <si>
+    <t>1;3000000@10000168;30</t>
+  </si>
+  <si>
+    <t>1;4000000@10000168;40</t>
+  </si>
+  <si>
+    <t>1;5000000@10000168;50@10000169;3</t>
+  </si>
+  <si>
+    <t>1;6000000@10000168;60</t>
+  </si>
+  <si>
+    <t>1;7000000@10000168;70</t>
+  </si>
+  <si>
+    <t>1;8000000@10000168;80</t>
+  </si>
+  <si>
+    <t>1;9000000@10000168;90</t>
+  </si>
+  <si>
+    <t>1;10000000@10000168;100@10000169;5</t>
+  </si>
+  <si>
+    <t>1;12000000@10000168;120</t>
+  </si>
+  <si>
+    <t>1;14000000@10000168;140</t>
+  </si>
+  <si>
+    <t>1;16000000@10000168;160</t>
+  </si>
+  <si>
+    <t>1;18000000@10000168;180</t>
+  </si>
+  <si>
+    <t>1;20000000@10000168;200@10000169;10</t>
+  </si>
+  <si>
+    <t>1;22000000@10000168;220</t>
+  </si>
+  <si>
+    <t>1;24000000@10000168;240</t>
+  </si>
+  <si>
+    <t>1;26000000@10000168;260</t>
+  </si>
+  <si>
+    <t>1;28000000@10000168;280</t>
+  </si>
+  <si>
+    <t>1;30000000@10000168;300@10000169;20</t>
+  </si>
+  <si>
+    <t>生命修炼1级</t>
+  </si>
+  <si>
+    <t>Life Training Level 1</t>
+  </si>
+  <si>
+    <t>生命修炼2级</t>
+  </si>
+  <si>
+    <t>Life Training Level 2</t>
+  </si>
+  <si>
+    <t>生命修炼3级</t>
+  </si>
+  <si>
+    <t>Life Training Level 3</t>
+  </si>
+  <si>
+    <t>生命修炼4级</t>
+  </si>
+  <si>
+    <t>Life Training Level 4</t>
+  </si>
+  <si>
+    <t>生命修炼5级</t>
+  </si>
+  <si>
+    <t>Life Training Level 5</t>
+  </si>
+  <si>
+    <t>生命修炼6级</t>
+  </si>
+  <si>
+    <t>Life Training Level 6</t>
+  </si>
+  <si>
+    <t>生命修炼7级</t>
+  </si>
+  <si>
+    <t>Life Training Level 7</t>
+  </si>
+  <si>
+    <t>生命修炼8级</t>
+  </si>
+  <si>
+    <t>Life Training Level 8</t>
+  </si>
+  <si>
+    <t>生命修炼9级</t>
+  </si>
+  <si>
+    <t>Life Training Level 9</t>
+  </si>
+  <si>
+    <t>生命修炼10级</t>
+  </si>
+  <si>
+    <t>Life Training Level 10</t>
+  </si>
+  <si>
+    <t>生命修炼11级</t>
+  </si>
+  <si>
+    <t>Life Training Level 11</t>
+  </si>
+  <si>
+    <t>生命修炼12级</t>
+  </si>
+  <si>
+    <t>Life Training Level 12</t>
+  </si>
+  <si>
+    <t>生命修炼13级</t>
+  </si>
+  <si>
+    <t>Life Training Level 13</t>
+  </si>
+  <si>
+    <t>生命修炼14级</t>
+  </si>
+  <si>
+    <t>Life Training Level 14</t>
+  </si>
+  <si>
+    <t>生命修炼15级</t>
+  </si>
+  <si>
+    <t>Life Training Level 15</t>
+  </si>
+  <si>
+    <t>生命修炼16级</t>
+  </si>
+  <si>
+    <t>Life Training Level 16</t>
+  </si>
+  <si>
+    <t>生命修炼17级</t>
+  </si>
+  <si>
+    <t>Life Training Level 17</t>
+  </si>
+  <si>
+    <t>生命修炼18级</t>
+  </si>
+  <si>
+    <t>Life Training Level 18</t>
+  </si>
+  <si>
+    <t>生命修炼19级</t>
+  </si>
+  <si>
+    <t>Life Training Level 19</t>
+  </si>
+  <si>
+    <t>防御修炼1级</t>
+  </si>
+  <si>
+    <t>Defense Training Level 1</t>
+  </si>
+  <si>
+    <t>防御修炼2级</t>
+  </si>
+  <si>
+    <t>Defense Training Level 2</t>
+  </si>
+  <si>
+    <t>防御修炼3级</t>
+  </si>
+  <si>
+    <t>Defense Training Level 3</t>
+  </si>
+  <si>
+    <t>防御修炼4级</t>
+  </si>
+  <si>
+    <t>Defense Training Level 4</t>
+  </si>
+  <si>
+    <t>防御修炼5级</t>
+  </si>
+  <si>
+    <t>Defense Training Level 5</t>
+  </si>
+  <si>
+    <t>防御修炼6级</t>
+  </si>
+  <si>
+    <t>Defense Training Level 6</t>
+  </si>
+  <si>
+    <t>防御修炼7级</t>
+  </si>
+  <si>
+    <t>Defense Training Level 7</t>
+  </si>
+  <si>
+    <t>防御修炼8级</t>
+  </si>
+  <si>
+    <t>Defense Training Level 8</t>
+  </si>
+  <si>
+    <t>防御修炼9级</t>
+  </si>
+  <si>
+    <t>Defense Training Level 9</t>
+  </si>
+  <si>
+    <t>防御修炼10级</t>
+  </si>
+  <si>
+    <t>Defense Training Level 10</t>
+  </si>
+  <si>
+    <t>防御修炼11级</t>
+  </si>
+  <si>
+    <t>Defense Training Level 11</t>
+  </si>
+  <si>
+    <t>防御修炼12级</t>
+  </si>
+  <si>
+    <t>Defense Training Level 12</t>
+  </si>
+  <si>
+    <t>防御修炼13级</t>
+  </si>
+  <si>
+    <t>Defense Training Level 13</t>
+  </si>
+  <si>
+    <t>防御修炼14级</t>
+  </si>
+  <si>
+    <t>Defense Training Level 14</t>
+  </si>
+  <si>
+    <t>防御修炼15级</t>
+  </si>
+  <si>
+    <t>Defense Training Level 15</t>
+  </si>
+  <si>
+    <t>防御修炼16级</t>
+  </si>
+  <si>
+    <t>Defense Training Level 16</t>
+  </si>
+  <si>
+    <t>防御修炼17级</t>
+  </si>
+  <si>
+    <t>Defense Training Level 17</t>
+  </si>
+  <si>
+    <t>防御修炼18级</t>
+  </si>
+  <si>
+    <t>Defense Training Level 18</t>
+  </si>
+  <si>
+    <t>防御修炼19级</t>
+  </si>
+  <si>
+    <t>Defense Training Level 19</t>
+  </si>
+  <si>
+    <t>法防修炼1级</t>
+  </si>
+  <si>
+    <t>Magic Defense Training Level 1</t>
+  </si>
+  <si>
+    <t>法防修炼2级</t>
+  </si>
+  <si>
+    <t>Magic Defense Training Level 2</t>
+  </si>
+  <si>
+    <t>法防修炼3级</t>
+  </si>
+  <si>
+    <t>Magic Defense Training Level 3</t>
+  </si>
+  <si>
+    <t>法防修炼4级</t>
+  </si>
+  <si>
+    <t>Magic Defense Training Level 4</t>
+  </si>
+  <si>
+    <t>法防修炼5级</t>
+  </si>
+  <si>
+    <t>Magic Defense Training Level 5</t>
+  </si>
+  <si>
+    <t>法防修炼6级</t>
+  </si>
+  <si>
+    <t>Magic Defense Training Level 6</t>
+  </si>
+  <si>
+    <t>法防修炼7级</t>
+  </si>
+  <si>
+    <t>Magic Defense Training Level 7</t>
+  </si>
+  <si>
+    <t>法防修炼8级</t>
+  </si>
+  <si>
+    <t>Magic Defense Training Level 8</t>
+  </si>
+  <si>
+    <t>法防修炼9级</t>
+  </si>
+  <si>
+    <t>Magic Defense Training Level 9</t>
+  </si>
+  <si>
+    <t>法防修炼10级</t>
+  </si>
+  <si>
+    <t>Magic Defense Training Level 10</t>
+  </si>
+  <si>
+    <t>法防修炼11级</t>
+  </si>
+  <si>
+    <t>Magic Defense Training Level 11</t>
+  </si>
+  <si>
+    <t>法防修炼12级</t>
+  </si>
+  <si>
+    <t>Magic Defense Training Level 12</t>
+  </si>
+  <si>
+    <t>法防修炼13级</t>
+  </si>
+  <si>
+    <t>Magic Defense Training Level 13</t>
+  </si>
+  <si>
+    <t>法防修炼14级</t>
+  </si>
+  <si>
+    <t>Magic Defense Training Level 14</t>
+  </si>
+  <si>
+    <t>法防修炼15级</t>
+  </si>
+  <si>
+    <t>Magic Defense Training Level 15</t>
+  </si>
+  <si>
+    <t>法防修炼16级</t>
+  </si>
+  <si>
+    <t>Magic Defense Training Level 16</t>
+  </si>
+  <si>
+    <t>法防修炼17级</t>
+  </si>
+  <si>
+    <t>Magic Defense Training Level 17</t>
+  </si>
+  <si>
+    <t>法防修炼18级</t>
+  </si>
+  <si>
+    <t>Magic Defense Training Level 18</t>
+  </si>
+  <si>
+    <t>法防修炼19级</t>
+  </si>
+  <si>
+    <t>Magic Defense Training Level 19</t>
+  </si>
+  <si>
+    <t>130103;75@231103;0.01</t>
+  </si>
+  <si>
+    <t>130103;150@231103;0.02</t>
+  </si>
+  <si>
+    <t>130103;225@231103;0.03</t>
+  </si>
+  <si>
+    <t>130103;300@231103;0.04</t>
+  </si>
+  <si>
+    <t>130103;400@231103;0.05</t>
+  </si>
+  <si>
+    <t>130103;500@231103;0.06</t>
+  </si>
+  <si>
+    <t>130103;650@231103;0.07</t>
+  </si>
+  <si>
+    <t>130103;800@231103;0.08</t>
+  </si>
+  <si>
+    <t>130103;1000@231103;0.09</t>
+  </si>
+  <si>
+    <t>130103;1200@231103;0.1</t>
+  </si>
+  <si>
+    <t>130103;1450@231103;0.11</t>
+  </si>
+  <si>
+    <t>130103;1700@231103;0.12</t>
+  </si>
+  <si>
+    <t>130103;2000@231103;0.13</t>
+  </si>
+  <si>
+    <t>130103;2400@231103;0.14</t>
+  </si>
+  <si>
+    <t>130103;3000@231103;0.15</t>
+  </si>
+  <si>
+    <t>130103;3600@231103;0.16</t>
+  </si>
+  <si>
+    <t>130103;4400@231103;0.17</t>
+  </si>
+  <si>
+    <t>130103;5200@231103;0.18</t>
+  </si>
+  <si>
+    <t>130103;6200@231103;0.19</t>
+  </si>
+  <si>
+    <t>130103;7200@231103;0.2</t>
+  </si>
+  <si>
+    <t>130003;75@231003;0.01</t>
+  </si>
+  <si>
+    <t>130003;150@231003;0.02</t>
+  </si>
+  <si>
+    <t>130003;225@231003;0.03</t>
+  </si>
+  <si>
+    <t>130003;300@231003;0.04</t>
+  </si>
+  <si>
+    <t>130003;400@231003;0.05</t>
+  </si>
+  <si>
+    <t>130003;500@231003;0.06</t>
+  </si>
+  <si>
+    <t>130003;650@231003;0.07</t>
+  </si>
+  <si>
+    <t>130003;800@231003;0.08</t>
+  </si>
+  <si>
+    <t>130003;1000@231003;0.09</t>
+  </si>
+  <si>
+    <t>130003;1200@231003;0.1</t>
+  </si>
+  <si>
+    <t>130003;1450@231003;0.11</t>
+  </si>
+  <si>
+    <t>130003;1700@231003;0.12</t>
+  </si>
+  <si>
+    <t>130003;2000@231003;0.13</t>
+  </si>
+  <si>
+    <t>130003;2400@231003;0.14</t>
+  </si>
+  <si>
+    <t>130003;3000@231003;0.15</t>
+  </si>
+  <si>
+    <t>130003;3600@231003;0.16</t>
+  </si>
+  <si>
+    <t>130003;4400@231003;0.17</t>
+  </si>
+  <si>
+    <t>130003;5200@231003;0.18</t>
+  </si>
+  <si>
+    <t>130003;6200@231003;0.19</t>
+  </si>
+  <si>
+    <t>130003;7200@231003;0.2</t>
+  </si>
+  <si>
+    <t>130203;75@230503;0.005@230603;0.005</t>
+  </si>
+  <si>
+    <t>130203;150@230503;0.01@230603;0.01</t>
+  </si>
+  <si>
+    <t>130203;225@230503;0.015@230603;0.015</t>
+  </si>
+  <si>
+    <t>130203;300@230503;0.02@230603;0.02</t>
+  </si>
+  <si>
+    <t>130203;400@230503;0.025@230603;0.025</t>
+  </si>
+  <si>
+    <t>130203;500@230503;0.03@230603;0.03</t>
+  </si>
+  <si>
+    <t>130203;650@230503;0.035@230603;0.035</t>
+  </si>
+  <si>
+    <t>130203;800@230503;0.04@230603;0.04</t>
+  </si>
+  <si>
+    <t>130203;1000@230503;0.045@230603;0.045</t>
+  </si>
+  <si>
+    <t>130203;1200@230503;0.05@230603;0.05</t>
+  </si>
+  <si>
+    <t>130203;1450@230503;0.055@230603;0.055</t>
+  </si>
+  <si>
+    <t>130203;1700@230503;0.06@230603;0.06</t>
+  </si>
+  <si>
+    <t>130203;2000@230503;0.065@230603;0.065</t>
+  </si>
+  <si>
+    <t>130203;2400@230503;0.07@230603;0.07</t>
+  </si>
+  <si>
+    <t>130203;3000@230503;0.075@230603;0.075</t>
+  </si>
+  <si>
+    <t>130203;3600@230503;0.08@230603;0.08</t>
+  </si>
+  <si>
+    <t>130203;4400@230503;0.085@230603;0.085</t>
+  </si>
+  <si>
+    <t>130203;5200@230503;0.09@230603;0.09</t>
+  </si>
+  <si>
+    <t>130203;6200@230503;0.095@230603;0.095</t>
+  </si>
+  <si>
+    <t>130203;7200@230503;0.1@230603;0.1</t>
+  </si>
+  <si>
+    <t>130303;75@230503;0.005@230603;0.005</t>
+  </si>
+  <si>
+    <t>130303;150@230503;0.01@230603;0.01</t>
+  </si>
+  <si>
+    <t>130303;225@230503;0.015@230603;0.015</t>
+  </si>
+  <si>
+    <t>130303;300@230503;0.02@230603;0.02</t>
+  </si>
+  <si>
+    <t>130303;400@230503;0.025@230603;0.025</t>
+  </si>
+  <si>
+    <t>130303;500@230503;0.03@230603;0.03</t>
+  </si>
+  <si>
+    <t>130303;650@230503;0.035@230603;0.035</t>
+  </si>
+  <si>
+    <t>130303;800@230503;0.04@230603;0.04</t>
+  </si>
+  <si>
+    <t>130303;1000@230503;0.045@230603;0.045</t>
+  </si>
+  <si>
+    <t>130303;1200@230503;0.05@230603;0.05</t>
+  </si>
+  <si>
+    <t>130303;1450@230503;0.055@230603;0.055</t>
+  </si>
+  <si>
+    <t>130303;1700@230503;0.06@230603;0.06</t>
+  </si>
+  <si>
+    <t>130303;2000@230503;0.065@230603;0.065</t>
+  </si>
+  <si>
+    <t>130303;2400@230503;0.07@230603;0.07</t>
+  </si>
+  <si>
+    <t>130303;3000@230503;0.075@230603;0.075</t>
+  </si>
+  <si>
+    <t>130303;3600@230503;0.08@230603;0.08</t>
+  </si>
+  <si>
+    <t>130303;4400@230503;0.085@230603;0.085</t>
+  </si>
+  <si>
+    <t>130303;5200@230503;0.09@230603;0.09</t>
+  </si>
+  <si>
+    <t>130303;6200@230503;0.095@230603;0.095</t>
+  </si>
+  <si>
+    <t>130303;7200@230503;0.1@230603;0.1</t>
+  </si>
+  <si>
+    <t>130403;375@231403;0.005@230703;0.01</t>
+  </si>
+  <si>
+    <t>130403;750@231403;0.01@230703;0.02</t>
+  </si>
+  <si>
+    <t>130403;1125@231403;0.015@230703;0.03</t>
+  </si>
+  <si>
+    <t>130403;1500@231403;0.02@230703;0.04</t>
+  </si>
+  <si>
+    <t>130403;2000@231403;0.025@230703;0.05</t>
+  </si>
+  <si>
+    <t>130403;2500@231403;0.03@230703;0.06</t>
+  </si>
+  <si>
+    <t>130403;3250@231403;0.035@230703;0.07</t>
+  </si>
+  <si>
+    <t>130403;4000@231403;0.04@230703;0.08</t>
+  </si>
+  <si>
+    <t>130403;5000@231403;0.045@230703;0.09</t>
+  </si>
+  <si>
+    <t>130403;6000@231403;0.05@230703;0.1</t>
+  </si>
+  <si>
+    <t>130403;7250@231403;0.055@230703;0.11</t>
+  </si>
+  <si>
+    <t>130403;8500@231403;0.06@230703;0.12</t>
+  </si>
+  <si>
+    <t>130403;10000@231403;0.065@230703;0.13</t>
+  </si>
+  <si>
+    <t>130403;12000@231403;0.07@230703;0.14</t>
+  </si>
+  <si>
+    <t>130403;15000@231403;0.075@230703;0.15</t>
+  </si>
+  <si>
+    <t>130403;18000@231403;0.08@230703;0.16</t>
+  </si>
+  <si>
+    <t>130403;22000@231403;0.085@230703;0.17</t>
+  </si>
+  <si>
+    <t>130403;26000@231403;0.09@230703;0.18</t>
+  </si>
+  <si>
+    <t>130403;31000@231403;0.095@230703;0.19</t>
+  </si>
+  <si>
+    <t>130403;36000@231403;0.1@230703;0.2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="29">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -354,12 +1140,14 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -367,190 +1155,44 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color indexed="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color indexed="8"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Helvetica Neue"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Helvetica Neue"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Helvetica Neue"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Helvetica Neue"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Helvetica Neue"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Helvetica Neue"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -575,194 +1217,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="16">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -867,251 +1323,9 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1144,57 +1358,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0"/>
   <colors>
     <indexedColors>
@@ -1267,6 +1434,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2337,32 +2507,33 @@
       </a:style>
     </a:txDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="C1:IE13"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="C1:IE110"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5" customHeight="1"/>
   <cols>
     <col min="3" max="3" width="8.5" style="2" customWidth="1"/>
     <col min="4" max="4" width="14.125" style="2" customWidth="1"/>
     <col min="5" max="5" width="30.625" style="2" customWidth="1"/>
     <col min="6" max="10" width="14.125" style="2" customWidth="1"/>
-    <col min="11" max="12" width="24.875" style="2" customWidth="1"/>
+    <col min="11" max="11" width="37.125" style="2" customWidth="1"/>
+    <col min="12" max="12" width="24.875" style="2" customWidth="1"/>
     <col min="13" max="13" width="21.75" style="2" customWidth="1"/>
     <col min="14" max="239" width="8.875" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="14.25"/>
-    <row r="2" customHeight="1" spans="3:239">
+    <row r="1" spans="3:13" s="1" customFormat="1" ht="14.25"/>
+    <row r="2" spans="3:13" ht="13.5" customHeight="1">
       <c r="D2" s="3"/>
       <c r="E2" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" ht="20.1" customHeight="1" spans="3:239">
+    <row r="3" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C3" s="4" t="s">
         <v>1</v>
       </c>
@@ -2397,7 +2568,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" ht="20.1" customHeight="1" spans="3:239">
+    <row r="4" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C4" s="4" t="s">
         <v>1</v>
       </c>
@@ -2432,7 +2603,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" ht="20.1" customHeight="1" spans="3:239">
+    <row r="5" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C5" s="4" t="s">
         <v>21</v>
       </c>
@@ -2467,7 +2638,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" ht="20.1" customHeight="1" spans="3:239">
+    <row r="6" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C6" s="8">
         <v>20100</v>
       </c>
@@ -2489,258 +2660,3716 @@
       <c r="I6" s="11">
         <v>1</v>
       </c>
-      <c r="J6" s="12">
-        <v>100</v>
-      </c>
-      <c r="K6" s="11"/>
+      <c r="J6" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K6" s="11" t="s">
+        <v>79</v>
+      </c>
       <c r="L6" s="11"/>
       <c r="M6" s="11">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="7" ht="19.5" customHeight="1" spans="3:239">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C7" s="8">
         <v>20101</v>
       </c>
       <c r="D7" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" s="8">
+        <v>20102</v>
+      </c>
+      <c r="G7" s="11">
+        <v>0</v>
+      </c>
+      <c r="H7" s="11">
+        <v>0</v>
+      </c>
+      <c r="I7" s="11">
+        <v>1</v>
+      </c>
+      <c r="J7" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K7" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="L7" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="M7" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="3:13" ht="20.100000000000001" customHeight="1">
+      <c r="C8" s="8">
+        <v>20102</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8" s="8">
+        <v>20103</v>
+      </c>
+      <c r="G8" s="11">
+        <v>0</v>
+      </c>
+      <c r="H8" s="11">
+        <v>0</v>
+      </c>
+      <c r="I8" s="11">
+        <v>1</v>
+      </c>
+      <c r="J8" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K8" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="L8" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="M8" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="3:13" ht="20.100000000000001" customHeight="1">
+      <c r="C9" s="8">
+        <v>20103</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="F9" s="8">
+        <v>20104</v>
+      </c>
+      <c r="G9" s="11">
+        <v>0</v>
+      </c>
+      <c r="H9" s="11">
+        <v>0</v>
+      </c>
+      <c r="I9" s="11">
+        <v>1</v>
+      </c>
+      <c r="J9" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K9" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="L9" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="M9" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="3:13" ht="20.100000000000001" customHeight="1">
+      <c r="C10" s="8">
+        <v>20104</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="F10" s="8">
+        <v>20105</v>
+      </c>
+      <c r="G10" s="11">
+        <v>0</v>
+      </c>
+      <c r="H10" s="11">
+        <v>0</v>
+      </c>
+      <c r="I10" s="11">
+        <v>1</v>
+      </c>
+      <c r="J10" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K10" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="L10" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="M10" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="3:13" ht="20.100000000000001" customHeight="1">
+      <c r="C11" s="8">
+        <v>20105</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F11" s="8">
+        <v>20106</v>
+      </c>
+      <c r="G11" s="11">
+        <v>0</v>
+      </c>
+      <c r="H11" s="11">
+        <v>0</v>
+      </c>
+      <c r="I11" s="11">
+        <v>1</v>
+      </c>
+      <c r="J11" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K11" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="L11" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="M11" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="3:13" ht="20.100000000000001" customHeight="1">
+      <c r="C12" s="8">
+        <v>20106</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="F12" s="8">
+        <v>20107</v>
+      </c>
+      <c r="G12" s="11">
+        <v>0</v>
+      </c>
+      <c r="H12" s="11">
+        <v>0</v>
+      </c>
+      <c r="I12" s="11">
+        <v>1</v>
+      </c>
+      <c r="J12" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K12" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="L12" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="M12" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="3:13" ht="20.100000000000001" customHeight="1">
+      <c r="C13" s="8">
+        <v>20107</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="F13" s="8">
+        <v>20108</v>
+      </c>
+      <c r="G13" s="11">
+        <v>0</v>
+      </c>
+      <c r="H13" s="11">
+        <v>0</v>
+      </c>
+      <c r="I13" s="11">
+        <v>1</v>
+      </c>
+      <c r="J13" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K13" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="L13" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="M13" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="3:13" ht="20.100000000000001" customHeight="1">
+      <c r="C14" s="8">
+        <v>20108</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="F14" s="8">
+        <v>20109</v>
+      </c>
+      <c r="G14" s="11">
+        <v>0</v>
+      </c>
+      <c r="H14" s="11">
+        <v>0</v>
+      </c>
+      <c r="I14" s="11">
+        <v>1</v>
+      </c>
+      <c r="J14" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K14" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="L14" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="M14" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="3:13" ht="20.100000000000001" customHeight="1">
+      <c r="C15" s="8">
+        <v>20109</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="F15" s="8">
+        <v>20110</v>
+      </c>
+      <c r="G15" s="11">
+        <v>0</v>
+      </c>
+      <c r="H15" s="11">
+        <v>0</v>
+      </c>
+      <c r="I15" s="11">
+        <v>1</v>
+      </c>
+      <c r="J15" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K15" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="L15" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="M15" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="3:13" ht="20.100000000000001" customHeight="1">
+      <c r="C16" s="8">
+        <v>20110</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F16" s="8">
+        <v>20111</v>
+      </c>
+      <c r="G16" s="11">
+        <v>0</v>
+      </c>
+      <c r="H16" s="11">
+        <v>0</v>
+      </c>
+      <c r="I16" s="11">
+        <v>1</v>
+      </c>
+      <c r="J16" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K16" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="L16" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="M16" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="3:13" ht="20.100000000000001" customHeight="1">
+      <c r="C17" s="8">
+        <v>20111</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="F17" s="8">
+        <v>20112</v>
+      </c>
+      <c r="G17" s="11">
+        <v>0</v>
+      </c>
+      <c r="H17" s="11">
+        <v>0</v>
+      </c>
+      <c r="I17" s="11">
+        <v>1</v>
+      </c>
+      <c r="J17" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K17" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="L17" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="M17" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:13" ht="20.100000000000001" customHeight="1">
+      <c r="C18" s="8">
+        <v>20112</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="F18" s="8">
+        <v>20113</v>
+      </c>
+      <c r="G18" s="11">
+        <v>0</v>
+      </c>
+      <c r="H18" s="11">
+        <v>0</v>
+      </c>
+      <c r="I18" s="11">
+        <v>1</v>
+      </c>
+      <c r="J18" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K18" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="L18" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="M18" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:13" ht="20.100000000000001" customHeight="1">
+      <c r="C19" s="8">
+        <v>20113</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="F19" s="8">
+        <v>20114</v>
+      </c>
+      <c r="G19" s="11">
+        <v>0</v>
+      </c>
+      <c r="H19" s="11">
+        <v>0</v>
+      </c>
+      <c r="I19" s="11">
+        <v>1</v>
+      </c>
+      <c r="J19" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K19" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="L19" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="M19" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="3:13" ht="20.100000000000001" customHeight="1">
+      <c r="C20" s="8">
+        <v>20114</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="F20" s="8">
+        <v>20115</v>
+      </c>
+      <c r="G20" s="11">
+        <v>0</v>
+      </c>
+      <c r="H20" s="11">
+        <v>0</v>
+      </c>
+      <c r="I20" s="11">
+        <v>1</v>
+      </c>
+      <c r="J20" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K20" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="L20" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="M20" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:13" ht="20.100000000000001" customHeight="1">
+      <c r="C21" s="8">
+        <v>20115</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="F21" s="8">
+        <v>20116</v>
+      </c>
+      <c r="G21" s="11">
+        <v>0</v>
+      </c>
+      <c r="H21" s="11">
+        <v>0</v>
+      </c>
+      <c r="I21" s="11">
+        <v>1</v>
+      </c>
+      <c r="J21" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K21" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="L21" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="M21" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="3:13" ht="20.100000000000001" customHeight="1">
+      <c r="C22" s="8">
+        <v>20116</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="F22" s="8">
+        <v>20117</v>
+      </c>
+      <c r="G22" s="11">
+        <v>0</v>
+      </c>
+      <c r="H22" s="11">
+        <v>0</v>
+      </c>
+      <c r="I22" s="11">
+        <v>1</v>
+      </c>
+      <c r="J22" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K22" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="L22" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="M22" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:13" ht="20.100000000000001" customHeight="1">
+      <c r="C23" s="8">
+        <v>20117</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="F23" s="8">
+        <v>20118</v>
+      </c>
+      <c r="G23" s="11">
+        <v>0</v>
+      </c>
+      <c r="H23" s="11">
+        <v>0</v>
+      </c>
+      <c r="I23" s="11">
+        <v>1</v>
+      </c>
+      <c r="J23" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K23" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="L23" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="M23" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:13" ht="20.100000000000001" customHeight="1">
+      <c r="C24" s="8">
+        <v>20118</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="F24" s="8">
+        <v>20119</v>
+      </c>
+      <c r="G24" s="11">
+        <v>0</v>
+      </c>
+      <c r="H24" s="11">
+        <v>0</v>
+      </c>
+      <c r="I24" s="11">
+        <v>1</v>
+      </c>
+      <c r="J24" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K24" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="L24" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="M24" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:13" ht="20.100000000000001" customHeight="1">
+      <c r="C25" s="8">
+        <v>20119</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="F25" s="8">
+        <v>20120</v>
+      </c>
+      <c r="G25" s="11">
+        <v>0</v>
+      </c>
+      <c r="H25" s="11">
+        <v>0</v>
+      </c>
+      <c r="I25" s="11">
+        <v>1</v>
+      </c>
+      <c r="J25" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K25" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="L25" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="M25" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" ht="20.100000000000001" customHeight="1">
+      <c r="C26" s="8">
+        <v>20120</v>
+      </c>
+      <c r="D26" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="E26" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="F7" s="8">
-        <v>0</v>
-      </c>
-      <c r="G7" s="11">
-        <v>20</v>
-      </c>
-      <c r="H7" s="11">
-        <v>0</v>
-      </c>
-      <c r="I7" s="11">
-        <v>0.3</v>
-      </c>
-      <c r="J7" s="12" t="s">
+      <c r="F26" s="8">
+        <v>0</v>
+      </c>
+      <c r="G26" s="11">
+        <v>0</v>
+      </c>
+      <c r="H26" s="11">
+        <v>0</v>
+      </c>
+      <c r="I26" s="11">
+        <v>1</v>
+      </c>
+      <c r="J26" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K26" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="L26" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="M26" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:13" ht="20.100000000000001" customHeight="1">
+      <c r="C27" s="8">
+        <v>20200</v>
+      </c>
+      <c r="D27" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="K7" s="11" t="s">
+      <c r="E27" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="L7" s="11" t="s">
+      <c r="F27" s="8">
+        <v>20201</v>
+      </c>
+      <c r="G27" s="11">
+        <v>0</v>
+      </c>
+      <c r="H27" s="11">
+        <v>0</v>
+      </c>
+      <c r="I27" s="11">
+        <v>1</v>
+      </c>
+      <c r="J27" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K27" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="L27" s="11"/>
+      <c r="M27" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:13" ht="20.100000000000001" customHeight="1">
+      <c r="C28" s="8">
+        <v>20201</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="F28" s="8">
+        <v>20202</v>
+      </c>
+      <c r="G28" s="11">
+        <v>0</v>
+      </c>
+      <c r="H28" s="11">
+        <v>0</v>
+      </c>
+      <c r="I28" s="11">
+        <v>1</v>
+      </c>
+      <c r="J28" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K28" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="L28" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="M28" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13" ht="20.100000000000001" customHeight="1">
+      <c r="C29" s="8">
+        <v>20202</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="F29" s="8">
+        <v>20203</v>
+      </c>
+      <c r="G29" s="11">
+        <v>0</v>
+      </c>
+      <c r="H29" s="11">
+        <v>0</v>
+      </c>
+      <c r="I29" s="11">
+        <v>1</v>
+      </c>
+      <c r="J29" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K29" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="L29" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="M29" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13" ht="20.100000000000001" customHeight="1">
+      <c r="C30" s="8">
+        <v>20203</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="E30" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="F30" s="8">
+        <v>20204</v>
+      </c>
+      <c r="G30" s="11">
+        <v>0</v>
+      </c>
+      <c r="H30" s="11">
+        <v>0</v>
+      </c>
+      <c r="I30" s="11">
+        <v>1</v>
+      </c>
+      <c r="J30" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K30" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="L30" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="M30" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" ht="20.100000000000001" customHeight="1">
+      <c r="C31" s="8">
+        <v>20204</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="F31" s="8">
+        <v>20205</v>
+      </c>
+      <c r="G31" s="11">
+        <v>0</v>
+      </c>
+      <c r="H31" s="11">
+        <v>0</v>
+      </c>
+      <c r="I31" s="11">
+        <v>1</v>
+      </c>
+      <c r="J31" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K31" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="L31" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="M31" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13" ht="20.100000000000001" customHeight="1">
+      <c r="C32" s="8">
+        <v>20205</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="E32" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="F32" s="8">
+        <v>20206</v>
+      </c>
+      <c r="G32" s="11">
+        <v>0</v>
+      </c>
+      <c r="H32" s="11">
+        <v>0</v>
+      </c>
+      <c r="I32" s="11">
+        <v>1</v>
+      </c>
+      <c r="J32" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K32" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="L32" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="M32" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="3:13" ht="20.100000000000001" customHeight="1">
+      <c r="C33" s="8">
+        <v>20206</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="F33" s="8">
+        <v>20207</v>
+      </c>
+      <c r="G33" s="11">
+        <v>0</v>
+      </c>
+      <c r="H33" s="11">
+        <v>0</v>
+      </c>
+      <c r="I33" s="11">
+        <v>1</v>
+      </c>
+      <c r="J33" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K33" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="L33" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="M33" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="3:13" ht="20.100000000000001" customHeight="1">
+      <c r="C34" s="8">
+        <v>20207</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="E34" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="F34" s="8">
+        <v>20208</v>
+      </c>
+      <c r="G34" s="11">
+        <v>0</v>
+      </c>
+      <c r="H34" s="11">
+        <v>0</v>
+      </c>
+      <c r="I34" s="11">
+        <v>1</v>
+      </c>
+      <c r="J34" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K34" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="L34" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="M34" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="3:13" ht="20.100000000000001" customHeight="1">
+      <c r="C35" s="8">
+        <v>20208</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="E35" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="F35" s="8">
+        <v>20209</v>
+      </c>
+      <c r="G35" s="11">
+        <v>0</v>
+      </c>
+      <c r="H35" s="11">
+        <v>0</v>
+      </c>
+      <c r="I35" s="11">
+        <v>1</v>
+      </c>
+      <c r="J35" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K35" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="L35" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="M35" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="3:13" ht="20.100000000000001" customHeight="1">
+      <c r="C36" s="8">
+        <v>20209</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="E36" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="F36" s="8">
+        <v>20210</v>
+      </c>
+      <c r="G36" s="11">
+        <v>0</v>
+      </c>
+      <c r="H36" s="11">
+        <v>0</v>
+      </c>
+      <c r="I36" s="11">
+        <v>1</v>
+      </c>
+      <c r="J36" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K36" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="L36" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="M36" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="3:13" ht="20.100000000000001" customHeight="1">
+      <c r="C37" s="8">
+        <v>20210</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="E37" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="F37" s="8">
+        <v>20211</v>
+      </c>
+      <c r="G37" s="11">
+        <v>0</v>
+      </c>
+      <c r="H37" s="11">
+        <v>0</v>
+      </c>
+      <c r="I37" s="11">
+        <v>1</v>
+      </c>
+      <c r="J37" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K37" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="L37" s="11" t="s">
+        <v>242</v>
+      </c>
+      <c r="M37" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="3:13" ht="20.100000000000001" customHeight="1">
+      <c r="C38" s="8">
+        <v>20211</v>
+      </c>
+      <c r="D38" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="E38" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="F38" s="8">
+        <v>20212</v>
+      </c>
+      <c r="G38" s="11">
+        <v>0</v>
+      </c>
+      <c r="H38" s="11">
+        <v>0</v>
+      </c>
+      <c r="I38" s="11">
+        <v>1</v>
+      </c>
+      <c r="J38" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K38" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="L38" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="M38" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="3:13" ht="20.100000000000001" customHeight="1">
+      <c r="C39" s="8">
+        <v>20212</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E39" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="F39" s="8">
+        <v>20213</v>
+      </c>
+      <c r="G39" s="11">
+        <v>0</v>
+      </c>
+      <c r="H39" s="11">
+        <v>0</v>
+      </c>
+      <c r="I39" s="11">
+        <v>1</v>
+      </c>
+      <c r="J39" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K39" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="L39" s="11" t="s">
+        <v>244</v>
+      </c>
+      <c r="M39" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="3:13" ht="20.100000000000001" customHeight="1">
+      <c r="C40" s="8">
+        <v>20213</v>
+      </c>
+      <c r="D40" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="E40" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="F40" s="8">
+        <v>20214</v>
+      </c>
+      <c r="G40" s="11">
+        <v>0</v>
+      </c>
+      <c r="H40" s="11">
+        <v>0</v>
+      </c>
+      <c r="I40" s="11">
+        <v>1</v>
+      </c>
+      <c r="J40" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K40" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="L40" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="M40" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="3:13" ht="20.100000000000001" customHeight="1">
+      <c r="C41" s="8">
+        <v>20214</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="E41" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="F41" s="8">
+        <v>20215</v>
+      </c>
+      <c r="G41" s="11">
+        <v>0</v>
+      </c>
+      <c r="H41" s="11">
+        <v>0</v>
+      </c>
+      <c r="I41" s="11">
+        <v>1</v>
+      </c>
+      <c r="J41" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K41" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="L41" s="11" t="s">
+        <v>246</v>
+      </c>
+      <c r="M41" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="3:13" ht="20.100000000000001" customHeight="1">
+      <c r="C42" s="8">
+        <v>20215</v>
+      </c>
+      <c r="D42" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="E42" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="F42" s="8">
+        <v>20216</v>
+      </c>
+      <c r="G42" s="11">
+        <v>0</v>
+      </c>
+      <c r="H42" s="11">
+        <v>0</v>
+      </c>
+      <c r="I42" s="11">
+        <v>1</v>
+      </c>
+      <c r="J42" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K42" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="L42" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="M42" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="3:13" ht="20.100000000000001" customHeight="1">
+      <c r="C43" s="8">
+        <v>20216</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="E43" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="F43" s="8">
+        <v>20217</v>
+      </c>
+      <c r="G43" s="11">
+        <v>0</v>
+      </c>
+      <c r="H43" s="11">
+        <v>0</v>
+      </c>
+      <c r="I43" s="11">
+        <v>1</v>
+      </c>
+      <c r="J43" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K43" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="L43" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="M43" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="3:13" ht="20.100000000000001" customHeight="1">
+      <c r="C44" s="8">
+        <v>20217</v>
+      </c>
+      <c r="D44" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="E44" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="F44" s="8">
+        <v>20218</v>
+      </c>
+      <c r="G44" s="11">
+        <v>0</v>
+      </c>
+      <c r="H44" s="11">
+        <v>0</v>
+      </c>
+      <c r="I44" s="11">
+        <v>1</v>
+      </c>
+      <c r="J44" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K44" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="L44" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="M44" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="3:13" ht="20.100000000000001" customHeight="1">
+      <c r="C45" s="8">
+        <v>20218</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="E45" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="F45" s="8">
+        <v>20219</v>
+      </c>
+      <c r="G45" s="11">
+        <v>0</v>
+      </c>
+      <c r="H45" s="11">
+        <v>0</v>
+      </c>
+      <c r="I45" s="11">
+        <v>1</v>
+      </c>
+      <c r="J45" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K45" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="L45" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="M45" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="3:13" ht="20.100000000000001" customHeight="1">
+      <c r="C46" s="8">
+        <v>20219</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="E46" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="F46" s="8">
+        <v>20220</v>
+      </c>
+      <c r="G46" s="11">
+        <v>0</v>
+      </c>
+      <c r="H46" s="11">
+        <v>0</v>
+      </c>
+      <c r="I46" s="11">
+        <v>1</v>
+      </c>
+      <c r="J46" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K46" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="L46" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="M46" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="3:13" ht="20.100000000000001" customHeight="1">
+      <c r="C47" s="8">
+        <v>20220</v>
+      </c>
+      <c r="D47" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="M7" s="11">
-        <v>0.02</v>
-      </c>
-      <c r="IE7"/>
-    </row>
-    <row r="8" ht="22.5" customHeight="1" spans="3:239">
-      <c r="C8" s="8">
-        <v>20200</v>
-      </c>
-      <c r="D8" s="9" t="s">
+      <c r="E47" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="F47" s="8">
+        <v>0</v>
+      </c>
+      <c r="G47" s="11">
+        <v>0</v>
+      </c>
+      <c r="H47" s="11">
+        <v>0</v>
+      </c>
+      <c r="I47" s="11">
+        <v>1</v>
+      </c>
+      <c r="J47" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K47" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="L47" s="11" t="s">
+        <v>252</v>
+      </c>
+      <c r="M47" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="3:13" ht="22.5" customHeight="1">
+      <c r="C48" s="8">
+        <v>20300</v>
+      </c>
+      <c r="D48" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="F8" s="8">
-        <v>20201</v>
-      </c>
-      <c r="G8" s="11">
-        <v>0</v>
-      </c>
-      <c r="H8" s="11">
-        <v>0</v>
-      </c>
-      <c r="I8" s="11">
-        <v>1</v>
-      </c>
-      <c r="J8" s="12">
-        <v>100</v>
-      </c>
-      <c r="K8" s="11"/>
-      <c r="L8" s="11"/>
-      <c r="M8" s="11">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="9" ht="19.5" customHeight="1" spans="3:239">
-      <c r="C9" s="8">
-        <v>20201</v>
-      </c>
-      <c r="D9" s="9" t="s">
+      <c r="E48" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="F48" s="8">
+        <v>20301</v>
+      </c>
+      <c r="G48" s="11">
+        <v>0</v>
+      </c>
+      <c r="H48" s="11">
+        <v>0</v>
+      </c>
+      <c r="I48" s="11">
+        <v>1</v>
+      </c>
+      <c r="J48" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K48" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="L48" s="11"/>
+      <c r="M48" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C49" s="8">
+        <v>20301</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="E49" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="F49" s="8">
+        <v>20302</v>
+      </c>
+      <c r="G49" s="11">
+        <v>0</v>
+      </c>
+      <c r="H49" s="11">
+        <v>0</v>
+      </c>
+      <c r="I49" s="11">
+        <v>1</v>
+      </c>
+      <c r="J49" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K49" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="L49" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="M49" s="11">
+        <v>0</v>
+      </c>
+      <c r="IE49"/>
+    </row>
+    <row r="50" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C50" s="8">
+        <v>20302</v>
+      </c>
+      <c r="D50" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="E50" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="F50" s="8">
+        <v>20303</v>
+      </c>
+      <c r="G50" s="11">
+        <v>0</v>
+      </c>
+      <c r="H50" s="11">
+        <v>0</v>
+      </c>
+      <c r="I50" s="11">
+        <v>1</v>
+      </c>
+      <c r="J50" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K50" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="L50" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="M50" s="11">
+        <v>0</v>
+      </c>
+      <c r="IE50"/>
+    </row>
+    <row r="51" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C51" s="8">
+        <v>20303</v>
+      </c>
+      <c r="D51" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="E51" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="F51" s="8">
+        <v>20304</v>
+      </c>
+      <c r="G51" s="11">
+        <v>0</v>
+      </c>
+      <c r="H51" s="11">
+        <v>0</v>
+      </c>
+      <c r="I51" s="11">
+        <v>1</v>
+      </c>
+      <c r="J51" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K51" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="L51" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="M51" s="11">
+        <v>0</v>
+      </c>
+      <c r="IE51"/>
+    </row>
+    <row r="52" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C52" s="8">
+        <v>20304</v>
+      </c>
+      <c r="D52" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="E52" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="F52" s="8">
+        <v>20305</v>
+      </c>
+      <c r="G52" s="11">
+        <v>0</v>
+      </c>
+      <c r="H52" s="11">
+        <v>0</v>
+      </c>
+      <c r="I52" s="11">
+        <v>1</v>
+      </c>
+      <c r="J52" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K52" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="L52" s="11" t="s">
+        <v>256</v>
+      </c>
+      <c r="M52" s="11">
+        <v>0</v>
+      </c>
+      <c r="IE52"/>
+    </row>
+    <row r="53" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C53" s="8">
+        <v>20305</v>
+      </c>
+      <c r="D53" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="E53" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="F53" s="8">
+        <v>20306</v>
+      </c>
+      <c r="G53" s="11">
+        <v>0</v>
+      </c>
+      <c r="H53" s="11">
+        <v>0</v>
+      </c>
+      <c r="I53" s="11">
+        <v>1</v>
+      </c>
+      <c r="J53" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K53" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="L53" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="M53" s="11">
+        <v>0</v>
+      </c>
+      <c r="IE53"/>
+    </row>
+    <row r="54" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C54" s="8">
+        <v>20306</v>
+      </c>
+      <c r="D54" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="E54" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="F54" s="8">
+        <v>20307</v>
+      </c>
+      <c r="G54" s="11">
+        <v>0</v>
+      </c>
+      <c r="H54" s="11">
+        <v>0</v>
+      </c>
+      <c r="I54" s="11">
+        <v>1</v>
+      </c>
+      <c r="J54" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K54" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="L54" s="11" t="s">
+        <v>258</v>
+      </c>
+      <c r="M54" s="11">
+        <v>0</v>
+      </c>
+      <c r="IE54"/>
+    </row>
+    <row r="55" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C55" s="8">
+        <v>20307</v>
+      </c>
+      <c r="D55" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="E55" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="F55" s="8">
+        <v>20308</v>
+      </c>
+      <c r="G55" s="11">
+        <v>0</v>
+      </c>
+      <c r="H55" s="11">
+        <v>0</v>
+      </c>
+      <c r="I55" s="11">
+        <v>1</v>
+      </c>
+      <c r="J55" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K55" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="L55" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="M55" s="11">
+        <v>0</v>
+      </c>
+      <c r="IE55"/>
+    </row>
+    <row r="56" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C56" s="8">
+        <v>20308</v>
+      </c>
+      <c r="D56" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="E56" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="F56" s="8">
+        <v>20309</v>
+      </c>
+      <c r="G56" s="11">
+        <v>0</v>
+      </c>
+      <c r="H56" s="11">
+        <v>0</v>
+      </c>
+      <c r="I56" s="11">
+        <v>1</v>
+      </c>
+      <c r="J56" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K56" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="L56" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="M56" s="11">
+        <v>0</v>
+      </c>
+      <c r="IE56"/>
+    </row>
+    <row r="57" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C57" s="8">
+        <v>20309</v>
+      </c>
+      <c r="D57" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="E57" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="F57" s="8">
+        <v>20310</v>
+      </c>
+      <c r="G57" s="11">
+        <v>0</v>
+      </c>
+      <c r="H57" s="11">
+        <v>0</v>
+      </c>
+      <c r="I57" s="11">
+        <v>1</v>
+      </c>
+      <c r="J57" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K57" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="L57" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="M57" s="11">
+        <v>0</v>
+      </c>
+      <c r="IE57"/>
+    </row>
+    <row r="58" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C58" s="8">
+        <v>20310</v>
+      </c>
+      <c r="D58" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="E58" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="F58" s="8">
+        <v>20311</v>
+      </c>
+      <c r="G58" s="11">
+        <v>0</v>
+      </c>
+      <c r="H58" s="11">
+        <v>0</v>
+      </c>
+      <c r="I58" s="11">
+        <v>1</v>
+      </c>
+      <c r="J58" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K58" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="L58" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="M58" s="11">
+        <v>0</v>
+      </c>
+      <c r="IE58"/>
+    </row>
+    <row r="59" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C59" s="8">
+        <v>20311</v>
+      </c>
+      <c r="D59" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="E59" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="F59" s="8">
+        <v>20312</v>
+      </c>
+      <c r="G59" s="11">
+        <v>0</v>
+      </c>
+      <c r="H59" s="11">
+        <v>0</v>
+      </c>
+      <c r="I59" s="11">
+        <v>1</v>
+      </c>
+      <c r="J59" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K59" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="L59" s="11" t="s">
+        <v>263</v>
+      </c>
+      <c r="M59" s="11">
+        <v>0</v>
+      </c>
+      <c r="IE59"/>
+    </row>
+    <row r="60" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C60" s="8">
+        <v>20312</v>
+      </c>
+      <c r="D60" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="E60" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="F60" s="8">
+        <v>20313</v>
+      </c>
+      <c r="G60" s="11">
+        <v>0</v>
+      </c>
+      <c r="H60" s="11">
+        <v>0</v>
+      </c>
+      <c r="I60" s="11">
+        <v>1</v>
+      </c>
+      <c r="J60" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K60" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="L60" s="11" t="s">
+        <v>264</v>
+      </c>
+      <c r="M60" s="11">
+        <v>0</v>
+      </c>
+      <c r="IE60"/>
+    </row>
+    <row r="61" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C61" s="8">
+        <v>20313</v>
+      </c>
+      <c r="D61" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="E61" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="F61" s="8">
+        <v>20314</v>
+      </c>
+      <c r="G61" s="11">
+        <v>0</v>
+      </c>
+      <c r="H61" s="11">
+        <v>0</v>
+      </c>
+      <c r="I61" s="11">
+        <v>1</v>
+      </c>
+      <c r="J61" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K61" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="L61" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="M61" s="11">
+        <v>0</v>
+      </c>
+      <c r="IE61"/>
+    </row>
+    <row r="62" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C62" s="8">
+        <v>20314</v>
+      </c>
+      <c r="D62" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="E62" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="F62" s="8">
+        <v>20315</v>
+      </c>
+      <c r="G62" s="11">
+        <v>0</v>
+      </c>
+      <c r="H62" s="11">
+        <v>0</v>
+      </c>
+      <c r="I62" s="11">
+        <v>1</v>
+      </c>
+      <c r="J62" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K62" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="L62" s="11" t="s">
+        <v>266</v>
+      </c>
+      <c r="M62" s="11">
+        <v>0</v>
+      </c>
+      <c r="IE62"/>
+    </row>
+    <row r="63" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C63" s="8">
+        <v>20315</v>
+      </c>
+      <c r="D63" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="E63" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="F63" s="8">
+        <v>20316</v>
+      </c>
+      <c r="G63" s="11">
+        <v>0</v>
+      </c>
+      <c r="H63" s="11">
+        <v>0</v>
+      </c>
+      <c r="I63" s="11">
+        <v>1</v>
+      </c>
+      <c r="J63" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K63" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="L63" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="M63" s="11">
+        <v>0</v>
+      </c>
+      <c r="IE63"/>
+    </row>
+    <row r="64" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C64" s="8">
+        <v>20316</v>
+      </c>
+      <c r="D64" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="E64" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="F64" s="8">
+        <v>20317</v>
+      </c>
+      <c r="G64" s="11">
+        <v>0</v>
+      </c>
+      <c r="H64" s="11">
+        <v>0</v>
+      </c>
+      <c r="I64" s="11">
+        <v>1</v>
+      </c>
+      <c r="J64" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K64" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="L64" s="11" t="s">
+        <v>268</v>
+      </c>
+      <c r="M64" s="11">
+        <v>0</v>
+      </c>
+      <c r="IE64"/>
+    </row>
+    <row r="65" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C65" s="8">
+        <v>20317</v>
+      </c>
+      <c r="D65" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="E65" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="F65" s="8">
+        <v>20318</v>
+      </c>
+      <c r="G65" s="11">
+        <v>0</v>
+      </c>
+      <c r="H65" s="11">
+        <v>0</v>
+      </c>
+      <c r="I65" s="11">
+        <v>1</v>
+      </c>
+      <c r="J65" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K65" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="L65" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="M65" s="11">
+        <v>0</v>
+      </c>
+      <c r="IE65"/>
+    </row>
+    <row r="66" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C66" s="8">
+        <v>20318</v>
+      </c>
+      <c r="D66" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="E66" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="F66" s="8">
+        <v>20319</v>
+      </c>
+      <c r="G66" s="11">
+        <v>0</v>
+      </c>
+      <c r="H66" s="11">
+        <v>0</v>
+      </c>
+      <c r="I66" s="11">
+        <v>1</v>
+      </c>
+      <c r="J66" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K66" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="L66" s="11" t="s">
+        <v>270</v>
+      </c>
+      <c r="M66" s="11">
+        <v>0</v>
+      </c>
+      <c r="IE66"/>
+    </row>
+    <row r="67" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C67" s="8">
+        <v>20319</v>
+      </c>
+      <c r="D67" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="E67" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="F67" s="8">
+        <v>20320</v>
+      </c>
+      <c r="G67" s="11">
+        <v>0</v>
+      </c>
+      <c r="H67" s="11">
+        <v>0</v>
+      </c>
+      <c r="I67" s="11">
+        <v>1</v>
+      </c>
+      <c r="J67" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K67" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="L67" s="11" t="s">
+        <v>271</v>
+      </c>
+      <c r="M67" s="11">
+        <v>0</v>
+      </c>
+      <c r="IE67"/>
+    </row>
+    <row r="68" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C68" s="8">
+        <v>20320</v>
+      </c>
+      <c r="D68" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="F9" s="8">
-        <v>0</v>
-      </c>
-      <c r="G9" s="11">
-        <v>20</v>
-      </c>
-      <c r="H9" s="11">
-        <v>0</v>
-      </c>
-      <c r="I9" s="11">
-        <v>0.3</v>
-      </c>
-      <c r="J9" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="K9" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="L9" s="11" t="s">
+      <c r="E68" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="M9" s="11">
-        <v>0.02</v>
-      </c>
-      <c r="IE9"/>
-    </row>
-    <row r="10" ht="22.5" customHeight="1" spans="3:239">
-      <c r="C10" s="8">
-        <v>20300</v>
-      </c>
-      <c r="D10" s="9" t="s">
+      <c r="F68" s="8">
+        <v>0</v>
+      </c>
+      <c r="G68" s="11">
+        <v>0</v>
+      </c>
+      <c r="H68" s="11">
+        <v>0</v>
+      </c>
+      <c r="I68" s="11">
+        <v>1</v>
+      </c>
+      <c r="J68" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K68" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="L68" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="M68" s="11">
+        <v>0</v>
+      </c>
+      <c r="IE68"/>
+    </row>
+    <row r="69" spans="3:239" ht="22.5" customHeight="1">
+      <c r="C69" s="8">
+        <v>20400</v>
+      </c>
+      <c r="D69" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="E69" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="F10" s="8">
-        <v>20301</v>
-      </c>
-      <c r="G10" s="11">
-        <v>0</v>
-      </c>
-      <c r="H10" s="11">
-        <v>0</v>
-      </c>
-      <c r="I10" s="11">
-        <v>1</v>
-      </c>
-      <c r="J10" s="12">
-        <v>100</v>
-      </c>
-      <c r="K10" s="11"/>
-      <c r="L10" s="11"/>
-      <c r="M10" s="11">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="11" ht="19.5" customHeight="1" spans="3:239">
-      <c r="C11" s="8">
-        <v>20301</v>
-      </c>
-      <c r="D11" s="9" t="s">
+      <c r="F69" s="8">
+        <v>20401</v>
+      </c>
+      <c r="G69" s="11">
+        <v>0</v>
+      </c>
+      <c r="H69" s="11">
+        <v>0</v>
+      </c>
+      <c r="I69" s="11">
+        <v>1</v>
+      </c>
+      <c r="J69" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K69" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="L69" s="11"/>
+      <c r="M69" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C70" s="8">
+        <v>20401</v>
+      </c>
+      <c r="D70" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="E70" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="F70" s="8">
+        <v>20402</v>
+      </c>
+      <c r="G70" s="11">
+        <v>0</v>
+      </c>
+      <c r="H70" s="11">
+        <v>0</v>
+      </c>
+      <c r="I70" s="11">
+        <v>1</v>
+      </c>
+      <c r="J70" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K70" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="L70" s="11" t="s">
+        <v>273</v>
+      </c>
+      <c r="M70" s="11">
+        <v>0</v>
+      </c>
+      <c r="IE70"/>
+    </row>
+    <row r="71" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C71" s="8">
+        <v>20402</v>
+      </c>
+      <c r="D71" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="E71" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="F71" s="8">
+        <v>20403</v>
+      </c>
+      <c r="G71" s="11">
+        <v>0</v>
+      </c>
+      <c r="H71" s="11">
+        <v>0</v>
+      </c>
+      <c r="I71" s="11">
+        <v>1</v>
+      </c>
+      <c r="J71" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K71" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="L71" s="11" t="s">
+        <v>274</v>
+      </c>
+      <c r="M71" s="11">
+        <v>0</v>
+      </c>
+      <c r="IE71"/>
+    </row>
+    <row r="72" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C72" s="8">
+        <v>20403</v>
+      </c>
+      <c r="D72" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="E72" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="F72" s="8">
+        <v>20404</v>
+      </c>
+      <c r="G72" s="11">
+        <v>0</v>
+      </c>
+      <c r="H72" s="11">
+        <v>0</v>
+      </c>
+      <c r="I72" s="11">
+        <v>1</v>
+      </c>
+      <c r="J72" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K72" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="L72" s="11" t="s">
+        <v>275</v>
+      </c>
+      <c r="M72" s="11">
+        <v>0</v>
+      </c>
+      <c r="IE72"/>
+    </row>
+    <row r="73" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C73" s="8">
+        <v>20404</v>
+      </c>
+      <c r="D73" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="E73" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="F73" s="8">
+        <v>20405</v>
+      </c>
+      <c r="G73" s="11">
+        <v>0</v>
+      </c>
+      <c r="H73" s="11">
+        <v>0</v>
+      </c>
+      <c r="I73" s="11">
+        <v>1</v>
+      </c>
+      <c r="J73" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K73" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="L73" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="M73" s="11">
+        <v>0</v>
+      </c>
+      <c r="IE73"/>
+    </row>
+    <row r="74" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C74" s="8">
+        <v>20405</v>
+      </c>
+      <c r="D74" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="E74" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="F74" s="8">
+        <v>20406</v>
+      </c>
+      <c r="G74" s="11">
+        <v>0</v>
+      </c>
+      <c r="H74" s="11">
+        <v>0</v>
+      </c>
+      <c r="I74" s="11">
+        <v>1</v>
+      </c>
+      <c r="J74" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K74" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="L74" s="11" t="s">
+        <v>277</v>
+      </c>
+      <c r="M74" s="11">
+        <v>0</v>
+      </c>
+      <c r="IE74"/>
+    </row>
+    <row r="75" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C75" s="8">
+        <v>20406</v>
+      </c>
+      <c r="D75" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="E75" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="F75" s="8">
+        <v>20407</v>
+      </c>
+      <c r="G75" s="11">
+        <v>0</v>
+      </c>
+      <c r="H75" s="11">
+        <v>0</v>
+      </c>
+      <c r="I75" s="11">
+        <v>1</v>
+      </c>
+      <c r="J75" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K75" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="L75" s="11" t="s">
+        <v>278</v>
+      </c>
+      <c r="M75" s="11">
+        <v>0</v>
+      </c>
+      <c r="IE75"/>
+    </row>
+    <row r="76" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C76" s="8">
+        <v>20407</v>
+      </c>
+      <c r="D76" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="E76" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="F76" s="8">
+        <v>20408</v>
+      </c>
+      <c r="G76" s="11">
+        <v>0</v>
+      </c>
+      <c r="H76" s="11">
+        <v>0</v>
+      </c>
+      <c r="I76" s="11">
+        <v>1</v>
+      </c>
+      <c r="J76" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K76" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="L76" s="11" t="s">
+        <v>279</v>
+      </c>
+      <c r="M76" s="11">
+        <v>0</v>
+      </c>
+      <c r="IE76"/>
+    </row>
+    <row r="77" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C77" s="8">
+        <v>20408</v>
+      </c>
+      <c r="D77" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="E77" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="F77" s="8">
+        <v>20409</v>
+      </c>
+      <c r="G77" s="11">
+        <v>0</v>
+      </c>
+      <c r="H77" s="11">
+        <v>0</v>
+      </c>
+      <c r="I77" s="11">
+        <v>1</v>
+      </c>
+      <c r="J77" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K77" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="L77" s="11" t="s">
+        <v>280</v>
+      </c>
+      <c r="M77" s="11">
+        <v>0</v>
+      </c>
+      <c r="IE77"/>
+    </row>
+    <row r="78" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C78" s="8">
+        <v>20409</v>
+      </c>
+      <c r="D78" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="E78" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="F78" s="8">
+        <v>20410</v>
+      </c>
+      <c r="G78" s="11">
+        <v>0</v>
+      </c>
+      <c r="H78" s="11">
+        <v>0</v>
+      </c>
+      <c r="I78" s="11">
+        <v>1</v>
+      </c>
+      <c r="J78" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K78" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="L78" s="11" t="s">
+        <v>281</v>
+      </c>
+      <c r="M78" s="11">
+        <v>0</v>
+      </c>
+      <c r="IE78"/>
+    </row>
+    <row r="79" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C79" s="8">
+        <v>20410</v>
+      </c>
+      <c r="D79" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="E79" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="F79" s="8">
+        <v>20411</v>
+      </c>
+      <c r="G79" s="11">
+        <v>0</v>
+      </c>
+      <c r="H79" s="11">
+        <v>0</v>
+      </c>
+      <c r="I79" s="11">
+        <v>1</v>
+      </c>
+      <c r="J79" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K79" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="L79" s="11" t="s">
+        <v>282</v>
+      </c>
+      <c r="M79" s="11">
+        <v>0</v>
+      </c>
+      <c r="IE79"/>
+    </row>
+    <row r="80" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C80" s="8">
+        <v>20411</v>
+      </c>
+      <c r="D80" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="E80" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="F80" s="8">
+        <v>20412</v>
+      </c>
+      <c r="G80" s="11">
+        <v>0</v>
+      </c>
+      <c r="H80" s="11">
+        <v>0</v>
+      </c>
+      <c r="I80" s="11">
+        <v>1</v>
+      </c>
+      <c r="J80" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K80" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="L80" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="M80" s="11">
+        <v>0</v>
+      </c>
+      <c r="IE80"/>
+    </row>
+    <row r="81" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C81" s="8">
+        <v>20412</v>
+      </c>
+      <c r="D81" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="E81" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="F81" s="8">
+        <v>20413</v>
+      </c>
+      <c r="G81" s="11">
+        <v>0</v>
+      </c>
+      <c r="H81" s="11">
+        <v>0</v>
+      </c>
+      <c r="I81" s="11">
+        <v>1</v>
+      </c>
+      <c r="J81" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K81" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="L81" s="11" t="s">
+        <v>284</v>
+      </c>
+      <c r="M81" s="11">
+        <v>0</v>
+      </c>
+      <c r="IE81"/>
+    </row>
+    <row r="82" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C82" s="8">
+        <v>20413</v>
+      </c>
+      <c r="D82" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="E82" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="F82" s="8">
+        <v>20414</v>
+      </c>
+      <c r="G82" s="11">
+        <v>0</v>
+      </c>
+      <c r="H82" s="11">
+        <v>0</v>
+      </c>
+      <c r="I82" s="11">
+        <v>1</v>
+      </c>
+      <c r="J82" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K82" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="L82" s="11" t="s">
+        <v>285</v>
+      </c>
+      <c r="M82" s="11">
+        <v>0</v>
+      </c>
+      <c r="IE82"/>
+    </row>
+    <row r="83" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C83" s="8">
+        <v>20414</v>
+      </c>
+      <c r="D83" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="E83" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="F83" s="8">
+        <v>20415</v>
+      </c>
+      <c r="G83" s="11">
+        <v>0</v>
+      </c>
+      <c r="H83" s="11">
+        <v>0</v>
+      </c>
+      <c r="I83" s="11">
+        <v>1</v>
+      </c>
+      <c r="J83" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K83" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="L83" s="11" t="s">
+        <v>286</v>
+      </c>
+      <c r="M83" s="11">
+        <v>0</v>
+      </c>
+      <c r="IE83"/>
+    </row>
+    <row r="84" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C84" s="8">
+        <v>20415</v>
+      </c>
+      <c r="D84" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="E84" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="F84" s="8">
+        <v>20416</v>
+      </c>
+      <c r="G84" s="11">
+        <v>0</v>
+      </c>
+      <c r="H84" s="11">
+        <v>0</v>
+      </c>
+      <c r="I84" s="11">
+        <v>1</v>
+      </c>
+      <c r="J84" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K84" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="L84" s="11" t="s">
+        <v>287</v>
+      </c>
+      <c r="M84" s="11">
+        <v>0</v>
+      </c>
+      <c r="IE84"/>
+    </row>
+    <row r="85" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C85" s="8">
+        <v>20416</v>
+      </c>
+      <c r="D85" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="E85" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="F85" s="8">
+        <v>20417</v>
+      </c>
+      <c r="G85" s="11">
+        <v>0</v>
+      </c>
+      <c r="H85" s="11">
+        <v>0</v>
+      </c>
+      <c r="I85" s="11">
+        <v>1</v>
+      </c>
+      <c r="J85" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K85" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="L85" s="11" t="s">
+        <v>288</v>
+      </c>
+      <c r="M85" s="11">
+        <v>0</v>
+      </c>
+      <c r="IE85"/>
+    </row>
+    <row r="86" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C86" s="8">
+        <v>20417</v>
+      </c>
+      <c r="D86" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="E86" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="F86" s="8">
+        <v>20418</v>
+      </c>
+      <c r="G86" s="11">
+        <v>0</v>
+      </c>
+      <c r="H86" s="11">
+        <v>0</v>
+      </c>
+      <c r="I86" s="11">
+        <v>1</v>
+      </c>
+      <c r="J86" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K86" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="L86" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="M86" s="11">
+        <v>0</v>
+      </c>
+      <c r="IE86"/>
+    </row>
+    <row r="87" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C87" s="8">
+        <v>20418</v>
+      </c>
+      <c r="D87" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="E87" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="F87" s="8">
+        <v>20419</v>
+      </c>
+      <c r="G87" s="11">
+        <v>0</v>
+      </c>
+      <c r="H87" s="11">
+        <v>0</v>
+      </c>
+      <c r="I87" s="11">
+        <v>1</v>
+      </c>
+      <c r="J87" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K87" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="L87" s="11" t="s">
+        <v>290</v>
+      </c>
+      <c r="M87" s="11">
+        <v>0</v>
+      </c>
+      <c r="IE87"/>
+    </row>
+    <row r="88" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C88" s="8">
+        <v>20419</v>
+      </c>
+      <c r="D88" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="E88" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="F88" s="8">
+        <v>20420</v>
+      </c>
+      <c r="G88" s="11">
+        <v>0</v>
+      </c>
+      <c r="H88" s="11">
+        <v>0</v>
+      </c>
+      <c r="I88" s="11">
+        <v>1</v>
+      </c>
+      <c r="J88" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K88" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="L88" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="M88" s="11">
+        <v>0</v>
+      </c>
+      <c r="IE88"/>
+    </row>
+    <row r="89" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C89" s="8">
+        <v>20420</v>
+      </c>
+      <c r="D89" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E89" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="F11" s="8">
-        <v>0</v>
-      </c>
-      <c r="G11" s="11">
-        <v>20</v>
-      </c>
-      <c r="H11" s="11">
-        <v>0</v>
-      </c>
-      <c r="I11" s="11">
-        <v>0.3</v>
-      </c>
-      <c r="J11" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="K11" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="L11" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="M11" s="11">
-        <v>0.02</v>
-      </c>
-      <c r="IE11"/>
-    </row>
-    <row r="12" ht="22.5" customHeight="1" spans="3:239">
-      <c r="C12" s="8">
-        <v>20400</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="F12" s="8">
-        <v>20401</v>
-      </c>
-      <c r="G12" s="11">
-        <v>0</v>
-      </c>
-      <c r="H12" s="11">
-        <v>0</v>
-      </c>
-      <c r="I12" s="11">
-        <v>1</v>
-      </c>
-      <c r="J12" s="12">
-        <v>100</v>
-      </c>
-      <c r="K12" s="11"/>
-      <c r="L12" s="11"/>
-      <c r="M12" s="11">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="13" ht="19.5" customHeight="1" spans="3:239">
-      <c r="C13" s="8">
-        <v>20401</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="F13" s="8">
-        <v>0</v>
-      </c>
-      <c r="G13" s="11">
-        <v>20</v>
-      </c>
-      <c r="H13" s="11">
-        <v>0</v>
-      </c>
-      <c r="I13" s="11">
-        <v>0.3</v>
-      </c>
-      <c r="J13" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="K13" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="L13" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="M13" s="11">
-        <v>0.02</v>
-      </c>
-      <c r="IE13"/>
+      <c r="F89" s="8">
+        <v>0</v>
+      </c>
+      <c r="G89" s="11">
+        <v>0</v>
+      </c>
+      <c r="H89" s="11">
+        <v>0</v>
+      </c>
+      <c r="I89" s="11">
+        <v>1</v>
+      </c>
+      <c r="J89" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K89" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="L89" s="11" t="s">
+        <v>292</v>
+      </c>
+      <c r="M89" s="11">
+        <v>0</v>
+      </c>
+      <c r="IE89"/>
+    </row>
+    <row r="90" spans="3:239" ht="22.5" customHeight="1">
+      <c r="C90" s="8">
+        <v>20500</v>
+      </c>
+      <c r="D90" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="E90" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="F90" s="8">
+        <v>20501</v>
+      </c>
+      <c r="G90" s="11">
+        <v>0</v>
+      </c>
+      <c r="H90" s="11">
+        <v>0</v>
+      </c>
+      <c r="I90" s="11">
+        <v>1</v>
+      </c>
+      <c r="J90" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K90" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="L90" s="11"/>
+      <c r="M90" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C91" s="8">
+        <v>20501</v>
+      </c>
+      <c r="D91" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="E91" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="F91" s="8">
+        <v>20502</v>
+      </c>
+      <c r="G91" s="11">
+        <v>0</v>
+      </c>
+      <c r="H91" s="11">
+        <v>0</v>
+      </c>
+      <c r="I91" s="11">
+        <v>1</v>
+      </c>
+      <c r="J91" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K91" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="L91" s="11" t="s">
+        <v>293</v>
+      </c>
+      <c r="M91" s="11">
+        <v>0</v>
+      </c>
+      <c r="IE91"/>
+    </row>
+    <row r="92" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C92" s="8">
+        <v>20502</v>
+      </c>
+      <c r="D92" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="E92" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="F92" s="8">
+        <v>20503</v>
+      </c>
+      <c r="G92" s="11">
+        <v>0</v>
+      </c>
+      <c r="H92" s="11">
+        <v>0</v>
+      </c>
+      <c r="I92" s="11">
+        <v>1</v>
+      </c>
+      <c r="J92" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K92" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="L92" s="11" t="s">
+        <v>294</v>
+      </c>
+      <c r="M92" s="11">
+        <v>0</v>
+      </c>
+      <c r="IE92"/>
+    </row>
+    <row r="93" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C93" s="8">
+        <v>20503</v>
+      </c>
+      <c r="D93" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="E93" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="F93" s="8">
+        <v>20504</v>
+      </c>
+      <c r="G93" s="11">
+        <v>0</v>
+      </c>
+      <c r="H93" s="11">
+        <v>0</v>
+      </c>
+      <c r="I93" s="11">
+        <v>1</v>
+      </c>
+      <c r="J93" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K93" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="L93" s="11" t="s">
+        <v>295</v>
+      </c>
+      <c r="M93" s="11">
+        <v>0</v>
+      </c>
+      <c r="IE93"/>
+    </row>
+    <row r="94" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C94" s="8">
+        <v>20504</v>
+      </c>
+      <c r="D94" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="E94" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="F94" s="8">
+        <v>20505</v>
+      </c>
+      <c r="G94" s="11">
+        <v>0</v>
+      </c>
+      <c r="H94" s="11">
+        <v>0</v>
+      </c>
+      <c r="I94" s="11">
+        <v>1</v>
+      </c>
+      <c r="J94" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K94" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="L94" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="M94" s="11">
+        <v>0</v>
+      </c>
+      <c r="IE94"/>
+    </row>
+    <row r="95" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C95" s="8">
+        <v>20505</v>
+      </c>
+      <c r="D95" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="E95" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="F95" s="8">
+        <v>20506</v>
+      </c>
+      <c r="G95" s="11">
+        <v>0</v>
+      </c>
+      <c r="H95" s="11">
+        <v>0</v>
+      </c>
+      <c r="I95" s="11">
+        <v>1</v>
+      </c>
+      <c r="J95" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K95" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="L95" s="11" t="s">
+        <v>297</v>
+      </c>
+      <c r="M95" s="11">
+        <v>0</v>
+      </c>
+      <c r="IE95"/>
+    </row>
+    <row r="96" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C96" s="8">
+        <v>20506</v>
+      </c>
+      <c r="D96" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="E96" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="F96" s="8">
+        <v>20507</v>
+      </c>
+      <c r="G96" s="11">
+        <v>0</v>
+      </c>
+      <c r="H96" s="11">
+        <v>0</v>
+      </c>
+      <c r="I96" s="11">
+        <v>1</v>
+      </c>
+      <c r="J96" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K96" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="L96" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="M96" s="11">
+        <v>0</v>
+      </c>
+      <c r="IE96"/>
+    </row>
+    <row r="97" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C97" s="8">
+        <v>20507</v>
+      </c>
+      <c r="D97" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="E97" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="F97" s="8">
+        <v>20508</v>
+      </c>
+      <c r="G97" s="11">
+        <v>0</v>
+      </c>
+      <c r="H97" s="11">
+        <v>0</v>
+      </c>
+      <c r="I97" s="11">
+        <v>1</v>
+      </c>
+      <c r="J97" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K97" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="L97" s="11" t="s">
+        <v>299</v>
+      </c>
+      <c r="M97" s="11">
+        <v>0</v>
+      </c>
+      <c r="IE97"/>
+    </row>
+    <row r="98" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C98" s="8">
+        <v>20508</v>
+      </c>
+      <c r="D98" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="E98" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="F98" s="8">
+        <v>20509</v>
+      </c>
+      <c r="G98" s="11">
+        <v>0</v>
+      </c>
+      <c r="H98" s="11">
+        <v>0</v>
+      </c>
+      <c r="I98" s="11">
+        <v>1</v>
+      </c>
+      <c r="J98" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K98" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="L98" s="11" t="s">
+        <v>300</v>
+      </c>
+      <c r="M98" s="11">
+        <v>0</v>
+      </c>
+      <c r="IE98"/>
+    </row>
+    <row r="99" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C99" s="8">
+        <v>20509</v>
+      </c>
+      <c r="D99" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="E99" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="F99" s="8">
+        <v>20510</v>
+      </c>
+      <c r="G99" s="11">
+        <v>0</v>
+      </c>
+      <c r="H99" s="11">
+        <v>0</v>
+      </c>
+      <c r="I99" s="11">
+        <v>1</v>
+      </c>
+      <c r="J99" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K99" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="L99" s="11" t="s">
+        <v>301</v>
+      </c>
+      <c r="M99" s="11">
+        <v>0</v>
+      </c>
+      <c r="IE99"/>
+    </row>
+    <row r="100" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C100" s="8">
+        <v>20510</v>
+      </c>
+      <c r="D100" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="E100" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="F100" s="8">
+        <v>20511</v>
+      </c>
+      <c r="G100" s="11">
+        <v>0</v>
+      </c>
+      <c r="H100" s="11">
+        <v>0</v>
+      </c>
+      <c r="I100" s="11">
+        <v>1</v>
+      </c>
+      <c r="J100" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K100" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="L100" s="11" t="s">
+        <v>302</v>
+      </c>
+      <c r="M100" s="11">
+        <v>0</v>
+      </c>
+      <c r="IE100"/>
+    </row>
+    <row r="101" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C101" s="8">
+        <v>20511</v>
+      </c>
+      <c r="D101" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="E101" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="F101" s="8">
+        <v>20512</v>
+      </c>
+      <c r="G101" s="11">
+        <v>0</v>
+      </c>
+      <c r="H101" s="11">
+        <v>0</v>
+      </c>
+      <c r="I101" s="11">
+        <v>1</v>
+      </c>
+      <c r="J101" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K101" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="L101" s="11" t="s">
+        <v>303</v>
+      </c>
+      <c r="M101" s="11">
+        <v>0</v>
+      </c>
+      <c r="IE101"/>
+    </row>
+    <row r="102" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C102" s="8">
+        <v>20512</v>
+      </c>
+      <c r="D102" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="E102" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="F102" s="8">
+        <v>20513</v>
+      </c>
+      <c r="G102" s="11">
+        <v>0</v>
+      </c>
+      <c r="H102" s="11">
+        <v>0</v>
+      </c>
+      <c r="I102" s="11">
+        <v>1</v>
+      </c>
+      <c r="J102" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K102" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="L102" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="M102" s="11">
+        <v>0</v>
+      </c>
+      <c r="IE102"/>
+    </row>
+    <row r="103" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C103" s="8">
+        <v>20513</v>
+      </c>
+      <c r="D103" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="E103" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="F103" s="8">
+        <v>20514</v>
+      </c>
+      <c r="G103" s="11">
+        <v>0</v>
+      </c>
+      <c r="H103" s="11">
+        <v>0</v>
+      </c>
+      <c r="I103" s="11">
+        <v>1</v>
+      </c>
+      <c r="J103" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K103" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="L103" s="11" t="s">
+        <v>305</v>
+      </c>
+      <c r="M103" s="11">
+        <v>0</v>
+      </c>
+      <c r="IE103"/>
+    </row>
+    <row r="104" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C104" s="8">
+        <v>20514</v>
+      </c>
+      <c r="D104" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="E104" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="F104" s="8">
+        <v>20515</v>
+      </c>
+      <c r="G104" s="11">
+        <v>0</v>
+      </c>
+      <c r="H104" s="11">
+        <v>0</v>
+      </c>
+      <c r="I104" s="11">
+        <v>1</v>
+      </c>
+      <c r="J104" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K104" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="L104" s="11" t="s">
+        <v>306</v>
+      </c>
+      <c r="M104" s="11">
+        <v>0</v>
+      </c>
+      <c r="IE104"/>
+    </row>
+    <row r="105" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C105" s="8">
+        <v>20515</v>
+      </c>
+      <c r="D105" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="E105" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="F105" s="8">
+        <v>20516</v>
+      </c>
+      <c r="G105" s="11">
+        <v>0</v>
+      </c>
+      <c r="H105" s="11">
+        <v>0</v>
+      </c>
+      <c r="I105" s="11">
+        <v>1</v>
+      </c>
+      <c r="J105" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K105" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="L105" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="M105" s="11">
+        <v>0</v>
+      </c>
+      <c r="IE105"/>
+    </row>
+    <row r="106" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C106" s="8">
+        <v>20516</v>
+      </c>
+      <c r="D106" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="E106" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="F106" s="8">
+        <v>20517</v>
+      </c>
+      <c r="G106" s="11">
+        <v>0</v>
+      </c>
+      <c r="H106" s="11">
+        <v>0</v>
+      </c>
+      <c r="I106" s="11">
+        <v>1</v>
+      </c>
+      <c r="J106" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K106" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="L106" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="M106" s="11">
+        <v>0</v>
+      </c>
+      <c r="IE106"/>
+    </row>
+    <row r="107" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C107" s="8">
+        <v>20517</v>
+      </c>
+      <c r="D107" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="E107" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="F107" s="8">
+        <v>20518</v>
+      </c>
+      <c r="G107" s="11">
+        <v>0</v>
+      </c>
+      <c r="H107" s="11">
+        <v>0</v>
+      </c>
+      <c r="I107" s="11">
+        <v>1</v>
+      </c>
+      <c r="J107" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K107" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="L107" s="11" t="s">
+        <v>309</v>
+      </c>
+      <c r="M107" s="11">
+        <v>0</v>
+      </c>
+      <c r="IE107"/>
+    </row>
+    <row r="108" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C108" s="8">
+        <v>20518</v>
+      </c>
+      <c r="D108" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="E108" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="F108" s="8">
+        <v>20519</v>
+      </c>
+      <c r="G108" s="11">
+        <v>0</v>
+      </c>
+      <c r="H108" s="11">
+        <v>0</v>
+      </c>
+      <c r="I108" s="11">
+        <v>1</v>
+      </c>
+      <c r="J108" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K108" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="L108" s="11" t="s">
+        <v>310</v>
+      </c>
+      <c r="M108" s="11">
+        <v>0</v>
+      </c>
+      <c r="IE108"/>
+    </row>
+    <row r="109" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C109" s="8">
+        <v>20519</v>
+      </c>
+      <c r="D109" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="E109" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="F109" s="8">
+        <v>20520</v>
+      </c>
+      <c r="G109" s="11">
+        <v>0</v>
+      </c>
+      <c r="H109" s="11">
+        <v>0</v>
+      </c>
+      <c r="I109" s="11">
+        <v>1</v>
+      </c>
+      <c r="J109" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K109" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="L109" s="11" t="s">
+        <v>311</v>
+      </c>
+      <c r="M109" s="11">
+        <v>0</v>
+      </c>
+      <c r="IE109"/>
+    </row>
+    <row r="110" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C110" s="8">
+        <v>20520</v>
+      </c>
+      <c r="D110" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E110" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F110" s="8">
+        <v>0</v>
+      </c>
+      <c r="G110" s="11">
+        <v>0</v>
+      </c>
+      <c r="H110" s="11">
+        <v>0</v>
+      </c>
+      <c r="I110" s="11">
+        <v>1</v>
+      </c>
+      <c r="J110" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K110" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="L110" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="M110" s="11">
+        <v>0</v>
+      </c>
+      <c r="IE110"/>
     </row>
   </sheetData>
-  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
+  <phoneticPr fontId="8" type="noConversion"/>
+  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Excel/PetTupoConfig.xlsx
+++ b/Excel/PetTupoConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{164642F1-3596-4379-AB8F-49C501B74E69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{954CEB9F-C26B-4031-9666-F9F289F06D64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PetTupoProto" sheetId="1" r:id="rId1"/>
@@ -435,9 +435,6 @@
     <t>1;4000000@10000168;40</t>
   </si>
   <si>
-    <t>1;5000000@10000168;50@10000169;3</t>
-  </si>
-  <si>
     <t>1;6000000@10000168;60</t>
   </si>
   <si>
@@ -450,9 +447,6 @@
     <t>1;9000000@10000168;90</t>
   </si>
   <si>
-    <t>1;10000000@10000168;100@10000169;5</t>
-  </si>
-  <si>
     <t>1;12000000@10000168;120</t>
   </si>
   <si>
@@ -465,9 +459,6 @@
     <t>1;18000000@10000168;180</t>
   </si>
   <si>
-    <t>1;20000000@10000168;200@10000169;10</t>
-  </si>
-  <si>
     <t>1;22000000@10000168;220</t>
   </si>
   <si>
@@ -480,9 +471,6 @@
     <t>1;28000000@10000168;280</t>
   </si>
   <si>
-    <t>1;30000000@10000168;300@10000169;20</t>
-  </si>
-  <si>
     <t>生命修炼1级</t>
   </si>
   <si>
@@ -1123,6 +1111,22 @@
   </si>
   <si>
     <t>130403;36000@231403;0.1@230703;0.2</t>
+  </si>
+  <si>
+    <t>1;5000000@10000168;50@10000169;10</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>1;10000000@10000168;100@10000169;20</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>1;20000000@10000168;200@10000169;30</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>1;30000000@10000168;300@10000169;40</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2700,7 +2704,7 @@
         <v>80</v>
       </c>
       <c r="L7" s="11" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="M7" s="11">
         <v>0</v>
@@ -2735,7 +2739,7 @@
         <v>81</v>
       </c>
       <c r="L8" s="11" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="M8" s="11">
         <v>0</v>
@@ -2770,7 +2774,7 @@
         <v>82</v>
       </c>
       <c r="L9" s="11" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="M9" s="11">
         <v>0</v>
@@ -2802,10 +2806,10 @@
         <v>78</v>
       </c>
       <c r="K10" s="11" t="s">
-        <v>83</v>
+        <v>309</v>
       </c>
       <c r="L10" s="11" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="M10" s="11">
         <v>0</v>
@@ -2837,10 +2841,10 @@
         <v>78</v>
       </c>
       <c r="K11" s="11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L11" s="11" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="M11" s="11">
         <v>0</v>
@@ -2872,10 +2876,10 @@
         <v>78</v>
       </c>
       <c r="K12" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="L12" s="11" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="M12" s="11">
         <v>0</v>
@@ -2907,10 +2911,10 @@
         <v>78</v>
       </c>
       <c r="K13" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L13" s="11" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="M13" s="11">
         <v>0</v>
@@ -2942,10 +2946,10 @@
         <v>78</v>
       </c>
       <c r="K14" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L14" s="11" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="M14" s="11">
         <v>0</v>
@@ -2977,10 +2981,10 @@
         <v>78</v>
       </c>
       <c r="K15" s="11" t="s">
-        <v>88</v>
+        <v>310</v>
       </c>
       <c r="L15" s="11" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="M15" s="11">
         <v>0</v>
@@ -3012,10 +3016,10 @@
         <v>78</v>
       </c>
       <c r="K16" s="11" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="L16" s="11" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="M16" s="11">
         <v>0</v>
@@ -3047,10 +3051,10 @@
         <v>78</v>
       </c>
       <c r="K17" s="11" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L17" s="11" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="M17" s="11">
         <v>0</v>
@@ -3082,10 +3086,10 @@
         <v>78</v>
       </c>
       <c r="K18" s="11" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="L18" s="11" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="M18" s="11">
         <v>0</v>
@@ -3117,10 +3121,10 @@
         <v>78</v>
       </c>
       <c r="K19" s="11" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="L19" s="11" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="M19" s="11">
         <v>0</v>
@@ -3152,10 +3156,10 @@
         <v>78</v>
       </c>
       <c r="K20" s="11" t="s">
-        <v>93</v>
+        <v>311</v>
       </c>
       <c r="L20" s="11" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="M20" s="11">
         <v>0</v>
@@ -3187,10 +3191,10 @@
         <v>78</v>
       </c>
       <c r="K21" s="11" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="L21" s="11" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="M21" s="11">
         <v>0</v>
@@ -3222,10 +3226,10 @@
         <v>78</v>
       </c>
       <c r="K22" s="11" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="L22" s="11" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="M22" s="11">
         <v>0</v>
@@ -3257,10 +3261,10 @@
         <v>78</v>
       </c>
       <c r="K23" s="11" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="L23" s="11" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="M23" s="11">
         <v>0</v>
@@ -3292,10 +3296,10 @@
         <v>78</v>
       </c>
       <c r="K24" s="11" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="L24" s="11" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="M24" s="11">
         <v>0</v>
@@ -3327,10 +3331,10 @@
         <v>78</v>
       </c>
       <c r="K25" s="11" t="s">
-        <v>98</v>
+        <v>312</v>
       </c>
       <c r="L25" s="11" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="M25" s="11">
         <v>0</v>
@@ -3362,10 +3366,10 @@
         <v>78</v>
       </c>
       <c r="K26" s="11" t="s">
-        <v>98</v>
+        <v>312</v>
       </c>
       <c r="L26" s="11" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="M26" s="11">
         <v>0</v>
@@ -3409,10 +3413,10 @@
         <v>20201</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F28" s="8">
         <v>20202</v>
@@ -3433,7 +3437,7 @@
         <v>80</v>
       </c>
       <c r="L28" s="11" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="M28" s="11">
         <v>0</v>
@@ -3444,10 +3448,10 @@
         <v>20202</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="F29" s="8">
         <v>20203</v>
@@ -3468,7 +3472,7 @@
         <v>81</v>
       </c>
       <c r="L29" s="11" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="M29" s="11">
         <v>0</v>
@@ -3479,10 +3483,10 @@
         <v>20203</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F30" s="8">
         <v>20204</v>
@@ -3503,7 +3507,7 @@
         <v>82</v>
       </c>
       <c r="L30" s="11" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="M30" s="11">
         <v>0</v>
@@ -3514,10 +3518,10 @@
         <v>20204</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="F31" s="8">
         <v>20205</v>
@@ -3535,10 +3539,10 @@
         <v>78</v>
       </c>
       <c r="K31" s="11" t="s">
-        <v>83</v>
+        <v>309</v>
       </c>
       <c r="L31" s="11" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="M31" s="11">
         <v>0</v>
@@ -3549,10 +3553,10 @@
         <v>20205</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="F32" s="8">
         <v>20206</v>
@@ -3570,10 +3574,10 @@
         <v>78</v>
       </c>
       <c r="K32" s="11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L32" s="11" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="M32" s="11">
         <v>0</v>
@@ -3584,10 +3588,10 @@
         <v>20206</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="F33" s="8">
         <v>20207</v>
@@ -3605,10 +3609,10 @@
         <v>78</v>
       </c>
       <c r="K33" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="L33" s="11" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="M33" s="11">
         <v>0</v>
@@ -3619,10 +3623,10 @@
         <v>20207</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="F34" s="8">
         <v>20208</v>
@@ -3640,10 +3644,10 @@
         <v>78</v>
       </c>
       <c r="K34" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L34" s="11" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="M34" s="11">
         <v>0</v>
@@ -3654,10 +3658,10 @@
         <v>20208</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F35" s="8">
         <v>20209</v>
@@ -3675,10 +3679,10 @@
         <v>78</v>
       </c>
       <c r="K35" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L35" s="11" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="M35" s="11">
         <v>0</v>
@@ -3689,10 +3693,10 @@
         <v>20209</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="F36" s="8">
         <v>20210</v>
@@ -3710,10 +3714,10 @@
         <v>78</v>
       </c>
       <c r="K36" s="11" t="s">
-        <v>88</v>
+        <v>310</v>
       </c>
       <c r="L36" s="11" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="M36" s="11">
         <v>0</v>
@@ -3724,10 +3728,10 @@
         <v>20210</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F37" s="8">
         <v>20211</v>
@@ -3745,10 +3749,10 @@
         <v>78</v>
       </c>
       <c r="K37" s="11" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="L37" s="11" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="M37" s="11">
         <v>0</v>
@@ -3759,10 +3763,10 @@
         <v>20211</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E38" s="10" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F38" s="8">
         <v>20212</v>
@@ -3780,10 +3784,10 @@
         <v>78</v>
       </c>
       <c r="K38" s="11" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L38" s="11" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="M38" s="11">
         <v>0</v>
@@ -3794,10 +3798,10 @@
         <v>20212</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="F39" s="8">
         <v>20213</v>
@@ -3815,10 +3819,10 @@
         <v>78</v>
       </c>
       <c r="K39" s="11" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="L39" s="11" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="M39" s="11">
         <v>0</v>
@@ -3829,10 +3833,10 @@
         <v>20213</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="F40" s="8">
         <v>20214</v>
@@ -3850,10 +3854,10 @@
         <v>78</v>
       </c>
       <c r="K40" s="11" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="L40" s="11" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="M40" s="11">
         <v>0</v>
@@ -3864,10 +3868,10 @@
         <v>20214</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F41" s="8">
         <v>20215</v>
@@ -3885,10 +3889,10 @@
         <v>78</v>
       </c>
       <c r="K41" s="11" t="s">
-        <v>93</v>
+        <v>311</v>
       </c>
       <c r="L41" s="11" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="M41" s="11">
         <v>0</v>
@@ -3899,10 +3903,10 @@
         <v>20215</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="F42" s="8">
         <v>20216</v>
@@ -3920,10 +3924,10 @@
         <v>78</v>
       </c>
       <c r="K42" s="11" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="L42" s="11" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="M42" s="11">
         <v>0</v>
@@ -3934,10 +3938,10 @@
         <v>20216</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F43" s="8">
         <v>20217</v>
@@ -3955,10 +3959,10 @@
         <v>78</v>
       </c>
       <c r="K43" s="11" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="L43" s="11" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="M43" s="11">
         <v>0</v>
@@ -3969,10 +3973,10 @@
         <v>20217</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E44" s="10" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F44" s="8">
         <v>20218</v>
@@ -3990,10 +3994,10 @@
         <v>78</v>
       </c>
       <c r="K44" s="11" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="L44" s="11" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="M44" s="11">
         <v>0</v>
@@ -4004,10 +4008,10 @@
         <v>20218</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="F45" s="8">
         <v>20219</v>
@@ -4025,10 +4029,10 @@
         <v>78</v>
       </c>
       <c r="K45" s="11" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="L45" s="11" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="M45" s="11">
         <v>0</v>
@@ -4039,10 +4043,10 @@
         <v>20219</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E46" s="10" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="F46" s="8">
         <v>20220</v>
@@ -4060,10 +4064,10 @@
         <v>78</v>
       </c>
       <c r="K46" s="11" t="s">
-        <v>98</v>
+        <v>312</v>
       </c>
       <c r="L46" s="11" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="M46" s="11">
         <v>0</v>
@@ -4095,10 +4099,10 @@
         <v>78</v>
       </c>
       <c r="K47" s="11" t="s">
-        <v>98</v>
+        <v>312</v>
       </c>
       <c r="L47" s="11" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="M47" s="11">
         <v>0</v>
@@ -4142,10 +4146,10 @@
         <v>20301</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="F49" s="8">
         <v>20302</v>
@@ -4166,7 +4170,7 @@
         <v>80</v>
       </c>
       <c r="L49" s="11" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="M49" s="11">
         <v>0</v>
@@ -4178,10 +4182,10 @@
         <v>20302</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E50" s="10" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="F50" s="8">
         <v>20303</v>
@@ -4202,7 +4206,7 @@
         <v>81</v>
       </c>
       <c r="L50" s="11" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="M50" s="11">
         <v>0</v>
@@ -4214,10 +4218,10 @@
         <v>20303</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="F51" s="8">
         <v>20304</v>
@@ -4238,7 +4242,7 @@
         <v>82</v>
       </c>
       <c r="L51" s="11" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="M51" s="11">
         <v>0</v>
@@ -4250,10 +4254,10 @@
         <v>20304</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E52" s="10" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F52" s="8">
         <v>20305</v>
@@ -4271,10 +4275,10 @@
         <v>78</v>
       </c>
       <c r="K52" s="11" t="s">
-        <v>83</v>
+        <v>309</v>
       </c>
       <c r="L52" s="11" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="M52" s="11">
         <v>0</v>
@@ -4286,10 +4290,10 @@
         <v>20305</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="F53" s="8">
         <v>20306</v>
@@ -4307,10 +4311,10 @@
         <v>78</v>
       </c>
       <c r="K53" s="11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L53" s="11" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="M53" s="11">
         <v>0</v>
@@ -4322,10 +4326,10 @@
         <v>20306</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="E54" s="10" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F54" s="8">
         <v>20307</v>
@@ -4343,10 +4347,10 @@
         <v>78</v>
       </c>
       <c r="K54" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="L54" s="11" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="M54" s="11">
         <v>0</v>
@@ -4358,10 +4362,10 @@
         <v>20307</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F55" s="8">
         <v>20308</v>
@@ -4379,10 +4383,10 @@
         <v>78</v>
       </c>
       <c r="K55" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L55" s="11" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="M55" s="11">
         <v>0</v>
@@ -4394,10 +4398,10 @@
         <v>20308</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E56" s="10" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="F56" s="8">
         <v>20309</v>
@@ -4415,10 +4419,10 @@
         <v>78</v>
       </c>
       <c r="K56" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L56" s="11" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="M56" s="11">
         <v>0</v>
@@ -4430,10 +4434,10 @@
         <v>20309</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="F57" s="8">
         <v>20310</v>
@@ -4451,10 +4455,10 @@
         <v>78</v>
       </c>
       <c r="K57" s="11" t="s">
-        <v>88</v>
+        <v>310</v>
       </c>
       <c r="L57" s="11" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="M57" s="11">
         <v>0</v>
@@ -4466,10 +4470,10 @@
         <v>20310</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="E58" s="10" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="F58" s="8">
         <v>20311</v>
@@ -4487,10 +4491,10 @@
         <v>78</v>
       </c>
       <c r="K58" s="11" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="L58" s="11" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="M58" s="11">
         <v>0</v>
@@ -4502,10 +4506,10 @@
         <v>20311</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="F59" s="8">
         <v>20312</v>
@@ -4523,10 +4527,10 @@
         <v>78</v>
       </c>
       <c r="K59" s="11" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L59" s="11" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="M59" s="11">
         <v>0</v>
@@ -4538,10 +4542,10 @@
         <v>20312</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="E60" s="10" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="F60" s="8">
         <v>20313</v>
@@ -4559,10 +4563,10 @@
         <v>78</v>
       </c>
       <c r="K60" s="11" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="L60" s="11" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="M60" s="11">
         <v>0</v>
@@ -4574,10 +4578,10 @@
         <v>20313</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="F61" s="8">
         <v>20314</v>
@@ -4595,10 +4599,10 @@
         <v>78</v>
       </c>
       <c r="K61" s="11" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="L61" s="11" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="M61" s="11">
         <v>0</v>
@@ -4610,10 +4614,10 @@
         <v>20314</v>
       </c>
       <c r="D62" s="9" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="E62" s="10" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="F62" s="8">
         <v>20315</v>
@@ -4631,10 +4635,10 @@
         <v>78</v>
       </c>
       <c r="K62" s="11" t="s">
-        <v>93</v>
+        <v>311</v>
       </c>
       <c r="L62" s="11" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="M62" s="11">
         <v>0</v>
@@ -4646,10 +4650,10 @@
         <v>20315</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="F63" s="8">
         <v>20316</v>
@@ -4667,10 +4671,10 @@
         <v>78</v>
       </c>
       <c r="K63" s="11" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="L63" s="11" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="M63" s="11">
         <v>0</v>
@@ -4682,10 +4686,10 @@
         <v>20316</v>
       </c>
       <c r="D64" s="9" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E64" s="10" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="F64" s="8">
         <v>20317</v>
@@ -4703,10 +4707,10 @@
         <v>78</v>
       </c>
       <c r="K64" s="11" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="L64" s="11" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="M64" s="11">
         <v>0</v>
@@ -4718,10 +4722,10 @@
         <v>20317</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="F65" s="8">
         <v>20318</v>
@@ -4739,10 +4743,10 @@
         <v>78</v>
       </c>
       <c r="K65" s="11" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="L65" s="11" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="M65" s="11">
         <v>0</v>
@@ -4754,10 +4758,10 @@
         <v>20318</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="E66" s="10" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F66" s="8">
         <v>20319</v>
@@ -4775,10 +4779,10 @@
         <v>78</v>
       </c>
       <c r="K66" s="11" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="L66" s="11" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="M66" s="11">
         <v>0</v>
@@ -4790,10 +4794,10 @@
         <v>20319</v>
       </c>
       <c r="D67" s="9" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="F67" s="8">
         <v>20320</v>
@@ -4811,10 +4815,10 @@
         <v>78</v>
       </c>
       <c r="K67" s="11" t="s">
-        <v>98</v>
+        <v>312</v>
       </c>
       <c r="L67" s="11" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="M67" s="11">
         <v>0</v>
@@ -4847,10 +4851,10 @@
         <v>78</v>
       </c>
       <c r="K68" s="11" t="s">
-        <v>98</v>
+        <v>312</v>
       </c>
       <c r="L68" s="11" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="M68" s="11">
         <v>0</v>
@@ -4895,10 +4899,10 @@
         <v>20401</v>
       </c>
       <c r="D70" s="9" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="E70" s="10" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="F70" s="8">
         <v>20402</v>
@@ -4919,7 +4923,7 @@
         <v>80</v>
       </c>
       <c r="L70" s="11" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="M70" s="11">
         <v>0</v>
@@ -4931,10 +4935,10 @@
         <v>20402</v>
       </c>
       <c r="D71" s="9" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="F71" s="8">
         <v>20403</v>
@@ -4955,7 +4959,7 @@
         <v>81</v>
       </c>
       <c r="L71" s="11" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="M71" s="11">
         <v>0</v>
@@ -4967,10 +4971,10 @@
         <v>20403</v>
       </c>
       <c r="D72" s="9" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="E72" s="10" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="F72" s="8">
         <v>20404</v>
@@ -4991,7 +4995,7 @@
         <v>82</v>
       </c>
       <c r="L72" s="11" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="M72" s="11">
         <v>0</v>
@@ -5003,10 +5007,10 @@
         <v>20404</v>
       </c>
       <c r="D73" s="9" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="F73" s="8">
         <v>20405</v>
@@ -5024,10 +5028,10 @@
         <v>78</v>
       </c>
       <c r="K73" s="11" t="s">
-        <v>83</v>
+        <v>309</v>
       </c>
       <c r="L73" s="11" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="M73" s="11">
         <v>0</v>
@@ -5039,10 +5043,10 @@
         <v>20405</v>
       </c>
       <c r="D74" s="9" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="E74" s="10" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F74" s="8">
         <v>20406</v>
@@ -5060,10 +5064,10 @@
         <v>78</v>
       </c>
       <c r="K74" s="11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L74" s="11" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="M74" s="11">
         <v>0</v>
@@ -5075,10 +5079,10 @@
         <v>20406</v>
       </c>
       <c r="D75" s="9" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F75" s="8">
         <v>20407</v>
@@ -5096,10 +5100,10 @@
         <v>78</v>
       </c>
       <c r="K75" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="L75" s="11" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="M75" s="11">
         <v>0</v>
@@ -5111,10 +5115,10 @@
         <v>20407</v>
       </c>
       <c r="D76" s="9" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="E76" s="10" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F76" s="8">
         <v>20408</v>
@@ -5132,10 +5136,10 @@
         <v>78</v>
       </c>
       <c r="K76" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L76" s="11" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="M76" s="11">
         <v>0</v>
@@ -5147,10 +5151,10 @@
         <v>20408</v>
       </c>
       <c r="D77" s="9" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F77" s="8">
         <v>20409</v>
@@ -5168,10 +5172,10 @@
         <v>78</v>
       </c>
       <c r="K77" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L77" s="11" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="M77" s="11">
         <v>0</v>
@@ -5183,10 +5187,10 @@
         <v>20409</v>
       </c>
       <c r="D78" s="9" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="E78" s="10" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="F78" s="8">
         <v>20410</v>
@@ -5204,10 +5208,10 @@
         <v>78</v>
       </c>
       <c r="K78" s="11" t="s">
-        <v>88</v>
+        <v>310</v>
       </c>
       <c r="L78" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="M78" s="11">
         <v>0</v>
@@ -5219,10 +5223,10 @@
         <v>20410</v>
       </c>
       <c r="D79" s="9" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="F79" s="8">
         <v>20411</v>
@@ -5240,10 +5244,10 @@
         <v>78</v>
       </c>
       <c r="K79" s="11" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="L79" s="11" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="M79" s="11">
         <v>0</v>
@@ -5255,10 +5259,10 @@
         <v>20411</v>
       </c>
       <c r="D80" s="9" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="E80" s="10" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="F80" s="8">
         <v>20412</v>
@@ -5276,10 +5280,10 @@
         <v>78</v>
       </c>
       <c r="K80" s="11" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L80" s="11" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="M80" s="11">
         <v>0</v>
@@ -5291,10 +5295,10 @@
         <v>20412</v>
       </c>
       <c r="D81" s="9" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="F81" s="8">
         <v>20413</v>
@@ -5312,10 +5316,10 @@
         <v>78</v>
       </c>
       <c r="K81" s="11" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="L81" s="11" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="M81" s="11">
         <v>0</v>
@@ -5327,10 +5331,10 @@
         <v>20413</v>
       </c>
       <c r="D82" s="9" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E82" s="10" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="F82" s="8">
         <v>20414</v>
@@ -5348,10 +5352,10 @@
         <v>78</v>
       </c>
       <c r="K82" s="11" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="L82" s="11" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="M82" s="11">
         <v>0</v>
@@ -5363,10 +5367,10 @@
         <v>20414</v>
       </c>
       <c r="D83" s="9" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="F83" s="8">
         <v>20415</v>
@@ -5384,10 +5388,10 @@
         <v>78</v>
       </c>
       <c r="K83" s="11" t="s">
-        <v>93</v>
+        <v>311</v>
       </c>
       <c r="L83" s="11" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="M83" s="11">
         <v>0</v>
@@ -5399,10 +5403,10 @@
         <v>20415</v>
       </c>
       <c r="D84" s="9" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="E84" s="10" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="F84" s="8">
         <v>20416</v>
@@ -5420,10 +5424,10 @@
         <v>78</v>
       </c>
       <c r="K84" s="11" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="L84" s="11" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="M84" s="11">
         <v>0</v>
@@ -5435,10 +5439,10 @@
         <v>20416</v>
       </c>
       <c r="D85" s="9" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="F85" s="8">
         <v>20417</v>
@@ -5456,10 +5460,10 @@
         <v>78</v>
       </c>
       <c r="K85" s="11" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="L85" s="11" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="M85" s="11">
         <v>0</v>
@@ -5471,10 +5475,10 @@
         <v>20417</v>
       </c>
       <c r="D86" s="9" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="E86" s="10" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="F86" s="8">
         <v>20418</v>
@@ -5492,10 +5496,10 @@
         <v>78</v>
       </c>
       <c r="K86" s="11" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="L86" s="11" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="M86" s="11">
         <v>0</v>
@@ -5507,10 +5511,10 @@
         <v>20418</v>
       </c>
       <c r="D87" s="9" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="F87" s="8">
         <v>20419</v>
@@ -5528,10 +5532,10 @@
         <v>78</v>
       </c>
       <c r="K87" s="11" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="L87" s="11" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="M87" s="11">
         <v>0</v>
@@ -5543,10 +5547,10 @@
         <v>20419</v>
       </c>
       <c r="D88" s="9" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E88" s="10" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="F88" s="8">
         <v>20420</v>
@@ -5564,10 +5568,10 @@
         <v>78</v>
       </c>
       <c r="K88" s="11" t="s">
-        <v>98</v>
+        <v>312</v>
       </c>
       <c r="L88" s="11" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="M88" s="11">
         <v>0</v>
@@ -5600,10 +5604,10 @@
         <v>78</v>
       </c>
       <c r="K89" s="11" t="s">
-        <v>98</v>
+        <v>312</v>
       </c>
       <c r="L89" s="11" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="M89" s="11">
         <v>0</v>
@@ -5648,10 +5652,10 @@
         <v>20501</v>
       </c>
       <c r="D91" s="9" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="F91" s="8">
         <v>20502</v>
@@ -5672,7 +5676,7 @@
         <v>80</v>
       </c>
       <c r="L91" s="11" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="M91" s="11">
         <v>0</v>
@@ -5684,10 +5688,10 @@
         <v>20502</v>
       </c>
       <c r="D92" s="9" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="E92" s="10" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="F92" s="8">
         <v>20503</v>
@@ -5708,7 +5712,7 @@
         <v>81</v>
       </c>
       <c r="L92" s="11" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="M92" s="11">
         <v>0</v>
@@ -5720,10 +5724,10 @@
         <v>20503</v>
       </c>
       <c r="D93" s="9" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="F93" s="8">
         <v>20504</v>
@@ -5744,7 +5748,7 @@
         <v>82</v>
       </c>
       <c r="L93" s="11" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="M93" s="11">
         <v>0</v>
@@ -5756,10 +5760,10 @@
         <v>20504</v>
       </c>
       <c r="D94" s="9" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E94" s="10" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="F94" s="8">
         <v>20505</v>
@@ -5777,10 +5781,10 @@
         <v>78</v>
       </c>
       <c r="K94" s="11" t="s">
-        <v>83</v>
+        <v>309</v>
       </c>
       <c r="L94" s="11" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="M94" s="11">
         <v>0</v>
@@ -5792,10 +5796,10 @@
         <v>20505</v>
       </c>
       <c r="D95" s="9" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F95" s="8">
         <v>20506</v>
@@ -5813,10 +5817,10 @@
         <v>78</v>
       </c>
       <c r="K95" s="11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L95" s="11" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="M95" s="11">
         <v>0</v>
@@ -5828,10 +5832,10 @@
         <v>20506</v>
       </c>
       <c r="D96" s="9" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E96" s="10" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F96" s="8">
         <v>20507</v>
@@ -5849,10 +5853,10 @@
         <v>78</v>
       </c>
       <c r="K96" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="L96" s="11" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="M96" s="11">
         <v>0</v>
@@ -5864,10 +5868,10 @@
         <v>20507</v>
       </c>
       <c r="D97" s="9" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F97" s="8">
         <v>20508</v>
@@ -5885,10 +5889,10 @@
         <v>78</v>
       </c>
       <c r="K97" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L97" s="11" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="M97" s="11">
         <v>0</v>
@@ -5900,10 +5904,10 @@
         <v>20508</v>
       </c>
       <c r="D98" s="9" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="E98" s="10" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F98" s="8">
         <v>20509</v>
@@ -5921,10 +5925,10 @@
         <v>78</v>
       </c>
       <c r="K98" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L98" s="11" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="M98" s="11">
         <v>0</v>
@@ -5936,10 +5940,10 @@
         <v>20509</v>
       </c>
       <c r="D99" s="9" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="F99" s="8">
         <v>20510</v>
@@ -5957,10 +5961,10 @@
         <v>78</v>
       </c>
       <c r="K99" s="11" t="s">
-        <v>88</v>
+        <v>310</v>
       </c>
       <c r="L99" s="11" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="M99" s="11">
         <v>0</v>
@@ -5972,10 +5976,10 @@
         <v>20510</v>
       </c>
       <c r="D100" s="9" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="E100" s="10" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="F100" s="8">
         <v>20511</v>
@@ -5993,10 +5997,10 @@
         <v>78</v>
       </c>
       <c r="K100" s="11" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="L100" s="11" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="M100" s="11">
         <v>0</v>
@@ -6008,10 +6012,10 @@
         <v>20511</v>
       </c>
       <c r="D101" s="9" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="F101" s="8">
         <v>20512</v>
@@ -6029,10 +6033,10 @@
         <v>78</v>
       </c>
       <c r="K101" s="11" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L101" s="11" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="M101" s="11">
         <v>0</v>
@@ -6044,10 +6048,10 @@
         <v>20512</v>
       </c>
       <c r="D102" s="9" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="E102" s="10" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="F102" s="8">
         <v>20513</v>
@@ -6065,10 +6069,10 @@
         <v>78</v>
       </c>
       <c r="K102" s="11" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="L102" s="11" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="M102" s="11">
         <v>0</v>
@@ -6080,10 +6084,10 @@
         <v>20513</v>
       </c>
       <c r="D103" s="9" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="F103" s="8">
         <v>20514</v>
@@ -6101,10 +6105,10 @@
         <v>78</v>
       </c>
       <c r="K103" s="11" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="L103" s="11" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="M103" s="11">
         <v>0</v>
@@ -6116,10 +6120,10 @@
         <v>20514</v>
       </c>
       <c r="D104" s="9" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="E104" s="10" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="F104" s="8">
         <v>20515</v>
@@ -6137,10 +6141,10 @@
         <v>78</v>
       </c>
       <c r="K104" s="11" t="s">
-        <v>93</v>
+        <v>311</v>
       </c>
       <c r="L104" s="11" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="M104" s="11">
         <v>0</v>
@@ -6152,10 +6156,10 @@
         <v>20515</v>
       </c>
       <c r="D105" s="9" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="F105" s="8">
         <v>20516</v>
@@ -6173,10 +6177,10 @@
         <v>78</v>
       </c>
       <c r="K105" s="11" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="L105" s="11" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="M105" s="11">
         <v>0</v>
@@ -6188,10 +6192,10 @@
         <v>20516</v>
       </c>
       <c r="D106" s="9" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="E106" s="10" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="F106" s="8">
         <v>20517</v>
@@ -6209,10 +6213,10 @@
         <v>78</v>
       </c>
       <c r="K106" s="11" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="L106" s="11" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="M106" s="11">
         <v>0</v>
@@ -6224,10 +6228,10 @@
         <v>20517</v>
       </c>
       <c r="D107" s="9" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="F107" s="8">
         <v>20518</v>
@@ -6245,10 +6249,10 @@
         <v>78</v>
       </c>
       <c r="K107" s="11" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="L107" s="11" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="M107" s="11">
         <v>0</v>
@@ -6260,10 +6264,10 @@
         <v>20518</v>
       </c>
       <c r="D108" s="9" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E108" s="10" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="F108" s="8">
         <v>20519</v>
@@ -6281,10 +6285,10 @@
         <v>78</v>
       </c>
       <c r="K108" s="11" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="L108" s="11" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="M108" s="11">
         <v>0</v>
@@ -6296,10 +6300,10 @@
         <v>20519</v>
       </c>
       <c r="D109" s="9" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="F109" s="8">
         <v>20520</v>
@@ -6317,10 +6321,10 @@
         <v>78</v>
       </c>
       <c r="K109" s="11" t="s">
-        <v>98</v>
+        <v>312</v>
       </c>
       <c r="L109" s="11" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="M109" s="11">
         <v>0</v>
@@ -6353,10 +6357,10 @@
         <v>78</v>
       </c>
       <c r="K110" s="11" t="s">
-        <v>98</v>
+        <v>312</v>
       </c>
       <c r="L110" s="11" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="M110" s="11">
         <v>0</v>

--- a/Excel/PetTupoConfig.xlsx
+++ b/Excel/PetTupoConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{954CEB9F-C26B-4031-9666-F9F289F06D64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5897F54-E485-457B-BA7D-AA387A8C608A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -183,7 +183,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="333">
   <si>
     <t>c</t>
   </si>
@@ -206,9 +206,6 @@
     <t>成功概率</t>
   </si>
   <si>
-    <t>消耗家族贡献</t>
-  </si>
-  <si>
     <t>消耗道具</t>
   </si>
   <si>
@@ -257,876 +254,937 @@
     <t>double</t>
   </si>
   <si>
-    <t>攻击修炼0级</t>
-  </si>
-  <si>
     <t>Attack Training Level 0</t>
   </si>
   <si>
-    <t>攻击修炼20级</t>
-  </si>
-  <si>
     <t>Attack Training Level 20</t>
   </si>
   <si>
-    <t>生命修炼0级</t>
-  </si>
-  <si>
     <t>Life Training Level 0</t>
   </si>
   <si>
-    <t>生命修炼20级</t>
-  </si>
-  <si>
     <t>Life Training Level 20</t>
   </si>
   <si>
-    <t>防御修炼0级</t>
-  </si>
-  <si>
     <t>Defense Training Level 0</t>
   </si>
   <si>
-    <t>防御修炼20级</t>
-  </si>
-  <si>
     <t>Defense Training Level 20</t>
   </si>
   <si>
-    <t>法防修炼0级</t>
-  </si>
-  <si>
     <t>Magic Defense Training Level 0</t>
   </si>
   <si>
-    <t>法防修炼20级</t>
-  </si>
-  <si>
     <t>Magic Defense Training Level 20</t>
   </si>
   <si>
-    <t>攻击修炼1级</t>
-  </si>
-  <si>
     <t>Attack Training Level 1</t>
   </si>
   <si>
-    <t>攻击修炼2级</t>
-  </si>
-  <si>
     <t>Attack Training Level 2</t>
   </si>
   <si>
-    <t>攻击修炼3级</t>
-  </si>
-  <si>
     <t>Attack Training Level 3</t>
   </si>
   <si>
-    <t>攻击修炼4级</t>
-  </si>
-  <si>
     <t>Attack Training Level 4</t>
   </si>
   <si>
-    <t>攻击修炼5级</t>
-  </si>
-  <si>
     <t>Attack Training Level 5</t>
   </si>
   <si>
-    <t>攻击修炼6级</t>
-  </si>
-  <si>
     <t>Attack Training Level 6</t>
   </si>
   <si>
-    <t>攻击修炼7级</t>
-  </si>
-  <si>
     <t>Attack Training Level 7</t>
   </si>
   <si>
-    <t>攻击修炼8级</t>
-  </si>
-  <si>
     <t>Attack Training Level 8</t>
   </si>
   <si>
-    <t>攻击修炼9级</t>
-  </si>
-  <si>
     <t>Attack Training Level 9</t>
   </si>
   <si>
-    <t>攻击修炼10级</t>
-  </si>
-  <si>
     <t>Attack Training Level 10</t>
   </si>
   <si>
-    <t>攻击修炼11级</t>
-  </si>
-  <si>
     <t>Attack Training Level 11</t>
   </si>
   <si>
-    <t>攻击修炼12级</t>
-  </si>
-  <si>
     <t>Attack Training Level 12</t>
   </si>
   <si>
-    <t>攻击修炼13级</t>
-  </si>
-  <si>
     <t>Attack Training Level 13</t>
   </si>
   <si>
-    <t>攻击修炼14级</t>
-  </si>
-  <si>
     <t>Attack Training Level 14</t>
   </si>
   <si>
-    <t>攻击修炼15级</t>
-  </si>
-  <si>
     <t>Attack Training Level 15</t>
   </si>
   <si>
-    <t>攻击修炼16级</t>
-  </si>
-  <si>
     <t>Attack Training Level 16</t>
   </si>
   <si>
-    <t>攻击修炼17级</t>
-  </si>
-  <si>
     <t>Attack Training Level 17</t>
   </si>
   <si>
-    <t>攻击修炼18级</t>
-  </si>
-  <si>
     <t>Attack Training Level 18</t>
   </si>
   <si>
-    <t>攻击修炼19级</t>
-  </si>
-  <si>
     <t>Attack Training Level 19</t>
   </si>
   <si>
-    <t>0</t>
+    <t>Life Training Level 1</t>
+  </si>
+  <si>
+    <t>Life Training Level 2</t>
+  </si>
+  <si>
+    <t>Life Training Level 3</t>
+  </si>
+  <si>
+    <t>Life Training Level 4</t>
+  </si>
+  <si>
+    <t>Life Training Level 5</t>
+  </si>
+  <si>
+    <t>Life Training Level 6</t>
+  </si>
+  <si>
+    <t>Life Training Level 7</t>
+  </si>
+  <si>
+    <t>Life Training Level 8</t>
+  </si>
+  <si>
+    <t>Life Training Level 9</t>
+  </si>
+  <si>
+    <t>Life Training Level 10</t>
+  </si>
+  <si>
+    <t>Life Training Level 11</t>
+  </si>
+  <si>
+    <t>Life Training Level 12</t>
+  </si>
+  <si>
+    <t>Life Training Level 13</t>
+  </si>
+  <si>
+    <t>Life Training Level 14</t>
+  </si>
+  <si>
+    <t>Life Training Level 15</t>
+  </si>
+  <si>
+    <t>Life Training Level 16</t>
+  </si>
+  <si>
+    <t>Life Training Level 17</t>
+  </si>
+  <si>
+    <t>Life Training Level 18</t>
+  </si>
+  <si>
+    <t>Life Training Level 19</t>
+  </si>
+  <si>
+    <t>Defense Training Level 1</t>
+  </si>
+  <si>
+    <t>Defense Training Level 2</t>
+  </si>
+  <si>
+    <t>Defense Training Level 3</t>
+  </si>
+  <si>
+    <t>Defense Training Level 4</t>
+  </si>
+  <si>
+    <t>Defense Training Level 5</t>
+  </si>
+  <si>
+    <t>Defense Training Level 6</t>
+  </si>
+  <si>
+    <t>Defense Training Level 7</t>
+  </si>
+  <si>
+    <t>Defense Training Level 8</t>
+  </si>
+  <si>
+    <t>Defense Training Level 9</t>
+  </si>
+  <si>
+    <t>Defense Training Level 10</t>
+  </si>
+  <si>
+    <t>Defense Training Level 11</t>
+  </si>
+  <si>
+    <t>Defense Training Level 12</t>
+  </si>
+  <si>
+    <t>Defense Training Level 13</t>
+  </si>
+  <si>
+    <t>Defense Training Level 14</t>
+  </si>
+  <si>
+    <t>Defense Training Level 15</t>
+  </si>
+  <si>
+    <t>Defense Training Level 16</t>
+  </si>
+  <si>
+    <t>Defense Training Level 17</t>
+  </si>
+  <si>
+    <t>Defense Training Level 18</t>
+  </si>
+  <si>
+    <t>Defense Training Level 19</t>
+  </si>
+  <si>
+    <t>Magic Defense Training Level 1</t>
+  </si>
+  <si>
+    <t>Magic Defense Training Level 2</t>
+  </si>
+  <si>
+    <t>Magic Defense Training Level 3</t>
+  </si>
+  <si>
+    <t>Magic Defense Training Level 4</t>
+  </si>
+  <si>
+    <t>Magic Defense Training Level 5</t>
+  </si>
+  <si>
+    <t>Magic Defense Training Level 6</t>
+  </si>
+  <si>
+    <t>Magic Defense Training Level 7</t>
+  </si>
+  <si>
+    <t>Magic Defense Training Level 8</t>
+  </si>
+  <si>
+    <t>Magic Defense Training Level 9</t>
+  </si>
+  <si>
+    <t>Magic Defense Training Level 10</t>
+  </si>
+  <si>
+    <t>Magic Defense Training Level 11</t>
+  </si>
+  <si>
+    <t>Magic Defense Training Level 12</t>
+  </si>
+  <si>
+    <t>Magic Defense Training Level 13</t>
+  </si>
+  <si>
+    <t>Magic Defense Training Level 14</t>
+  </si>
+  <si>
+    <t>Magic Defense Training Level 15</t>
+  </si>
+  <si>
+    <t>Magic Defense Training Level 16</t>
+  </si>
+  <si>
+    <t>Magic Defense Training Level 17</t>
+  </si>
+  <si>
+    <t>Magic Defense Training Level 18</t>
+  </si>
+  <si>
+    <t>Magic Defense Training Level 19</t>
+  </si>
+  <si>
+    <t>130103;75@231103;0.01</t>
+  </si>
+  <si>
+    <t>130103;150@231103;0.02</t>
+  </si>
+  <si>
+    <t>130103;225@231103;0.03</t>
+  </si>
+  <si>
+    <t>130103;300@231103;0.04</t>
+  </si>
+  <si>
+    <t>130103;400@231103;0.05</t>
+  </si>
+  <si>
+    <t>130103;500@231103;0.06</t>
+  </si>
+  <si>
+    <t>130103;650@231103;0.07</t>
+  </si>
+  <si>
+    <t>130103;800@231103;0.08</t>
+  </si>
+  <si>
+    <t>130103;1000@231103;0.09</t>
+  </si>
+  <si>
+    <t>130103;1200@231103;0.1</t>
+  </si>
+  <si>
+    <t>130103;1450@231103;0.11</t>
+  </si>
+  <si>
+    <t>130103;1700@231103;0.12</t>
+  </si>
+  <si>
+    <t>130103;2000@231103;0.13</t>
+  </si>
+  <si>
+    <t>130103;3000@231103;0.15</t>
+  </si>
+  <si>
+    <t>130103;3600@231103;0.16</t>
+  </si>
+  <si>
+    <t>130103;4400@231103;0.17</t>
+  </si>
+  <si>
+    <t>130103;5200@231103;0.18</t>
+  </si>
+  <si>
+    <t>130103;6200@231103;0.19</t>
+  </si>
+  <si>
+    <t>130103;7200@231103;0.2</t>
+  </si>
+  <si>
+    <t>130003;75@231003;0.01</t>
+  </si>
+  <si>
+    <t>130003;150@231003;0.02</t>
+  </si>
+  <si>
+    <t>130003;225@231003;0.03</t>
+  </si>
+  <si>
+    <t>130003;300@231003;0.04</t>
+  </si>
+  <si>
+    <t>130003;400@231003;0.05</t>
+  </si>
+  <si>
+    <t>130003;500@231003;0.06</t>
+  </si>
+  <si>
+    <t>130003;650@231003;0.07</t>
+  </si>
+  <si>
+    <t>130003;800@231003;0.08</t>
+  </si>
+  <si>
+    <t>130003;1000@231003;0.09</t>
+  </si>
+  <si>
+    <t>130003;1200@231003;0.1</t>
+  </si>
+  <si>
+    <t>130003;1450@231003;0.11</t>
+  </si>
+  <si>
+    <t>130003;1700@231003;0.12</t>
+  </si>
+  <si>
+    <t>130003;2000@231003;0.13</t>
+  </si>
+  <si>
+    <t>130003;2400@231003;0.14</t>
+  </si>
+  <si>
+    <t>130003;3000@231003;0.15</t>
+  </si>
+  <si>
+    <t>130003;3600@231003;0.16</t>
+  </si>
+  <si>
+    <t>130003;4400@231003;0.17</t>
+  </si>
+  <si>
+    <t>130003;5200@231003;0.18</t>
+  </si>
+  <si>
+    <t>130003;6200@231003;0.19</t>
+  </si>
+  <si>
+    <t>130003;7200@231003;0.2</t>
+  </si>
+  <si>
+    <t>130203;75@230503;0.005@230603;0.005</t>
+  </si>
+  <si>
+    <t>130203;150@230503;0.01@230603;0.01</t>
+  </si>
+  <si>
+    <t>130203;225@230503;0.015@230603;0.015</t>
+  </si>
+  <si>
+    <t>130203;300@230503;0.02@230603;0.02</t>
+  </si>
+  <si>
+    <t>130203;400@230503;0.025@230603;0.025</t>
+  </si>
+  <si>
+    <t>130203;500@230503;0.03@230603;0.03</t>
+  </si>
+  <si>
+    <t>130203;650@230503;0.035@230603;0.035</t>
+  </si>
+  <si>
+    <t>130203;800@230503;0.04@230603;0.04</t>
+  </si>
+  <si>
+    <t>130203;1000@230503;0.045@230603;0.045</t>
+  </si>
+  <si>
+    <t>130203;1200@230503;0.05@230603;0.05</t>
+  </si>
+  <si>
+    <t>130203;1450@230503;0.055@230603;0.055</t>
+  </si>
+  <si>
+    <t>130203;1700@230503;0.06@230603;0.06</t>
+  </si>
+  <si>
+    <t>130203;2000@230503;0.065@230603;0.065</t>
+  </si>
+  <si>
+    <t>130203;2400@230503;0.07@230603;0.07</t>
+  </si>
+  <si>
+    <t>130203;3000@230503;0.075@230603;0.075</t>
+  </si>
+  <si>
+    <t>130203;3600@230503;0.08@230603;0.08</t>
+  </si>
+  <si>
+    <t>130203;4400@230503;0.085@230603;0.085</t>
+  </si>
+  <si>
+    <t>130203;5200@230503;0.09@230603;0.09</t>
+  </si>
+  <si>
+    <t>130203;6200@230503;0.095@230603;0.095</t>
+  </si>
+  <si>
+    <t>130203;7200@230503;0.1@230603;0.1</t>
+  </si>
+  <si>
+    <t>130303;150@230503;0.01@230603;0.01</t>
+  </si>
+  <si>
+    <t>130303;225@230503;0.015@230603;0.015</t>
+  </si>
+  <si>
+    <t>130303;300@230503;0.02@230603;0.02</t>
+  </si>
+  <si>
+    <t>130303;400@230503;0.025@230603;0.025</t>
+  </si>
+  <si>
+    <t>130303;500@230503;0.03@230603;0.03</t>
+  </si>
+  <si>
+    <t>130303;650@230503;0.035@230603;0.035</t>
+  </si>
+  <si>
+    <t>130303;800@230503;0.04@230603;0.04</t>
+  </si>
+  <si>
+    <t>130303;1000@230503;0.045@230603;0.045</t>
+  </si>
+  <si>
+    <t>130303;1200@230503;0.05@230603;0.05</t>
+  </si>
+  <si>
+    <t>130303;1450@230503;0.055@230603;0.055</t>
+  </si>
+  <si>
+    <t>130303;1700@230503;0.06@230603;0.06</t>
+  </si>
+  <si>
+    <t>130303;2000@230503;0.065@230603;0.065</t>
+  </si>
+  <si>
+    <t>130303;2400@230503;0.07@230603;0.07</t>
+  </si>
+  <si>
+    <t>130303;3000@230503;0.075@230603;0.075</t>
+  </si>
+  <si>
+    <t>130303;3600@230503;0.08@230603;0.08</t>
+  </si>
+  <si>
+    <t>130303;4400@230503;0.085@230603;0.085</t>
+  </si>
+  <si>
+    <t>130303;5200@230503;0.09@230603;0.09</t>
+  </si>
+  <si>
+    <t>130303;6200@230503;0.095@230603;0.095</t>
+  </si>
+  <si>
+    <t>130303;7200@230503;0.1@230603;0.1</t>
+  </si>
+  <si>
+    <t>130403;375@231403;0.005@230703;0.01</t>
+  </si>
+  <si>
+    <t>130403;750@231403;0.01@230703;0.02</t>
+  </si>
+  <si>
+    <t>130403;1125@231403;0.015@230703;0.03</t>
+  </si>
+  <si>
+    <t>130403;1500@231403;0.02@230703;0.04</t>
+  </si>
+  <si>
+    <t>130403;2000@231403;0.025@230703;0.05</t>
+  </si>
+  <si>
+    <t>130403;2500@231403;0.03@230703;0.06</t>
+  </si>
+  <si>
+    <t>130403;3250@231403;0.035@230703;0.07</t>
+  </si>
+  <si>
+    <t>130403;4000@231403;0.04@230703;0.08</t>
+  </si>
+  <si>
+    <t>130403;5000@231403;0.045@230703;0.09</t>
+  </si>
+  <si>
+    <t>130403;6000@231403;0.05@230703;0.1</t>
+  </si>
+  <si>
+    <t>130403;7250@231403;0.055@230703;0.11</t>
+  </si>
+  <si>
+    <t>130403;8500@231403;0.06@230703;0.12</t>
+  </si>
+  <si>
+    <t>130403;10000@231403;0.065@230703;0.13</t>
+  </si>
+  <si>
+    <t>130403;12000@231403;0.07@230703;0.14</t>
+  </si>
+  <si>
+    <t>130403;15000@231403;0.075@230703;0.15</t>
+  </si>
+  <si>
+    <t>130403;18000@231403;0.08@230703;0.16</t>
+  </si>
+  <si>
+    <t>130403;22000@231403;0.085@230703;0.17</t>
+  </si>
+  <si>
+    <t>130403;26000@231403;0.09@230703;0.18</t>
+  </si>
+  <si>
+    <t>130403;31000@231403;0.095@230703;0.19</t>
+  </si>
+  <si>
+    <t>130403;36000@231403;0.1@230703;0.2</t>
+  </si>
+  <si>
+    <t>攻击突破0级</t>
+  </si>
+  <si>
+    <t>攻击突破1级</t>
+  </si>
+  <si>
+    <t>攻击突破2级</t>
+  </si>
+  <si>
+    <t>攻击突破3级</t>
+  </si>
+  <si>
+    <t>攻击突破4级</t>
+  </si>
+  <si>
+    <t>攻击突破5级</t>
+  </si>
+  <si>
+    <t>攻击突破6级</t>
+  </si>
+  <si>
+    <t>攻击突破7级</t>
+  </si>
+  <si>
+    <t>攻击突破8级</t>
+  </si>
+  <si>
+    <t>攻击突破9级</t>
+  </si>
+  <si>
+    <t>攻击突破10级</t>
+  </si>
+  <si>
+    <t>攻击突破11级</t>
+  </si>
+  <si>
+    <t>攻击突破12级</t>
+  </si>
+  <si>
+    <t>攻击突破13级</t>
+  </si>
+  <si>
+    <t>攻击突破14级</t>
+  </si>
+  <si>
+    <t>攻击突破15级</t>
+  </si>
+  <si>
+    <t>攻击突破16级</t>
+  </si>
+  <si>
+    <t>攻击突破17级</t>
+  </si>
+  <si>
+    <t>攻击突破18级</t>
+  </si>
+  <si>
+    <t>攻击突破19级</t>
+  </si>
+  <si>
+    <t>攻击突破20级</t>
+  </si>
+  <si>
+    <t>魔法突破0级</t>
+  </si>
+  <si>
+    <t>魔法突破1级</t>
+  </si>
+  <si>
+    <t>魔法突破2级</t>
+  </si>
+  <si>
+    <t>魔法突破3级</t>
+  </si>
+  <si>
+    <t>魔法突破4级</t>
+  </si>
+  <si>
+    <t>魔法突破5级</t>
+  </si>
+  <si>
+    <t>魔法突破6级</t>
+  </si>
+  <si>
+    <t>魔法突破7级</t>
+  </si>
+  <si>
+    <t>魔法突破8级</t>
+  </si>
+  <si>
+    <t>魔法突破9级</t>
+  </si>
+  <si>
+    <t>魔法突破10级</t>
+  </si>
+  <si>
+    <t>魔法突破11级</t>
+  </si>
+  <si>
+    <t>魔法突破12级</t>
+  </si>
+  <si>
+    <t>魔法突破13级</t>
+  </si>
+  <si>
+    <t>魔法突破14级</t>
+  </si>
+  <si>
+    <t>魔法突破15级</t>
+  </si>
+  <si>
+    <t>魔法突破16级</t>
+  </si>
+  <si>
+    <t>魔法突破17级</t>
+  </si>
+  <si>
+    <t>魔法突破18级</t>
+  </si>
+  <si>
+    <t>魔法突破19级</t>
+  </si>
+  <si>
+    <t>魔法突破20级</t>
+  </si>
+  <si>
+    <t>防御突破0级</t>
+  </si>
+  <si>
+    <t>防御突破1级</t>
+  </si>
+  <si>
+    <t>防御突破2级</t>
+  </si>
+  <si>
+    <t>防御突破3级</t>
+  </si>
+  <si>
+    <t>防御突破4级</t>
+  </si>
+  <si>
+    <t>防御突破5级</t>
+  </si>
+  <si>
+    <t>防御突破6级</t>
+  </si>
+  <si>
+    <t>防御突破7级</t>
+  </si>
+  <si>
+    <t>防御突破8级</t>
+  </si>
+  <si>
+    <t>防御突破9级</t>
+  </si>
+  <si>
+    <t>防御突破10级</t>
+  </si>
+  <si>
+    <t>防御突破11级</t>
+  </si>
+  <si>
+    <t>防御突破12级</t>
+  </si>
+  <si>
+    <t>防御突破13级</t>
+  </si>
+  <si>
+    <t>防御突破14级</t>
+  </si>
+  <si>
+    <t>防御突破15级</t>
+  </si>
+  <si>
+    <t>防御突破16级</t>
+  </si>
+  <si>
+    <t>防御突破17级</t>
+  </si>
+  <si>
+    <t>防御突破18级</t>
+  </si>
+  <si>
+    <t>防御突破19级</t>
+  </si>
+  <si>
+    <t>防御突破20级</t>
+  </si>
+  <si>
+    <t>法防突破0级</t>
+  </si>
+  <si>
+    <t>法防突破1级</t>
+  </si>
+  <si>
+    <t>法防突破2级</t>
+  </si>
+  <si>
+    <t>法防突破3级</t>
+  </si>
+  <si>
+    <t>法防突破4级</t>
+  </si>
+  <si>
+    <t>法防突破5级</t>
+  </si>
+  <si>
+    <t>法防突破6级</t>
+  </si>
+  <si>
+    <t>法防突破7级</t>
+  </si>
+  <si>
+    <t>法防突破8级</t>
+  </si>
+  <si>
+    <t>法防突破9级</t>
+  </si>
+  <si>
+    <t>法防突破10级</t>
+  </si>
+  <si>
+    <t>法防突破11级</t>
+  </si>
+  <si>
+    <t>法防突破12级</t>
+  </si>
+  <si>
+    <t>法防突破13级</t>
+  </si>
+  <si>
+    <t>法防突破14级</t>
+  </si>
+  <si>
+    <t>法防突破15级</t>
+  </si>
+  <si>
+    <t>法防突破16级</t>
+  </si>
+  <si>
+    <t>法防突破17级</t>
+  </si>
+  <si>
+    <t>法防突破18级</t>
+  </si>
+  <si>
+    <t>法防突破19级</t>
+  </si>
+  <si>
+    <t>法防突破20级</t>
+  </si>
+  <si>
+    <t>生命突破0级</t>
+  </si>
+  <si>
+    <t>生命突破1级</t>
+  </si>
+  <si>
+    <t>生命突破2级</t>
+  </si>
+  <si>
+    <t>生命突破3级</t>
+  </si>
+  <si>
+    <t>生命突破4级</t>
+  </si>
+  <si>
+    <t>生命突破5级</t>
+  </si>
+  <si>
+    <t>生命突破6级</t>
+  </si>
+  <si>
+    <t>生命突破7级</t>
+  </si>
+  <si>
+    <t>生命突破8级</t>
+  </si>
+  <si>
+    <t>生命突破9级</t>
+  </si>
+  <si>
+    <t>生命突破10级</t>
+  </si>
+  <si>
+    <t>生命突破11级</t>
+  </si>
+  <si>
+    <t>生命突破12级</t>
+  </si>
+  <si>
+    <t>生命突破13级</t>
+  </si>
+  <si>
+    <t>生命突破14级</t>
+  </si>
+  <si>
+    <t>生命突破15级</t>
+  </si>
+  <si>
+    <t>生命突破16级</t>
+  </si>
+  <si>
+    <t>生命突破17级</t>
+  </si>
+  <si>
+    <t>生命突破18级</t>
+  </si>
+  <si>
+    <t>生命突破19级</t>
+  </si>
+  <si>
+    <t>生命突破20级</t>
+  </si>
+  <si>
+    <t>130103;2400@231103;0.14</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>1;1000000@10000168;10</t>
-  </si>
-  <si>
-    <t>1;2000000@10000168;20</t>
-  </si>
-  <si>
-    <t>1;3000000@10000168;30</t>
-  </si>
-  <si>
-    <t>1;4000000@10000168;40</t>
-  </si>
-  <si>
-    <t>1;6000000@10000168;60</t>
-  </si>
-  <si>
-    <t>1;7000000@10000168;70</t>
-  </si>
-  <si>
-    <t>1;8000000@10000168;80</t>
-  </si>
-  <si>
-    <t>1;9000000@10000168;90</t>
-  </si>
-  <si>
-    <t>1;12000000@10000168;120</t>
-  </si>
-  <si>
-    <t>1;14000000@10000168;140</t>
-  </si>
-  <si>
-    <t>1;16000000@10000168;160</t>
-  </si>
-  <si>
-    <t>1;18000000@10000168;180</t>
-  </si>
-  <si>
-    <t>1;22000000@10000168;220</t>
-  </si>
-  <si>
-    <t>1;24000000@10000168;240</t>
-  </si>
-  <si>
-    <t>1;26000000@10000168;260</t>
-  </si>
-  <si>
-    <t>1;28000000@10000168;280</t>
-  </si>
-  <si>
-    <t>生命修炼1级</t>
-  </si>
-  <si>
-    <t>Life Training Level 1</t>
-  </si>
-  <si>
-    <t>生命修炼2级</t>
-  </si>
-  <si>
-    <t>Life Training Level 2</t>
-  </si>
-  <si>
-    <t>生命修炼3级</t>
-  </si>
-  <si>
-    <t>Life Training Level 3</t>
-  </si>
-  <si>
-    <t>生命修炼4级</t>
-  </si>
-  <si>
-    <t>Life Training Level 4</t>
-  </si>
-  <si>
-    <t>生命修炼5级</t>
-  </si>
-  <si>
-    <t>Life Training Level 5</t>
-  </si>
-  <si>
-    <t>生命修炼6级</t>
-  </si>
-  <si>
-    <t>Life Training Level 6</t>
-  </si>
-  <si>
-    <t>生命修炼7级</t>
-  </si>
-  <si>
-    <t>Life Training Level 7</t>
-  </si>
-  <si>
-    <t>生命修炼8级</t>
-  </si>
-  <si>
-    <t>Life Training Level 8</t>
-  </si>
-  <si>
-    <t>生命修炼9级</t>
-  </si>
-  <si>
-    <t>Life Training Level 9</t>
-  </si>
-  <si>
-    <t>生命修炼10级</t>
-  </si>
-  <si>
-    <t>Life Training Level 10</t>
-  </si>
-  <si>
-    <t>生命修炼11级</t>
-  </si>
-  <si>
-    <t>Life Training Level 11</t>
-  </si>
-  <si>
-    <t>生命修炼12级</t>
-  </si>
-  <si>
-    <t>Life Training Level 12</t>
-  </si>
-  <si>
-    <t>生命修炼13级</t>
-  </si>
-  <si>
-    <t>Life Training Level 13</t>
-  </si>
-  <si>
-    <t>生命修炼14级</t>
-  </si>
-  <si>
-    <t>Life Training Level 14</t>
-  </si>
-  <si>
-    <t>生命修炼15级</t>
-  </si>
-  <si>
-    <t>Life Training Level 15</t>
-  </si>
-  <si>
-    <t>生命修炼16级</t>
-  </si>
-  <si>
-    <t>Life Training Level 16</t>
-  </si>
-  <si>
-    <t>生命修炼17级</t>
-  </si>
-  <si>
-    <t>Life Training Level 17</t>
-  </si>
-  <si>
-    <t>生命修炼18级</t>
-  </si>
-  <si>
-    <t>Life Training Level 18</t>
-  </si>
-  <si>
-    <t>生命修炼19级</t>
-  </si>
-  <si>
-    <t>Life Training Level 19</t>
-  </si>
-  <si>
-    <t>防御修炼1级</t>
-  </si>
-  <si>
-    <t>Defense Training Level 1</t>
-  </si>
-  <si>
-    <t>防御修炼2级</t>
-  </si>
-  <si>
-    <t>Defense Training Level 2</t>
-  </si>
-  <si>
-    <t>防御修炼3级</t>
-  </si>
-  <si>
-    <t>Defense Training Level 3</t>
-  </si>
-  <si>
-    <t>防御修炼4级</t>
-  </si>
-  <si>
-    <t>Defense Training Level 4</t>
-  </si>
-  <si>
-    <t>防御修炼5级</t>
-  </si>
-  <si>
-    <t>Defense Training Level 5</t>
-  </si>
-  <si>
-    <t>防御修炼6级</t>
-  </si>
-  <si>
-    <t>Defense Training Level 6</t>
-  </si>
-  <si>
-    <t>防御修炼7级</t>
-  </si>
-  <si>
-    <t>Defense Training Level 7</t>
-  </si>
-  <si>
-    <t>防御修炼8级</t>
-  </si>
-  <si>
-    <t>Defense Training Level 8</t>
-  </si>
-  <si>
-    <t>防御修炼9级</t>
-  </si>
-  <si>
-    <t>Defense Training Level 9</t>
-  </si>
-  <si>
-    <t>防御修炼10级</t>
-  </si>
-  <si>
-    <t>Defense Training Level 10</t>
-  </si>
-  <si>
-    <t>防御修炼11级</t>
-  </si>
-  <si>
-    <t>Defense Training Level 11</t>
-  </si>
-  <si>
-    <t>防御修炼12级</t>
-  </si>
-  <si>
-    <t>Defense Training Level 12</t>
-  </si>
-  <si>
-    <t>防御修炼13级</t>
-  </si>
-  <si>
-    <t>Defense Training Level 13</t>
-  </si>
-  <si>
-    <t>防御修炼14级</t>
-  </si>
-  <si>
-    <t>Defense Training Level 14</t>
-  </si>
-  <si>
-    <t>防御修炼15级</t>
-  </si>
-  <si>
-    <t>Defense Training Level 15</t>
-  </si>
-  <si>
-    <t>防御修炼16级</t>
-  </si>
-  <si>
-    <t>Defense Training Level 16</t>
-  </si>
-  <si>
-    <t>防御修炼17级</t>
-  </si>
-  <si>
-    <t>Defense Training Level 17</t>
-  </si>
-  <si>
-    <t>防御修炼18级</t>
-  </si>
-  <si>
-    <t>Defense Training Level 18</t>
-  </si>
-  <si>
-    <t>防御修炼19级</t>
-  </si>
-  <si>
-    <t>Defense Training Level 19</t>
-  </si>
-  <si>
-    <t>法防修炼1级</t>
-  </si>
-  <si>
-    <t>Magic Defense Training Level 1</t>
-  </si>
-  <si>
-    <t>法防修炼2级</t>
-  </si>
-  <si>
-    <t>Magic Defense Training Level 2</t>
-  </si>
-  <si>
-    <t>法防修炼3级</t>
-  </si>
-  <si>
-    <t>Magic Defense Training Level 3</t>
-  </si>
-  <si>
-    <t>法防修炼4级</t>
-  </si>
-  <si>
-    <t>Magic Defense Training Level 4</t>
-  </si>
-  <si>
-    <t>法防修炼5级</t>
-  </si>
-  <si>
-    <t>Magic Defense Training Level 5</t>
-  </si>
-  <si>
-    <t>法防修炼6级</t>
-  </si>
-  <si>
-    <t>Magic Defense Training Level 6</t>
-  </si>
-  <si>
-    <t>法防修炼7级</t>
-  </si>
-  <si>
-    <t>Magic Defense Training Level 7</t>
-  </si>
-  <si>
-    <t>法防修炼8级</t>
-  </si>
-  <si>
-    <t>Magic Defense Training Level 8</t>
-  </si>
-  <si>
-    <t>法防修炼9级</t>
-  </si>
-  <si>
-    <t>Magic Defense Training Level 9</t>
-  </si>
-  <si>
-    <t>法防修炼10级</t>
-  </si>
-  <si>
-    <t>Magic Defense Training Level 10</t>
-  </si>
-  <si>
-    <t>法防修炼11级</t>
-  </si>
-  <si>
-    <t>Magic Defense Training Level 11</t>
-  </si>
-  <si>
-    <t>法防修炼12级</t>
-  </si>
-  <si>
-    <t>Magic Defense Training Level 12</t>
-  </si>
-  <si>
-    <t>法防修炼13级</t>
-  </si>
-  <si>
-    <t>Magic Defense Training Level 13</t>
-  </si>
-  <si>
-    <t>法防修炼14级</t>
-  </si>
-  <si>
-    <t>Magic Defense Training Level 14</t>
-  </si>
-  <si>
-    <t>法防修炼15级</t>
-  </si>
-  <si>
-    <t>Magic Defense Training Level 15</t>
-  </si>
-  <si>
-    <t>法防修炼16级</t>
-  </si>
-  <si>
-    <t>Magic Defense Training Level 16</t>
-  </si>
-  <si>
-    <t>法防修炼17级</t>
-  </si>
-  <si>
-    <t>Magic Defense Training Level 17</t>
-  </si>
-  <si>
-    <t>法防修炼18级</t>
-  </si>
-  <si>
-    <t>Magic Defense Training Level 18</t>
-  </si>
-  <si>
-    <t>法防修炼19级</t>
-  </si>
-  <si>
-    <t>Magic Defense Training Level 19</t>
-  </si>
-  <si>
-    <t>130103;75@231103;0.01</t>
-  </si>
-  <si>
-    <t>130103;150@231103;0.02</t>
-  </si>
-  <si>
-    <t>130103;225@231103;0.03</t>
-  </si>
-  <si>
-    <t>130103;300@231103;0.04</t>
-  </si>
-  <si>
-    <t>130103;400@231103;0.05</t>
-  </si>
-  <si>
-    <t>130103;500@231103;0.06</t>
-  </si>
-  <si>
-    <t>130103;650@231103;0.07</t>
-  </si>
-  <si>
-    <t>130103;800@231103;0.08</t>
-  </si>
-  <si>
-    <t>130103;1000@231103;0.09</t>
-  </si>
-  <si>
-    <t>130103;1200@231103;0.1</t>
-  </si>
-  <si>
-    <t>130103;1450@231103;0.11</t>
-  </si>
-  <si>
-    <t>130103;1700@231103;0.12</t>
-  </si>
-  <si>
-    <t>130103;2000@231103;0.13</t>
-  </si>
-  <si>
-    <t>130103;2400@231103;0.14</t>
-  </si>
-  <si>
-    <t>130103;3000@231103;0.15</t>
-  </si>
-  <si>
-    <t>130103;3600@231103;0.16</t>
-  </si>
-  <si>
-    <t>130103;4400@231103;0.17</t>
-  </si>
-  <si>
-    <t>130103;5200@231103;0.18</t>
-  </si>
-  <si>
-    <t>130103;6200@231103;0.19</t>
-  </si>
-  <si>
-    <t>130103;7200@231103;0.2</t>
-  </si>
-  <si>
-    <t>130003;75@231003;0.01</t>
-  </si>
-  <si>
-    <t>130003;150@231003;0.02</t>
-  </si>
-  <si>
-    <t>130003;225@231003;0.03</t>
-  </si>
-  <si>
-    <t>130003;300@231003;0.04</t>
-  </si>
-  <si>
-    <t>130003;400@231003;0.05</t>
-  </si>
-  <si>
-    <t>130003;500@231003;0.06</t>
-  </si>
-  <si>
-    <t>130003;650@231003;0.07</t>
-  </si>
-  <si>
-    <t>130003;800@231003;0.08</t>
-  </si>
-  <si>
-    <t>130003;1000@231003;0.09</t>
-  </si>
-  <si>
-    <t>130003;1200@231003;0.1</t>
-  </si>
-  <si>
-    <t>130003;1450@231003;0.11</t>
-  </si>
-  <si>
-    <t>130003;1700@231003;0.12</t>
-  </si>
-  <si>
-    <t>130003;2000@231003;0.13</t>
-  </si>
-  <si>
-    <t>130003;2400@231003;0.14</t>
-  </si>
-  <si>
-    <t>130003;3000@231003;0.15</t>
-  </si>
-  <si>
-    <t>130003;3600@231003;0.16</t>
-  </si>
-  <si>
-    <t>130003;4400@231003;0.17</t>
-  </si>
-  <si>
-    <t>130003;5200@231003;0.18</t>
-  </si>
-  <si>
-    <t>130003;6200@231003;0.19</t>
-  </si>
-  <si>
-    <t>130003;7200@231003;0.2</t>
-  </si>
-  <si>
-    <t>130203;75@230503;0.005@230603;0.005</t>
-  </si>
-  <si>
-    <t>130203;150@230503;0.01@230603;0.01</t>
-  </si>
-  <si>
-    <t>130203;225@230503;0.015@230603;0.015</t>
-  </si>
-  <si>
-    <t>130203;300@230503;0.02@230603;0.02</t>
-  </si>
-  <si>
-    <t>130203;400@230503;0.025@230603;0.025</t>
-  </si>
-  <si>
-    <t>130203;500@230503;0.03@230603;0.03</t>
-  </si>
-  <si>
-    <t>130203;650@230503;0.035@230603;0.035</t>
-  </si>
-  <si>
-    <t>130203;800@230503;0.04@230603;0.04</t>
-  </si>
-  <si>
-    <t>130203;1000@230503;0.045@230603;0.045</t>
-  </si>
-  <si>
-    <t>130203;1200@230503;0.05@230603;0.05</t>
-  </si>
-  <si>
-    <t>130203;1450@230503;0.055@230603;0.055</t>
-  </si>
-  <si>
-    <t>130203;1700@230503;0.06@230603;0.06</t>
-  </si>
-  <si>
-    <t>130203;2000@230503;0.065@230603;0.065</t>
-  </si>
-  <si>
-    <t>130203;2400@230503;0.07@230603;0.07</t>
-  </si>
-  <si>
-    <t>130203;3000@230503;0.075@230603;0.075</t>
-  </si>
-  <si>
-    <t>130203;3600@230503;0.08@230603;0.08</t>
-  </si>
-  <si>
-    <t>130203;4400@230503;0.085@230603;0.085</t>
-  </si>
-  <si>
-    <t>130203;5200@230503;0.09@230603;0.09</t>
-  </si>
-  <si>
-    <t>130203;6200@230503;0.095@230603;0.095</t>
-  </si>
-  <si>
-    <t>130203;7200@230503;0.1@230603;0.1</t>
-  </si>
-  <si>
     <t>130303;75@230503;0.005@230603;0.005</t>
-  </si>
-  <si>
-    <t>130303;150@230503;0.01@230603;0.01</t>
-  </si>
-  <si>
-    <t>130303;225@230503;0.015@230603;0.015</t>
-  </si>
-  <si>
-    <t>130303;300@230503;0.02@230603;0.02</t>
-  </si>
-  <si>
-    <t>130303;400@230503;0.025@230603;0.025</t>
-  </si>
-  <si>
-    <t>130303;500@230503;0.03@230603;0.03</t>
-  </si>
-  <si>
-    <t>130303;650@230503;0.035@230603;0.035</t>
-  </si>
-  <si>
-    <t>130303;800@230503;0.04@230603;0.04</t>
-  </si>
-  <si>
-    <t>130303;1000@230503;0.045@230603;0.045</t>
-  </si>
-  <si>
-    <t>130303;1200@230503;0.05@230603;0.05</t>
-  </si>
-  <si>
-    <t>130303;1450@230503;0.055@230603;0.055</t>
-  </si>
-  <si>
-    <t>130303;1700@230503;0.06@230603;0.06</t>
-  </si>
-  <si>
-    <t>130303;2000@230503;0.065@230603;0.065</t>
-  </si>
-  <si>
-    <t>130303;2400@230503;0.07@230603;0.07</t>
-  </si>
-  <si>
-    <t>130303;3000@230503;0.075@230603;0.075</t>
-  </si>
-  <si>
-    <t>130303;3600@230503;0.08@230603;0.08</t>
-  </si>
-  <si>
-    <t>130303;4400@230503;0.085@230603;0.085</t>
-  </si>
-  <si>
-    <t>130303;5200@230503;0.09@230603;0.09</t>
-  </si>
-  <si>
-    <t>130303;6200@230503;0.095@230603;0.095</t>
-  </si>
-  <si>
-    <t>130303;7200@230503;0.1@230603;0.1</t>
-  </si>
-  <si>
-    <t>130403;375@231403;0.005@230703;0.01</t>
-  </si>
-  <si>
-    <t>130403;750@231403;0.01@230703;0.02</t>
-  </si>
-  <si>
-    <t>130403;1125@231403;0.015@230703;0.03</t>
-  </si>
-  <si>
-    <t>130403;1500@231403;0.02@230703;0.04</t>
-  </si>
-  <si>
-    <t>130403;2000@231403;0.025@230703;0.05</t>
-  </si>
-  <si>
-    <t>130403;2500@231403;0.03@230703;0.06</t>
-  </si>
-  <si>
-    <t>130403;3250@231403;0.035@230703;0.07</t>
-  </si>
-  <si>
-    <t>130403;4000@231403;0.04@230703;0.08</t>
-  </si>
-  <si>
-    <t>130403;5000@231403;0.045@230703;0.09</t>
-  </si>
-  <si>
-    <t>130403;6000@231403;0.05@230703;0.1</t>
-  </si>
-  <si>
-    <t>130403;7250@231403;0.055@230703;0.11</t>
-  </si>
-  <si>
-    <t>130403;8500@231403;0.06@230703;0.12</t>
-  </si>
-  <si>
-    <t>130403;10000@231403;0.065@230703;0.13</t>
-  </si>
-  <si>
-    <t>130403;12000@231403;0.07@230703;0.14</t>
-  </si>
-  <si>
-    <t>130403;15000@231403;0.075@230703;0.15</t>
-  </si>
-  <si>
-    <t>130403;18000@231403;0.08@230703;0.16</t>
-  </si>
-  <si>
-    <t>130403;22000@231403;0.085@230703;0.17</t>
-  </si>
-  <si>
-    <t>130403;26000@231403;0.09@230703;0.18</t>
-  </si>
-  <si>
-    <t>130403;31000@231403;0.095@230703;0.19</t>
-  </si>
-  <si>
-    <t>130403;36000@231403;0.1@230703;0.2</t>
-  </si>
-  <si>
-    <t>1;5000000@10000168;50@10000169;10</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>1;10000000@10000168;100@10000169;20</t>
+    <t>消耗金币</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>1;20000000@10000168;200@10000169;30</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>1;30000000@10000168;300@10000169;40</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <t>10000168;20@10000169;5</t>
+  </si>
+  <si>
+    <t>10000168;30@10000169;5</t>
+  </si>
+  <si>
+    <t>10000168;40@10000169;5</t>
+  </si>
+  <si>
+    <t>10000168;50@10000169;5</t>
+  </si>
+  <si>
+    <t>10000168;60@10000169;10</t>
+  </si>
+  <si>
+    <t>10000168;70@10000169;10</t>
+  </si>
+  <si>
+    <t>10000168;80@10000169;10</t>
+  </si>
+  <si>
+    <t>10000168;90@10000169;10</t>
+  </si>
+  <si>
+    <t>10000168;100@10000169;10</t>
+  </si>
+  <si>
+    <t>10000168;120@10000169;20</t>
+  </si>
+  <si>
+    <t>10000168;140@10000169;20</t>
+  </si>
+  <si>
+    <t>10000168;160@10000169;20</t>
+  </si>
+  <si>
+    <t>10000168;180@10000169;20</t>
+  </si>
+  <si>
+    <t>10000168;200@10000169;20</t>
+  </si>
+  <si>
+    <t>10000168;220@10000169;30</t>
+  </si>
+  <si>
+    <t>10000168;240@10000169;30</t>
+  </si>
+  <si>
+    <t>10000168;260@10000169;30</t>
+  </si>
+  <si>
+    <t>10000168;280@10000169;30</t>
+  </si>
+  <si>
+    <t>10000168;300@10000169;30</t>
+  </si>
+  <si>
+    <t>10000168;25@10000169;5</t>
   </si>
 </sst>
 </file>
@@ -2525,7 +2583,7 @@
     <col min="5" max="5" width="30.625" style="2" customWidth="1"/>
     <col min="6" max="10" width="14.125" style="2" customWidth="1"/>
     <col min="11" max="11" width="37.125" style="2" customWidth="1"/>
-    <col min="12" max="12" width="24.875" style="2" customWidth="1"/>
+    <col min="12" max="12" width="41.625" style="2" customWidth="1"/>
     <col min="13" max="13" width="21.75" style="2" customWidth="1"/>
     <col min="14" max="239" width="8.875" style="2" customWidth="1"/>
   </cols>
@@ -2560,16 +2618,16 @@
         <v>6</v>
       </c>
       <c r="J3" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="K3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="L3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="M3" s="5" t="s">
         <v>9</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="4" spans="3:13" ht="20.100000000000001" customHeight="1">
@@ -2577,69 +2635,69 @@
         <v>1</v>
       </c>
       <c r="D4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="F4" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="G4" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="H4" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="I4" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="J4" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="K4" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="K4" s="7" t="s">
+      <c r="L4" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="M4" s="7" t="s">
         <v>19</v>
-      </c>
-      <c r="M4" s="7" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="5" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="E5" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="J5" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M5" s="7" t="s">
         <v>22</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="L5" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="M5" s="7" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="6" spans="3:13" ht="20.100000000000001" customHeight="1">
@@ -2647,10 +2705,10 @@
         <v>20100</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>24</v>
+        <v>205</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F6" s="8">
         <v>20101</v>
@@ -2664,11 +2722,11 @@
       <c r="I6" s="11">
         <v>1</v>
       </c>
-      <c r="J6" s="12" t="s">
-        <v>78</v>
+      <c r="J6" s="12">
+        <v>1000000</v>
       </c>
       <c r="K6" s="11" t="s">
-        <v>79</v>
+        <v>313</v>
       </c>
       <c r="L6" s="11"/>
       <c r="M6" s="11">
@@ -2680,10 +2738,10 @@
         <v>20101</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>40</v>
+        <v>206</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="F7" s="8">
         <v>20102</v>
@@ -2697,14 +2755,14 @@
       <c r="I7" s="11">
         <v>1</v>
       </c>
-      <c r="J7" s="12" t="s">
-        <v>78</v>
+      <c r="J7" s="12">
+        <v>2000000</v>
       </c>
       <c r="K7" s="11" t="s">
-        <v>80</v>
+        <v>332</v>
       </c>
       <c r="L7" s="11" t="s">
-        <v>209</v>
+        <v>107</v>
       </c>
       <c r="M7" s="11">
         <v>0</v>
@@ -2715,10 +2773,10 @@
         <v>20102</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>42</v>
+        <v>207</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="F8" s="8">
         <v>20103</v>
@@ -2732,14 +2790,14 @@
       <c r="I8" s="11">
         <v>1</v>
       </c>
-      <c r="J8" s="12" t="s">
-        <v>78</v>
+      <c r="J8" s="12">
+        <v>3000000</v>
       </c>
       <c r="K8" s="11" t="s">
-        <v>81</v>
+        <v>314</v>
       </c>
       <c r="L8" s="11" t="s">
-        <v>210</v>
+        <v>108</v>
       </c>
       <c r="M8" s="11">
         <v>0</v>
@@ -2750,10 +2808,10 @@
         <v>20103</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>44</v>
+        <v>208</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="F9" s="8">
         <v>20104</v>
@@ -2767,14 +2825,14 @@
       <c r="I9" s="11">
         <v>1</v>
       </c>
-      <c r="J9" s="12" t="s">
-        <v>78</v>
+      <c r="J9" s="12">
+        <v>4000000</v>
       </c>
       <c r="K9" s="11" t="s">
-        <v>82</v>
+        <v>315</v>
       </c>
       <c r="L9" s="11" t="s">
-        <v>211</v>
+        <v>109</v>
       </c>
       <c r="M9" s="11">
         <v>0</v>
@@ -2785,10 +2843,10 @@
         <v>20104</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>46</v>
+        <v>209</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="F10" s="8">
         <v>20105</v>
@@ -2802,14 +2860,14 @@
       <c r="I10" s="11">
         <v>1</v>
       </c>
-      <c r="J10" s="12" t="s">
-        <v>78</v>
+      <c r="J10" s="12">
+        <v>5000000</v>
       </c>
       <c r="K10" s="11" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="L10" s="11" t="s">
-        <v>212</v>
+        <v>110</v>
       </c>
       <c r="M10" s="11">
         <v>0</v>
@@ -2820,10 +2878,10 @@
         <v>20105</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>48</v>
+        <v>210</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="F11" s="8">
         <v>20106</v>
@@ -2837,14 +2895,14 @@
       <c r="I11" s="11">
         <v>1</v>
       </c>
-      <c r="J11" s="12" t="s">
-        <v>78</v>
+      <c r="J11" s="12">
+        <v>6000000</v>
       </c>
       <c r="K11" s="11" t="s">
-        <v>83</v>
+        <v>317</v>
       </c>
       <c r="L11" s="11" t="s">
-        <v>213</v>
+        <v>111</v>
       </c>
       <c r="M11" s="11">
         <v>0</v>
@@ -2855,10 +2913,10 @@
         <v>20106</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>50</v>
+        <v>211</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="F12" s="8">
         <v>20107</v>
@@ -2872,14 +2930,14 @@
       <c r="I12" s="11">
         <v>1</v>
       </c>
-      <c r="J12" s="12" t="s">
-        <v>78</v>
+      <c r="J12" s="12">
+        <v>7000000</v>
       </c>
       <c r="K12" s="11" t="s">
-        <v>84</v>
+        <v>318</v>
       </c>
       <c r="L12" s="11" t="s">
-        <v>214</v>
+        <v>112</v>
       </c>
       <c r="M12" s="11">
         <v>0</v>
@@ -2890,10 +2948,10 @@
         <v>20107</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>52</v>
+        <v>212</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="F13" s="8">
         <v>20108</v>
@@ -2907,14 +2965,14 @@
       <c r="I13" s="11">
         <v>1</v>
       </c>
-      <c r="J13" s="12" t="s">
-        <v>78</v>
+      <c r="J13" s="12">
+        <v>8000000</v>
       </c>
       <c r="K13" s="11" t="s">
-        <v>85</v>
+        <v>319</v>
       </c>
       <c r="L13" s="11" t="s">
-        <v>215</v>
+        <v>113</v>
       </c>
       <c r="M13" s="11">
         <v>0</v>
@@ -2925,10 +2983,10 @@
         <v>20108</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>54</v>
+        <v>213</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F14" s="8">
         <v>20109</v>
@@ -2942,14 +3000,14 @@
       <c r="I14" s="11">
         <v>1</v>
       </c>
-      <c r="J14" s="12" t="s">
-        <v>78</v>
+      <c r="J14" s="12">
+        <v>9000000</v>
       </c>
       <c r="K14" s="11" t="s">
-        <v>86</v>
+        <v>320</v>
       </c>
       <c r="L14" s="11" t="s">
-        <v>216</v>
+        <v>114</v>
       </c>
       <c r="M14" s="11">
         <v>0</v>
@@ -2960,10 +3018,10 @@
         <v>20109</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>56</v>
+        <v>214</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="F15" s="8">
         <v>20110</v>
@@ -2977,14 +3035,14 @@
       <c r="I15" s="11">
         <v>1</v>
       </c>
-      <c r="J15" s="12" t="s">
-        <v>78</v>
+      <c r="J15" s="12">
+        <v>10000000</v>
       </c>
       <c r="K15" s="11" t="s">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="L15" s="11" t="s">
-        <v>217</v>
+        <v>115</v>
       </c>
       <c r="M15" s="11">
         <v>0</v>
@@ -2995,10 +3053,10 @@
         <v>20110</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>58</v>
+        <v>215</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="F16" s="8">
         <v>20111</v>
@@ -3012,14 +3070,14 @@
       <c r="I16" s="11">
         <v>1</v>
       </c>
-      <c r="J16" s="12" t="s">
-        <v>78</v>
+      <c r="J16" s="12">
+        <v>12000000</v>
       </c>
       <c r="K16" s="11" t="s">
-        <v>87</v>
+        <v>322</v>
       </c>
       <c r="L16" s="11" t="s">
-        <v>218</v>
+        <v>116</v>
       </c>
       <c r="M16" s="11">
         <v>0</v>
@@ -3030,10 +3088,10 @@
         <v>20111</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>60</v>
+        <v>216</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="F17" s="8">
         <v>20112</v>
@@ -3047,14 +3105,14 @@
       <c r="I17" s="11">
         <v>1</v>
       </c>
-      <c r="J17" s="12" t="s">
-        <v>78</v>
+      <c r="J17" s="12">
+        <v>14000000</v>
       </c>
       <c r="K17" s="11" t="s">
-        <v>88</v>
+        <v>323</v>
       </c>
       <c r="L17" s="11" t="s">
-        <v>219</v>
+        <v>117</v>
       </c>
       <c r="M17" s="11">
         <v>0</v>
@@ -3065,10 +3123,10 @@
         <v>20112</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>62</v>
+        <v>217</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="F18" s="8">
         <v>20113</v>
@@ -3082,14 +3140,14 @@
       <c r="I18" s="11">
         <v>1</v>
       </c>
-      <c r="J18" s="12" t="s">
-        <v>78</v>
+      <c r="J18" s="12">
+        <v>16000000</v>
       </c>
       <c r="K18" s="11" t="s">
-        <v>89</v>
+        <v>324</v>
       </c>
       <c r="L18" s="11" t="s">
-        <v>220</v>
+        <v>118</v>
       </c>
       <c r="M18" s="11">
         <v>0</v>
@@ -3100,10 +3158,10 @@
         <v>20113</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>64</v>
+        <v>218</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="F19" s="8">
         <v>20114</v>
@@ -3117,14 +3175,14 @@
       <c r="I19" s="11">
         <v>1</v>
       </c>
-      <c r="J19" s="12" t="s">
-        <v>78</v>
+      <c r="J19" s="12">
+        <v>18000000</v>
       </c>
       <c r="K19" s="11" t="s">
-        <v>90</v>
+        <v>325</v>
       </c>
       <c r="L19" s="11" t="s">
-        <v>221</v>
+        <v>119</v>
       </c>
       <c r="M19" s="11">
         <v>0</v>
@@ -3135,10 +3193,10 @@
         <v>20114</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>66</v>
+        <v>219</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="F20" s="8">
         <v>20115</v>
@@ -3152,14 +3210,14 @@
       <c r="I20" s="11">
         <v>1</v>
       </c>
-      <c r="J20" s="12" t="s">
-        <v>78</v>
+      <c r="J20" s="12">
+        <v>20000000</v>
       </c>
       <c r="K20" s="11" t="s">
-        <v>311</v>
+        <v>326</v>
       </c>
       <c r="L20" s="11" t="s">
-        <v>222</v>
+        <v>310</v>
       </c>
       <c r="M20" s="11">
         <v>0</v>
@@ -3170,10 +3228,10 @@
         <v>20115</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>68</v>
+        <v>220</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="F21" s="8">
         <v>20116</v>
@@ -3187,14 +3245,14 @@
       <c r="I21" s="11">
         <v>1</v>
       </c>
-      <c r="J21" s="12" t="s">
-        <v>78</v>
+      <c r="J21" s="12">
+        <v>22000000</v>
       </c>
       <c r="K21" s="11" t="s">
-        <v>91</v>
+        <v>327</v>
       </c>
       <c r="L21" s="11" t="s">
-        <v>223</v>
+        <v>120</v>
       </c>
       <c r="M21" s="11">
         <v>0</v>
@@ -3205,10 +3263,10 @@
         <v>20116</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>70</v>
+        <v>221</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="F22" s="8">
         <v>20117</v>
@@ -3222,14 +3280,14 @@
       <c r="I22" s="11">
         <v>1</v>
       </c>
-      <c r="J22" s="12" t="s">
-        <v>78</v>
+      <c r="J22" s="12">
+        <v>24000000</v>
       </c>
       <c r="K22" s="11" t="s">
-        <v>92</v>
+        <v>328</v>
       </c>
       <c r="L22" s="11" t="s">
-        <v>224</v>
+        <v>121</v>
       </c>
       <c r="M22" s="11">
         <v>0</v>
@@ -3240,10 +3298,10 @@
         <v>20117</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>72</v>
+        <v>222</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="F23" s="8">
         <v>20118</v>
@@ -3257,14 +3315,14 @@
       <c r="I23" s="11">
         <v>1</v>
       </c>
-      <c r="J23" s="12" t="s">
-        <v>78</v>
+      <c r="J23" s="12">
+        <v>26000000</v>
       </c>
       <c r="K23" s="11" t="s">
-        <v>93</v>
+        <v>329</v>
       </c>
       <c r="L23" s="11" t="s">
-        <v>225</v>
+        <v>122</v>
       </c>
       <c r="M23" s="11">
         <v>0</v>
@@ -3275,10 +3333,10 @@
         <v>20118</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>74</v>
+        <v>223</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="F24" s="8">
         <v>20119</v>
@@ -3292,14 +3350,14 @@
       <c r="I24" s="11">
         <v>1</v>
       </c>
-      <c r="J24" s="12" t="s">
-        <v>78</v>
+      <c r="J24" s="12">
+        <v>28000000</v>
       </c>
       <c r="K24" s="11" t="s">
-        <v>94</v>
+        <v>330</v>
       </c>
       <c r="L24" s="11" t="s">
-        <v>226</v>
+        <v>123</v>
       </c>
       <c r="M24" s="11">
         <v>0</v>
@@ -3310,10 +3368,10 @@
         <v>20119</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>76</v>
+        <v>224</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="F25" s="8">
         <v>20120</v>
@@ -3327,14 +3385,14 @@
       <c r="I25" s="11">
         <v>1</v>
       </c>
-      <c r="J25" s="12" t="s">
-        <v>78</v>
+      <c r="J25" s="12">
+        <v>30000000</v>
       </c>
       <c r="K25" s="11" t="s">
-        <v>312</v>
+        <v>331</v>
       </c>
       <c r="L25" s="11" t="s">
-        <v>227</v>
+        <v>124</v>
       </c>
       <c r="M25" s="11">
         <v>0</v>
@@ -3345,10 +3403,10 @@
         <v>20120</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>26</v>
+        <v>225</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F26" s="8">
         <v>0</v>
@@ -3362,14 +3420,14 @@
       <c r="I26" s="11">
         <v>1</v>
       </c>
-      <c r="J26" s="12" t="s">
-        <v>78</v>
+      <c r="J26" s="12">
+        <v>30000000</v>
       </c>
       <c r="K26" s="11" t="s">
-        <v>312</v>
+        <v>331</v>
       </c>
       <c r="L26" s="11" t="s">
-        <v>228</v>
+        <v>125</v>
       </c>
       <c r="M26" s="11">
         <v>0</v>
@@ -3380,10 +3438,10 @@
         <v>20200</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>28</v>
+        <v>226</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F27" s="8">
         <v>20201</v>
@@ -3397,11 +3455,11 @@
       <c r="I27" s="11">
         <v>1</v>
       </c>
-      <c r="J27" s="12" t="s">
-        <v>78</v>
+      <c r="J27" s="12">
+        <v>1000000</v>
       </c>
       <c r="K27" s="11" t="s">
-        <v>79</v>
+        <v>313</v>
       </c>
       <c r="L27" s="11"/>
       <c r="M27" s="11">
@@ -3413,10 +3471,10 @@
         <v>20201</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>95</v>
+        <v>227</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>96</v>
+        <v>50</v>
       </c>
       <c r="F28" s="8">
         <v>20202</v>
@@ -3430,14 +3488,14 @@
       <c r="I28" s="11">
         <v>1</v>
       </c>
-      <c r="J28" s="12" t="s">
-        <v>78</v>
+      <c r="J28" s="12">
+        <v>2000000</v>
       </c>
       <c r="K28" s="11" t="s">
-        <v>80</v>
+        <v>332</v>
       </c>
       <c r="L28" s="11" t="s">
-        <v>229</v>
+        <v>126</v>
       </c>
       <c r="M28" s="11">
         <v>0</v>
@@ -3448,10 +3506,10 @@
         <v>20202</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>97</v>
+        <v>228</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>98</v>
+        <v>51</v>
       </c>
       <c r="F29" s="8">
         <v>20203</v>
@@ -3465,14 +3523,14 @@
       <c r="I29" s="11">
         <v>1</v>
       </c>
-      <c r="J29" s="12" t="s">
-        <v>78</v>
+      <c r="J29" s="12">
+        <v>3000000</v>
       </c>
       <c r="K29" s="11" t="s">
-        <v>81</v>
+        <v>314</v>
       </c>
       <c r="L29" s="11" t="s">
-        <v>230</v>
+        <v>127</v>
       </c>
       <c r="M29" s="11">
         <v>0</v>
@@ -3483,10 +3541,10 @@
         <v>20203</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>99</v>
+        <v>229</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>100</v>
+        <v>52</v>
       </c>
       <c r="F30" s="8">
         <v>20204</v>
@@ -3500,14 +3558,14 @@
       <c r="I30" s="11">
         <v>1</v>
       </c>
-      <c r="J30" s="12" t="s">
-        <v>78</v>
+      <c r="J30" s="12">
+        <v>4000000</v>
       </c>
       <c r="K30" s="11" t="s">
-        <v>82</v>
+        <v>315</v>
       </c>
       <c r="L30" s="11" t="s">
-        <v>231</v>
+        <v>128</v>
       </c>
       <c r="M30" s="11">
         <v>0</v>
@@ -3518,10 +3576,10 @@
         <v>20204</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>101</v>
+        <v>230</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>102</v>
+        <v>53</v>
       </c>
       <c r="F31" s="8">
         <v>20205</v>
@@ -3535,14 +3593,14 @@
       <c r="I31" s="11">
         <v>1</v>
       </c>
-      <c r="J31" s="12" t="s">
-        <v>78</v>
+      <c r="J31" s="12">
+        <v>5000000</v>
       </c>
       <c r="K31" s="11" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="L31" s="11" t="s">
-        <v>232</v>
+        <v>129</v>
       </c>
       <c r="M31" s="11">
         <v>0</v>
@@ -3553,10 +3611,10 @@
         <v>20205</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>103</v>
+        <v>231</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>104</v>
+        <v>54</v>
       </c>
       <c r="F32" s="8">
         <v>20206</v>
@@ -3570,14 +3628,14 @@
       <c r="I32" s="11">
         <v>1</v>
       </c>
-      <c r="J32" s="12" t="s">
-        <v>78</v>
+      <c r="J32" s="12">
+        <v>6000000</v>
       </c>
       <c r="K32" s="11" t="s">
-        <v>83</v>
+        <v>317</v>
       </c>
       <c r="L32" s="11" t="s">
-        <v>233</v>
+        <v>130</v>
       </c>
       <c r="M32" s="11">
         <v>0</v>
@@ -3588,10 +3646,10 @@
         <v>20206</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>105</v>
+        <v>232</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
       <c r="F33" s="8">
         <v>20207</v>
@@ -3605,14 +3663,14 @@
       <c r="I33" s="11">
         <v>1</v>
       </c>
-      <c r="J33" s="12" t="s">
-        <v>78</v>
+      <c r="J33" s="12">
+        <v>7000000</v>
       </c>
       <c r="K33" s="11" t="s">
-        <v>84</v>
+        <v>318</v>
       </c>
       <c r="L33" s="11" t="s">
-        <v>234</v>
+        <v>131</v>
       </c>
       <c r="M33" s="11">
         <v>0</v>
@@ -3623,10 +3681,10 @@
         <v>20207</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>107</v>
+        <v>233</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>108</v>
+        <v>56</v>
       </c>
       <c r="F34" s="8">
         <v>20208</v>
@@ -3640,14 +3698,14 @@
       <c r="I34" s="11">
         <v>1</v>
       </c>
-      <c r="J34" s="12" t="s">
-        <v>78</v>
+      <c r="J34" s="12">
+        <v>8000000</v>
       </c>
       <c r="K34" s="11" t="s">
-        <v>85</v>
+        <v>319</v>
       </c>
       <c r="L34" s="11" t="s">
-        <v>235</v>
+        <v>132</v>
       </c>
       <c r="M34" s="11">
         <v>0</v>
@@ -3658,10 +3716,10 @@
         <v>20208</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>109</v>
+        <v>234</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>110</v>
+        <v>57</v>
       </c>
       <c r="F35" s="8">
         <v>20209</v>
@@ -3675,14 +3733,14 @@
       <c r="I35" s="11">
         <v>1</v>
       </c>
-      <c r="J35" s="12" t="s">
-        <v>78</v>
+      <c r="J35" s="12">
+        <v>9000000</v>
       </c>
       <c r="K35" s="11" t="s">
-        <v>86</v>
+        <v>320</v>
       </c>
       <c r="L35" s="11" t="s">
-        <v>236</v>
+        <v>133</v>
       </c>
       <c r="M35" s="11">
         <v>0</v>
@@ -3693,10 +3751,10 @@
         <v>20209</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>111</v>
+        <v>235</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>112</v>
+        <v>58</v>
       </c>
       <c r="F36" s="8">
         <v>20210</v>
@@ -3710,14 +3768,14 @@
       <c r="I36" s="11">
         <v>1</v>
       </c>
-      <c r="J36" s="12" t="s">
-        <v>78</v>
+      <c r="J36" s="12">
+        <v>10000000</v>
       </c>
       <c r="K36" s="11" t="s">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="L36" s="11" t="s">
-        <v>237</v>
+        <v>134</v>
       </c>
       <c r="M36" s="11">
         <v>0</v>
@@ -3728,10 +3786,10 @@
         <v>20210</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>113</v>
+        <v>236</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>114</v>
+        <v>59</v>
       </c>
       <c r="F37" s="8">
         <v>20211</v>
@@ -3745,14 +3803,14 @@
       <c r="I37" s="11">
         <v>1</v>
       </c>
-      <c r="J37" s="12" t="s">
-        <v>78</v>
+      <c r="J37" s="12">
+        <v>12000000</v>
       </c>
       <c r="K37" s="11" t="s">
-        <v>87</v>
+        <v>322</v>
       </c>
       <c r="L37" s="11" t="s">
-        <v>238</v>
+        <v>135</v>
       </c>
       <c r="M37" s="11">
         <v>0</v>
@@ -3763,10 +3821,10 @@
         <v>20211</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>115</v>
+        <v>237</v>
       </c>
       <c r="E38" s="10" t="s">
-        <v>116</v>
+        <v>60</v>
       </c>
       <c r="F38" s="8">
         <v>20212</v>
@@ -3780,14 +3838,14 @@
       <c r="I38" s="11">
         <v>1</v>
       </c>
-      <c r="J38" s="12" t="s">
-        <v>78</v>
+      <c r="J38" s="12">
+        <v>14000000</v>
       </c>
       <c r="K38" s="11" t="s">
-        <v>88</v>
+        <v>323</v>
       </c>
       <c r="L38" s="11" t="s">
-        <v>239</v>
+        <v>136</v>
       </c>
       <c r="M38" s="11">
         <v>0</v>
@@ -3798,10 +3856,10 @@
         <v>20212</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>117</v>
+        <v>238</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>118</v>
+        <v>61</v>
       </c>
       <c r="F39" s="8">
         <v>20213</v>
@@ -3815,14 +3873,14 @@
       <c r="I39" s="11">
         <v>1</v>
       </c>
-      <c r="J39" s="12" t="s">
-        <v>78</v>
+      <c r="J39" s="12">
+        <v>16000000</v>
       </c>
       <c r="K39" s="11" t="s">
-        <v>89</v>
+        <v>324</v>
       </c>
       <c r="L39" s="11" t="s">
-        <v>240</v>
+        <v>137</v>
       </c>
       <c r="M39" s="11">
         <v>0</v>
@@ -3833,10 +3891,10 @@
         <v>20213</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>119</v>
+        <v>239</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>120</v>
+        <v>62</v>
       </c>
       <c r="F40" s="8">
         <v>20214</v>
@@ -3850,14 +3908,14 @@
       <c r="I40" s="11">
         <v>1</v>
       </c>
-      <c r="J40" s="12" t="s">
-        <v>78</v>
+      <c r="J40" s="12">
+        <v>18000000</v>
       </c>
       <c r="K40" s="11" t="s">
-        <v>90</v>
+        <v>325</v>
       </c>
       <c r="L40" s="11" t="s">
-        <v>241</v>
+        <v>138</v>
       </c>
       <c r="M40" s="11">
         <v>0</v>
@@ -3868,10 +3926,10 @@
         <v>20214</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>121</v>
+        <v>240</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>122</v>
+        <v>63</v>
       </c>
       <c r="F41" s="8">
         <v>20215</v>
@@ -3885,14 +3943,14 @@
       <c r="I41" s="11">
         <v>1</v>
       </c>
-      <c r="J41" s="12" t="s">
-        <v>78</v>
+      <c r="J41" s="12">
+        <v>20000000</v>
       </c>
       <c r="K41" s="11" t="s">
-        <v>311</v>
+        <v>326</v>
       </c>
       <c r="L41" s="11" t="s">
-        <v>242</v>
+        <v>139</v>
       </c>
       <c r="M41" s="11">
         <v>0</v>
@@ -3903,10 +3961,10 @@
         <v>20215</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>123</v>
+        <v>241</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>124</v>
+        <v>64</v>
       </c>
       <c r="F42" s="8">
         <v>20216</v>
@@ -3920,14 +3978,14 @@
       <c r="I42" s="11">
         <v>1</v>
       </c>
-      <c r="J42" s="12" t="s">
-        <v>78</v>
+      <c r="J42" s="12">
+        <v>22000000</v>
       </c>
       <c r="K42" s="11" t="s">
-        <v>91</v>
+        <v>327</v>
       </c>
       <c r="L42" s="11" t="s">
-        <v>243</v>
+        <v>140</v>
       </c>
       <c r="M42" s="11">
         <v>0</v>
@@ -3938,10 +3996,10 @@
         <v>20216</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>125</v>
+        <v>242</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>126</v>
+        <v>65</v>
       </c>
       <c r="F43" s="8">
         <v>20217</v>
@@ -3955,14 +4013,14 @@
       <c r="I43" s="11">
         <v>1</v>
       </c>
-      <c r="J43" s="12" t="s">
-        <v>78</v>
+      <c r="J43" s="12">
+        <v>24000000</v>
       </c>
       <c r="K43" s="11" t="s">
-        <v>92</v>
+        <v>328</v>
       </c>
       <c r="L43" s="11" t="s">
-        <v>244</v>
+        <v>141</v>
       </c>
       <c r="M43" s="11">
         <v>0</v>
@@ -3973,10 +4031,10 @@
         <v>20217</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>127</v>
+        <v>243</v>
       </c>
       <c r="E44" s="10" t="s">
-        <v>128</v>
+        <v>66</v>
       </c>
       <c r="F44" s="8">
         <v>20218</v>
@@ -3990,14 +4048,14 @@
       <c r="I44" s="11">
         <v>1</v>
       </c>
-      <c r="J44" s="12" t="s">
-        <v>78</v>
+      <c r="J44" s="12">
+        <v>26000000</v>
       </c>
       <c r="K44" s="11" t="s">
-        <v>93</v>
+        <v>329</v>
       </c>
       <c r="L44" s="11" t="s">
-        <v>245</v>
+        <v>142</v>
       </c>
       <c r="M44" s="11">
         <v>0</v>
@@ -4008,10 +4066,10 @@
         <v>20218</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>129</v>
+        <v>244</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>130</v>
+        <v>67</v>
       </c>
       <c r="F45" s="8">
         <v>20219</v>
@@ -4025,14 +4083,14 @@
       <c r="I45" s="11">
         <v>1</v>
       </c>
-      <c r="J45" s="12" t="s">
-        <v>78</v>
+      <c r="J45" s="12">
+        <v>28000000</v>
       </c>
       <c r="K45" s="11" t="s">
-        <v>94</v>
+        <v>330</v>
       </c>
       <c r="L45" s="11" t="s">
-        <v>246</v>
+        <v>143</v>
       </c>
       <c r="M45" s="11">
         <v>0</v>
@@ -4043,10 +4101,10 @@
         <v>20219</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>131</v>
+        <v>245</v>
       </c>
       <c r="E46" s="10" t="s">
-        <v>132</v>
+        <v>68</v>
       </c>
       <c r="F46" s="8">
         <v>20220</v>
@@ -4060,14 +4118,14 @@
       <c r="I46" s="11">
         <v>1</v>
       </c>
-      <c r="J46" s="12" t="s">
-        <v>78</v>
+      <c r="J46" s="12">
+        <v>30000000</v>
       </c>
       <c r="K46" s="11" t="s">
-        <v>312</v>
+        <v>331</v>
       </c>
       <c r="L46" s="11" t="s">
-        <v>247</v>
+        <v>144</v>
       </c>
       <c r="M46" s="11">
         <v>0</v>
@@ -4078,10 +4136,10 @@
         <v>20220</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>30</v>
+        <v>246</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F47" s="8">
         <v>0</v>
@@ -4095,14 +4153,14 @@
       <c r="I47" s="11">
         <v>1</v>
       </c>
-      <c r="J47" s="12" t="s">
-        <v>78</v>
+      <c r="J47" s="12">
+        <v>30000000</v>
       </c>
       <c r="K47" s="11" t="s">
-        <v>312</v>
+        <v>331</v>
       </c>
       <c r="L47" s="11" t="s">
-        <v>248</v>
+        <v>145</v>
       </c>
       <c r="M47" s="11">
         <v>0</v>
@@ -4113,10 +4171,10 @@
         <v>20300</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>32</v>
+        <v>247</v>
       </c>
       <c r="E48" s="10" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F48" s="8">
         <v>20301</v>
@@ -4130,11 +4188,11 @@
       <c r="I48" s="11">
         <v>1</v>
       </c>
-      <c r="J48" s="12" t="s">
-        <v>78</v>
+      <c r="J48" s="12">
+        <v>1000000</v>
       </c>
       <c r="K48" s="11" t="s">
-        <v>79</v>
+        <v>313</v>
       </c>
       <c r="L48" s="11"/>
       <c r="M48" s="11">
@@ -4146,10 +4204,10 @@
         <v>20301</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>133</v>
+        <v>248</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>134</v>
+        <v>69</v>
       </c>
       <c r="F49" s="8">
         <v>20302</v>
@@ -4163,14 +4221,14 @@
       <c r="I49" s="11">
         <v>1</v>
       </c>
-      <c r="J49" s="12" t="s">
-        <v>78</v>
+      <c r="J49" s="12">
+        <v>2000000</v>
       </c>
       <c r="K49" s="11" t="s">
-        <v>80</v>
+        <v>332</v>
       </c>
       <c r="L49" s="11" t="s">
-        <v>249</v>
+        <v>146</v>
       </c>
       <c r="M49" s="11">
         <v>0</v>
@@ -4182,10 +4240,10 @@
         <v>20302</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>135</v>
+        <v>249</v>
       </c>
       <c r="E50" s="10" t="s">
-        <v>136</v>
+        <v>70</v>
       </c>
       <c r="F50" s="8">
         <v>20303</v>
@@ -4199,14 +4257,14 @@
       <c r="I50" s="11">
         <v>1</v>
       </c>
-      <c r="J50" s="12" t="s">
-        <v>78</v>
+      <c r="J50" s="12">
+        <v>3000000</v>
       </c>
       <c r="K50" s="11" t="s">
-        <v>81</v>
+        <v>314</v>
       </c>
       <c r="L50" s="11" t="s">
-        <v>250</v>
+        <v>147</v>
       </c>
       <c r="M50" s="11">
         <v>0</v>
@@ -4218,10 +4276,10 @@
         <v>20303</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>137</v>
+        <v>250</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>138</v>
+        <v>71</v>
       </c>
       <c r="F51" s="8">
         <v>20304</v>
@@ -4235,14 +4293,14 @@
       <c r="I51" s="11">
         <v>1</v>
       </c>
-      <c r="J51" s="12" t="s">
-        <v>78</v>
+      <c r="J51" s="12">
+        <v>4000000</v>
       </c>
       <c r="K51" s="11" t="s">
-        <v>82</v>
+        <v>315</v>
       </c>
       <c r="L51" s="11" t="s">
-        <v>251</v>
+        <v>148</v>
       </c>
       <c r="M51" s="11">
         <v>0</v>
@@ -4254,10 +4312,10 @@
         <v>20304</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>139</v>
+        <v>251</v>
       </c>
       <c r="E52" s="10" t="s">
-        <v>140</v>
+        <v>72</v>
       </c>
       <c r="F52" s="8">
         <v>20305</v>
@@ -4271,14 +4329,14 @@
       <c r="I52" s="11">
         <v>1</v>
       </c>
-      <c r="J52" s="12" t="s">
-        <v>78</v>
+      <c r="J52" s="12">
+        <v>5000000</v>
       </c>
       <c r="K52" s="11" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="L52" s="11" t="s">
-        <v>252</v>
+        <v>149</v>
       </c>
       <c r="M52" s="11">
         <v>0</v>
@@ -4290,10 +4348,10 @@
         <v>20305</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>141</v>
+        <v>252</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>142</v>
+        <v>73</v>
       </c>
       <c r="F53" s="8">
         <v>20306</v>
@@ -4307,14 +4365,14 @@
       <c r="I53" s="11">
         <v>1</v>
       </c>
-      <c r="J53" s="12" t="s">
-        <v>78</v>
+      <c r="J53" s="12">
+        <v>6000000</v>
       </c>
       <c r="K53" s="11" t="s">
-        <v>83</v>
+        <v>317</v>
       </c>
       <c r="L53" s="11" t="s">
-        <v>253</v>
+        <v>150</v>
       </c>
       <c r="M53" s="11">
         <v>0</v>
@@ -4326,10 +4384,10 @@
         <v>20306</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>143</v>
+        <v>253</v>
       </c>
       <c r="E54" s="10" t="s">
-        <v>144</v>
+        <v>74</v>
       </c>
       <c r="F54" s="8">
         <v>20307</v>
@@ -4343,14 +4401,14 @@
       <c r="I54" s="11">
         <v>1</v>
       </c>
-      <c r="J54" s="12" t="s">
-        <v>78</v>
+      <c r="J54" s="12">
+        <v>7000000</v>
       </c>
       <c r="K54" s="11" t="s">
-        <v>84</v>
+        <v>318</v>
       </c>
       <c r="L54" s="11" t="s">
-        <v>254</v>
+        <v>151</v>
       </c>
       <c r="M54" s="11">
         <v>0</v>
@@ -4362,10 +4420,10 @@
         <v>20307</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>145</v>
+        <v>254</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>146</v>
+        <v>75</v>
       </c>
       <c r="F55" s="8">
         <v>20308</v>
@@ -4379,14 +4437,14 @@
       <c r="I55" s="11">
         <v>1</v>
       </c>
-      <c r="J55" s="12" t="s">
-        <v>78</v>
+      <c r="J55" s="12">
+        <v>8000000</v>
       </c>
       <c r="K55" s="11" t="s">
-        <v>85</v>
+        <v>319</v>
       </c>
       <c r="L55" s="11" t="s">
-        <v>255</v>
+        <v>152</v>
       </c>
       <c r="M55" s="11">
         <v>0</v>
@@ -4398,10 +4456,10 @@
         <v>20308</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>147</v>
+        <v>255</v>
       </c>
       <c r="E56" s="10" t="s">
-        <v>148</v>
+        <v>76</v>
       </c>
       <c r="F56" s="8">
         <v>20309</v>
@@ -4415,14 +4473,14 @@
       <c r="I56" s="11">
         <v>1</v>
       </c>
-      <c r="J56" s="12" t="s">
-        <v>78</v>
+      <c r="J56" s="12">
+        <v>9000000</v>
       </c>
       <c r="K56" s="11" t="s">
-        <v>86</v>
+        <v>320</v>
       </c>
       <c r="L56" s="11" t="s">
-        <v>256</v>
+        <v>153</v>
       </c>
       <c r="M56" s="11">
         <v>0</v>
@@ -4434,10 +4492,10 @@
         <v>20309</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>149</v>
+        <v>256</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>150</v>
+        <v>77</v>
       </c>
       <c r="F57" s="8">
         <v>20310</v>
@@ -4451,14 +4509,14 @@
       <c r="I57" s="11">
         <v>1</v>
       </c>
-      <c r="J57" s="12" t="s">
-        <v>78</v>
+      <c r="J57" s="12">
+        <v>10000000</v>
       </c>
       <c r="K57" s="11" t="s">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="L57" s="11" t="s">
-        <v>257</v>
+        <v>154</v>
       </c>
       <c r="M57" s="11">
         <v>0</v>
@@ -4470,10 +4528,10 @@
         <v>20310</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>151</v>
+        <v>257</v>
       </c>
       <c r="E58" s="10" t="s">
-        <v>152</v>
+        <v>78</v>
       </c>
       <c r="F58" s="8">
         <v>20311</v>
@@ -4487,14 +4545,14 @@
       <c r="I58" s="11">
         <v>1</v>
       </c>
-      <c r="J58" s="12" t="s">
-        <v>78</v>
+      <c r="J58" s="12">
+        <v>12000000</v>
       </c>
       <c r="K58" s="11" t="s">
-        <v>87</v>
+        <v>322</v>
       </c>
       <c r="L58" s="11" t="s">
-        <v>258</v>
+        <v>155</v>
       </c>
       <c r="M58" s="11">
         <v>0</v>
@@ -4506,10 +4564,10 @@
         <v>20311</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>153</v>
+        <v>258</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>154</v>
+        <v>79</v>
       </c>
       <c r="F59" s="8">
         <v>20312</v>
@@ -4523,14 +4581,14 @@
       <c r="I59" s="11">
         <v>1</v>
       </c>
-      <c r="J59" s="12" t="s">
-        <v>78</v>
+      <c r="J59" s="12">
+        <v>14000000</v>
       </c>
       <c r="K59" s="11" t="s">
-        <v>88</v>
+        <v>323</v>
       </c>
       <c r="L59" s="11" t="s">
-        <v>259</v>
+        <v>156</v>
       </c>
       <c r="M59" s="11">
         <v>0</v>
@@ -4542,10 +4600,10 @@
         <v>20312</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>155</v>
+        <v>259</v>
       </c>
       <c r="E60" s="10" t="s">
-        <v>156</v>
+        <v>80</v>
       </c>
       <c r="F60" s="8">
         <v>20313</v>
@@ -4559,14 +4617,14 @@
       <c r="I60" s="11">
         <v>1</v>
       </c>
-      <c r="J60" s="12" t="s">
-        <v>78</v>
+      <c r="J60" s="12">
+        <v>16000000</v>
       </c>
       <c r="K60" s="11" t="s">
-        <v>89</v>
+        <v>324</v>
       </c>
       <c r="L60" s="11" t="s">
-        <v>260</v>
+        <v>157</v>
       </c>
       <c r="M60" s="11">
         <v>0</v>
@@ -4578,10 +4636,10 @@
         <v>20313</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>157</v>
+        <v>260</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>158</v>
+        <v>81</v>
       </c>
       <c r="F61" s="8">
         <v>20314</v>
@@ -4595,14 +4653,14 @@
       <c r="I61" s="11">
         <v>1</v>
       </c>
-      <c r="J61" s="12" t="s">
-        <v>78</v>
+      <c r="J61" s="12">
+        <v>18000000</v>
       </c>
       <c r="K61" s="11" t="s">
-        <v>90</v>
+        <v>325</v>
       </c>
       <c r="L61" s="11" t="s">
-        <v>261</v>
+        <v>158</v>
       </c>
       <c r="M61" s="11">
         <v>0</v>
@@ -4614,10 +4672,10 @@
         <v>20314</v>
       </c>
       <c r="D62" s="9" t="s">
-        <v>159</v>
+        <v>261</v>
       </c>
       <c r="E62" s="10" t="s">
-        <v>160</v>
+        <v>82</v>
       </c>
       <c r="F62" s="8">
         <v>20315</v>
@@ -4631,14 +4689,14 @@
       <c r="I62" s="11">
         <v>1</v>
       </c>
-      <c r="J62" s="12" t="s">
-        <v>78</v>
+      <c r="J62" s="12">
+        <v>20000000</v>
       </c>
       <c r="K62" s="11" t="s">
-        <v>311</v>
+        <v>326</v>
       </c>
       <c r="L62" s="11" t="s">
-        <v>262</v>
+        <v>159</v>
       </c>
       <c r="M62" s="11">
         <v>0</v>
@@ -4650,10 +4708,10 @@
         <v>20315</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>161</v>
+        <v>262</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>162</v>
+        <v>83</v>
       </c>
       <c r="F63" s="8">
         <v>20316</v>
@@ -4667,14 +4725,14 @@
       <c r="I63" s="11">
         <v>1</v>
       </c>
-      <c r="J63" s="12" t="s">
-        <v>78</v>
+      <c r="J63" s="12">
+        <v>22000000</v>
       </c>
       <c r="K63" s="11" t="s">
-        <v>91</v>
+        <v>327</v>
       </c>
       <c r="L63" s="11" t="s">
-        <v>263</v>
+        <v>160</v>
       </c>
       <c r="M63" s="11">
         <v>0</v>
@@ -4686,10 +4744,10 @@
         <v>20316</v>
       </c>
       <c r="D64" s="9" t="s">
-        <v>163</v>
+        <v>263</v>
       </c>
       <c r="E64" s="10" t="s">
-        <v>164</v>
+        <v>84</v>
       </c>
       <c r="F64" s="8">
         <v>20317</v>
@@ -4703,14 +4761,14 @@
       <c r="I64" s="11">
         <v>1</v>
       </c>
-      <c r="J64" s="12" t="s">
-        <v>78</v>
+      <c r="J64" s="12">
+        <v>24000000</v>
       </c>
       <c r="K64" s="11" t="s">
-        <v>92</v>
+        <v>328</v>
       </c>
       <c r="L64" s="11" t="s">
-        <v>264</v>
+        <v>161</v>
       </c>
       <c r="M64" s="11">
         <v>0</v>
@@ -4722,10 +4780,10 @@
         <v>20317</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>165</v>
+        <v>264</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>166</v>
+        <v>85</v>
       </c>
       <c r="F65" s="8">
         <v>20318</v>
@@ -4739,14 +4797,14 @@
       <c r="I65" s="11">
         <v>1</v>
       </c>
-      <c r="J65" s="12" t="s">
-        <v>78</v>
+      <c r="J65" s="12">
+        <v>26000000</v>
       </c>
       <c r="K65" s="11" t="s">
-        <v>93</v>
+        <v>329</v>
       </c>
       <c r="L65" s="11" t="s">
-        <v>265</v>
+        <v>162</v>
       </c>
       <c r="M65" s="11">
         <v>0</v>
@@ -4758,10 +4816,10 @@
         <v>20318</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>167</v>
+        <v>265</v>
       </c>
       <c r="E66" s="10" t="s">
-        <v>168</v>
+        <v>86</v>
       </c>
       <c r="F66" s="8">
         <v>20319</v>
@@ -4775,14 +4833,14 @@
       <c r="I66" s="11">
         <v>1</v>
       </c>
-      <c r="J66" s="12" t="s">
-        <v>78</v>
+      <c r="J66" s="12">
+        <v>28000000</v>
       </c>
       <c r="K66" s="11" t="s">
-        <v>94</v>
+        <v>330</v>
       </c>
       <c r="L66" s="11" t="s">
-        <v>266</v>
+        <v>163</v>
       </c>
       <c r="M66" s="11">
         <v>0</v>
@@ -4794,10 +4852,10 @@
         <v>20319</v>
       </c>
       <c r="D67" s="9" t="s">
-        <v>169</v>
+        <v>266</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>170</v>
+        <v>87</v>
       </c>
       <c r="F67" s="8">
         <v>20320</v>
@@ -4811,14 +4869,14 @@
       <c r="I67" s="11">
         <v>1</v>
       </c>
-      <c r="J67" s="12" t="s">
-        <v>78</v>
+      <c r="J67" s="12">
+        <v>30000000</v>
       </c>
       <c r="K67" s="11" t="s">
-        <v>312</v>
+        <v>331</v>
       </c>
       <c r="L67" s="11" t="s">
-        <v>267</v>
+        <v>164</v>
       </c>
       <c r="M67" s="11">
         <v>0</v>
@@ -4830,10 +4888,10 @@
         <v>20320</v>
       </c>
       <c r="D68" s="9" t="s">
-        <v>34</v>
+        <v>267</v>
       </c>
       <c r="E68" s="10" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="F68" s="8">
         <v>0</v>
@@ -4847,14 +4905,14 @@
       <c r="I68" s="11">
         <v>1</v>
       </c>
-      <c r="J68" s="12" t="s">
-        <v>78</v>
+      <c r="J68" s="12">
+        <v>30000000</v>
       </c>
       <c r="K68" s="11" t="s">
-        <v>312</v>
+        <v>331</v>
       </c>
       <c r="L68" s="11" t="s">
-        <v>268</v>
+        <v>165</v>
       </c>
       <c r="M68" s="11">
         <v>0</v>
@@ -4866,10 +4924,10 @@
         <v>20400</v>
       </c>
       <c r="D69" s="9" t="s">
-        <v>36</v>
+        <v>268</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="F69" s="8">
         <v>20401</v>
@@ -4883,11 +4941,11 @@
       <c r="I69" s="11">
         <v>1</v>
       </c>
-      <c r="J69" s="12" t="s">
-        <v>78</v>
+      <c r="J69" s="12">
+        <v>1000000</v>
       </c>
       <c r="K69" s="11" t="s">
-        <v>79</v>
+        <v>313</v>
       </c>
       <c r="L69" s="11"/>
       <c r="M69" s="11">
@@ -4899,10 +4957,10 @@
         <v>20401</v>
       </c>
       <c r="D70" s="9" t="s">
-        <v>171</v>
+        <v>269</v>
       </c>
       <c r="E70" s="10" t="s">
-        <v>172</v>
+        <v>88</v>
       </c>
       <c r="F70" s="8">
         <v>20402</v>
@@ -4916,14 +4974,14 @@
       <c r="I70" s="11">
         <v>1</v>
       </c>
-      <c r="J70" s="12" t="s">
-        <v>78</v>
+      <c r="J70" s="12">
+        <v>2000000</v>
       </c>
       <c r="K70" s="11" t="s">
-        <v>80</v>
+        <v>332</v>
       </c>
       <c r="L70" s="11" t="s">
-        <v>269</v>
+        <v>311</v>
       </c>
       <c r="M70" s="11">
         <v>0</v>
@@ -4935,10 +4993,10 @@
         <v>20402</v>
       </c>
       <c r="D71" s="9" t="s">
-        <v>173</v>
+        <v>270</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>174</v>
+        <v>89</v>
       </c>
       <c r="F71" s="8">
         <v>20403</v>
@@ -4952,14 +5010,14 @@
       <c r="I71" s="11">
         <v>1</v>
       </c>
-      <c r="J71" s="12" t="s">
-        <v>78</v>
+      <c r="J71" s="12">
+        <v>3000000</v>
       </c>
       <c r="K71" s="11" t="s">
-        <v>81</v>
+        <v>314</v>
       </c>
       <c r="L71" s="11" t="s">
-        <v>270</v>
+        <v>166</v>
       </c>
       <c r="M71" s="11">
         <v>0</v>
@@ -4971,10 +5029,10 @@
         <v>20403</v>
       </c>
       <c r="D72" s="9" t="s">
-        <v>175</v>
+        <v>271</v>
       </c>
       <c r="E72" s="10" t="s">
-        <v>176</v>
+        <v>90</v>
       </c>
       <c r="F72" s="8">
         <v>20404</v>
@@ -4988,14 +5046,14 @@
       <c r="I72" s="11">
         <v>1</v>
       </c>
-      <c r="J72" s="12" t="s">
-        <v>78</v>
+      <c r="J72" s="12">
+        <v>4000000</v>
       </c>
       <c r="K72" s="11" t="s">
-        <v>82</v>
+        <v>315</v>
       </c>
       <c r="L72" s="11" t="s">
-        <v>271</v>
+        <v>167</v>
       </c>
       <c r="M72" s="11">
         <v>0</v>
@@ -5007,10 +5065,10 @@
         <v>20404</v>
       </c>
       <c r="D73" s="9" t="s">
-        <v>177</v>
+        <v>272</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>178</v>
+        <v>91</v>
       </c>
       <c r="F73" s="8">
         <v>20405</v>
@@ -5024,14 +5082,14 @@
       <c r="I73" s="11">
         <v>1</v>
       </c>
-      <c r="J73" s="12" t="s">
-        <v>78</v>
+      <c r="J73" s="12">
+        <v>5000000</v>
       </c>
       <c r="K73" s="11" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="L73" s="11" t="s">
-        <v>272</v>
+        <v>168</v>
       </c>
       <c r="M73" s="11">
         <v>0</v>
@@ -5043,10 +5101,10 @@
         <v>20405</v>
       </c>
       <c r="D74" s="9" t="s">
-        <v>179</v>
+        <v>273</v>
       </c>
       <c r="E74" s="10" t="s">
-        <v>180</v>
+        <v>92</v>
       </c>
       <c r="F74" s="8">
         <v>20406</v>
@@ -5060,14 +5118,14 @@
       <c r="I74" s="11">
         <v>1</v>
       </c>
-      <c r="J74" s="12" t="s">
-        <v>78</v>
+      <c r="J74" s="12">
+        <v>6000000</v>
       </c>
       <c r="K74" s="11" t="s">
-        <v>83</v>
+        <v>317</v>
       </c>
       <c r="L74" s="11" t="s">
-        <v>273</v>
+        <v>169</v>
       </c>
       <c r="M74" s="11">
         <v>0</v>
@@ -5079,10 +5137,10 @@
         <v>20406</v>
       </c>
       <c r="D75" s="9" t="s">
-        <v>181</v>
+        <v>274</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>182</v>
+        <v>93</v>
       </c>
       <c r="F75" s="8">
         <v>20407</v>
@@ -5096,14 +5154,14 @@
       <c r="I75" s="11">
         <v>1</v>
       </c>
-      <c r="J75" s="12" t="s">
-        <v>78</v>
+      <c r="J75" s="12">
+        <v>7000000</v>
       </c>
       <c r="K75" s="11" t="s">
-        <v>84</v>
+        <v>318</v>
       </c>
       <c r="L75" s="11" t="s">
-        <v>274</v>
+        <v>170</v>
       </c>
       <c r="M75" s="11">
         <v>0</v>
@@ -5115,10 +5173,10 @@
         <v>20407</v>
       </c>
       <c r="D76" s="9" t="s">
-        <v>183</v>
+        <v>275</v>
       </c>
       <c r="E76" s="10" t="s">
-        <v>184</v>
+        <v>94</v>
       </c>
       <c r="F76" s="8">
         <v>20408</v>
@@ -5132,14 +5190,14 @@
       <c r="I76" s="11">
         <v>1</v>
       </c>
-      <c r="J76" s="12" t="s">
-        <v>78</v>
+      <c r="J76" s="12">
+        <v>8000000</v>
       </c>
       <c r="K76" s="11" t="s">
-        <v>85</v>
+        <v>319</v>
       </c>
       <c r="L76" s="11" t="s">
-        <v>275</v>
+        <v>171</v>
       </c>
       <c r="M76" s="11">
         <v>0</v>
@@ -5151,10 +5209,10 @@
         <v>20408</v>
       </c>
       <c r="D77" s="9" t="s">
-        <v>185</v>
+        <v>276</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>186</v>
+        <v>95</v>
       </c>
       <c r="F77" s="8">
         <v>20409</v>
@@ -5168,14 +5226,14 @@
       <c r="I77" s="11">
         <v>1</v>
       </c>
-      <c r="J77" s="12" t="s">
-        <v>78</v>
+      <c r="J77" s="12">
+        <v>9000000</v>
       </c>
       <c r="K77" s="11" t="s">
-        <v>86</v>
+        <v>320</v>
       </c>
       <c r="L77" s="11" t="s">
-        <v>276</v>
+        <v>172</v>
       </c>
       <c r="M77" s="11">
         <v>0</v>
@@ -5187,10 +5245,10 @@
         <v>20409</v>
       </c>
       <c r="D78" s="9" t="s">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="E78" s="10" t="s">
-        <v>188</v>
+        <v>96</v>
       </c>
       <c r="F78" s="8">
         <v>20410</v>
@@ -5204,14 +5262,14 @@
       <c r="I78" s="11">
         <v>1</v>
       </c>
-      <c r="J78" s="12" t="s">
-        <v>78</v>
+      <c r="J78" s="12">
+        <v>10000000</v>
       </c>
       <c r="K78" s="11" t="s">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="L78" s="11" t="s">
-        <v>277</v>
+        <v>173</v>
       </c>
       <c r="M78" s="11">
         <v>0</v>
@@ -5223,10 +5281,10 @@
         <v>20410</v>
       </c>
       <c r="D79" s="9" t="s">
-        <v>189</v>
+        <v>278</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>190</v>
+        <v>97</v>
       </c>
       <c r="F79" s="8">
         <v>20411</v>
@@ -5240,14 +5298,14 @@
       <c r="I79" s="11">
         <v>1</v>
       </c>
-      <c r="J79" s="12" t="s">
-        <v>78</v>
+      <c r="J79" s="12">
+        <v>12000000</v>
       </c>
       <c r="K79" s="11" t="s">
-        <v>87</v>
+        <v>322</v>
       </c>
       <c r="L79" s="11" t="s">
-        <v>278</v>
+        <v>174</v>
       </c>
       <c r="M79" s="11">
         <v>0</v>
@@ -5259,10 +5317,10 @@
         <v>20411</v>
       </c>
       <c r="D80" s="9" t="s">
-        <v>191</v>
+        <v>279</v>
       </c>
       <c r="E80" s="10" t="s">
-        <v>192</v>
+        <v>98</v>
       </c>
       <c r="F80" s="8">
         <v>20412</v>
@@ -5276,14 +5334,14 @@
       <c r="I80" s="11">
         <v>1</v>
       </c>
-      <c r="J80" s="12" t="s">
-        <v>78</v>
+      <c r="J80" s="12">
+        <v>14000000</v>
       </c>
       <c r="K80" s="11" t="s">
-        <v>88</v>
+        <v>323</v>
       </c>
       <c r="L80" s="11" t="s">
-        <v>279</v>
+        <v>175</v>
       </c>
       <c r="M80" s="11">
         <v>0</v>
@@ -5295,10 +5353,10 @@
         <v>20412</v>
       </c>
       <c r="D81" s="9" t="s">
-        <v>193</v>
+        <v>280</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>194</v>
+        <v>99</v>
       </c>
       <c r="F81" s="8">
         <v>20413</v>
@@ -5312,14 +5370,14 @@
       <c r="I81" s="11">
         <v>1</v>
       </c>
-      <c r="J81" s="12" t="s">
-        <v>78</v>
+      <c r="J81" s="12">
+        <v>16000000</v>
       </c>
       <c r="K81" s="11" t="s">
-        <v>89</v>
+        <v>324</v>
       </c>
       <c r="L81" s="11" t="s">
-        <v>280</v>
+        <v>176</v>
       </c>
       <c r="M81" s="11">
         <v>0</v>
@@ -5331,10 +5389,10 @@
         <v>20413</v>
       </c>
       <c r="D82" s="9" t="s">
-        <v>195</v>
+        <v>281</v>
       </c>
       <c r="E82" s="10" t="s">
-        <v>196</v>
+        <v>100</v>
       </c>
       <c r="F82" s="8">
         <v>20414</v>
@@ -5348,14 +5406,14 @@
       <c r="I82" s="11">
         <v>1</v>
       </c>
-      <c r="J82" s="12" t="s">
-        <v>78</v>
+      <c r="J82" s="12">
+        <v>18000000</v>
       </c>
       <c r="K82" s="11" t="s">
-        <v>90</v>
+        <v>325</v>
       </c>
       <c r="L82" s="11" t="s">
-        <v>281</v>
+        <v>177</v>
       </c>
       <c r="M82" s="11">
         <v>0</v>
@@ -5367,10 +5425,10 @@
         <v>20414</v>
       </c>
       <c r="D83" s="9" t="s">
-        <v>197</v>
+        <v>282</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>198</v>
+        <v>101</v>
       </c>
       <c r="F83" s="8">
         <v>20415</v>
@@ -5384,14 +5442,14 @@
       <c r="I83" s="11">
         <v>1</v>
       </c>
-      <c r="J83" s="12" t="s">
-        <v>78</v>
+      <c r="J83" s="12">
+        <v>20000000</v>
       </c>
       <c r="K83" s="11" t="s">
-        <v>311</v>
+        <v>326</v>
       </c>
       <c r="L83" s="11" t="s">
-        <v>282</v>
+        <v>178</v>
       </c>
       <c r="M83" s="11">
         <v>0</v>
@@ -5403,10 +5461,10 @@
         <v>20415</v>
       </c>
       <c r="D84" s="9" t="s">
-        <v>199</v>
+        <v>283</v>
       </c>
       <c r="E84" s="10" t="s">
-        <v>200</v>
+        <v>102</v>
       </c>
       <c r="F84" s="8">
         <v>20416</v>
@@ -5420,14 +5478,14 @@
       <c r="I84" s="11">
         <v>1</v>
       </c>
-      <c r="J84" s="12" t="s">
-        <v>78</v>
+      <c r="J84" s="12">
+        <v>22000000</v>
       </c>
       <c r="K84" s="11" t="s">
-        <v>91</v>
+        <v>327</v>
       </c>
       <c r="L84" s="11" t="s">
-        <v>283</v>
+        <v>179</v>
       </c>
       <c r="M84" s="11">
         <v>0</v>
@@ -5439,10 +5497,10 @@
         <v>20416</v>
       </c>
       <c r="D85" s="9" t="s">
-        <v>201</v>
+        <v>284</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>202</v>
+        <v>103</v>
       </c>
       <c r="F85" s="8">
         <v>20417</v>
@@ -5456,14 +5514,14 @@
       <c r="I85" s="11">
         <v>1</v>
       </c>
-      <c r="J85" s="12" t="s">
-        <v>78</v>
+      <c r="J85" s="12">
+        <v>24000000</v>
       </c>
       <c r="K85" s="11" t="s">
-        <v>92</v>
+        <v>328</v>
       </c>
       <c r="L85" s="11" t="s">
-        <v>284</v>
+        <v>180</v>
       </c>
       <c r="M85" s="11">
         <v>0</v>
@@ -5475,10 +5533,10 @@
         <v>20417</v>
       </c>
       <c r="D86" s="9" t="s">
-        <v>203</v>
+        <v>285</v>
       </c>
       <c r="E86" s="10" t="s">
-        <v>204</v>
+        <v>104</v>
       </c>
       <c r="F86" s="8">
         <v>20418</v>
@@ -5492,14 +5550,14 @@
       <c r="I86" s="11">
         <v>1</v>
       </c>
-      <c r="J86" s="12" t="s">
-        <v>78</v>
+      <c r="J86" s="12">
+        <v>26000000</v>
       </c>
       <c r="K86" s="11" t="s">
-        <v>93</v>
+        <v>329</v>
       </c>
       <c r="L86" s="11" t="s">
-        <v>285</v>
+        <v>181</v>
       </c>
       <c r="M86" s="11">
         <v>0</v>
@@ -5511,10 +5569,10 @@
         <v>20418</v>
       </c>
       <c r="D87" s="9" t="s">
-        <v>205</v>
+        <v>286</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>206</v>
+        <v>105</v>
       </c>
       <c r="F87" s="8">
         <v>20419</v>
@@ -5528,14 +5586,14 @@
       <c r="I87" s="11">
         <v>1</v>
       </c>
-      <c r="J87" s="12" t="s">
-        <v>78</v>
+      <c r="J87" s="12">
+        <v>28000000</v>
       </c>
       <c r="K87" s="11" t="s">
-        <v>94</v>
+        <v>330</v>
       </c>
       <c r="L87" s="11" t="s">
-        <v>286</v>
+        <v>182</v>
       </c>
       <c r="M87" s="11">
         <v>0</v>
@@ -5547,10 +5605,10 @@
         <v>20419</v>
       </c>
       <c r="D88" s="9" t="s">
-        <v>207</v>
+        <v>287</v>
       </c>
       <c r="E88" s="10" t="s">
-        <v>208</v>
+        <v>106</v>
       </c>
       <c r="F88" s="8">
         <v>20420</v>
@@ -5564,14 +5622,14 @@
       <c r="I88" s="11">
         <v>1</v>
       </c>
-      <c r="J88" s="12" t="s">
-        <v>78</v>
+      <c r="J88" s="12">
+        <v>30000000</v>
       </c>
       <c r="K88" s="11" t="s">
-        <v>312</v>
+        <v>331</v>
       </c>
       <c r="L88" s="11" t="s">
-        <v>287</v>
+        <v>183</v>
       </c>
       <c r="M88" s="11">
         <v>0</v>
@@ -5583,10 +5641,10 @@
         <v>20420</v>
       </c>
       <c r="D89" s="9" t="s">
-        <v>38</v>
+        <v>288</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="F89" s="8">
         <v>0</v>
@@ -5600,14 +5658,14 @@
       <c r="I89" s="11">
         <v>1</v>
       </c>
-      <c r="J89" s="12" t="s">
-        <v>78</v>
+      <c r="J89" s="12">
+        <v>30000000</v>
       </c>
       <c r="K89" s="11" t="s">
-        <v>312</v>
+        <v>331</v>
       </c>
       <c r="L89" s="11" t="s">
-        <v>288</v>
+        <v>184</v>
       </c>
       <c r="M89" s="11">
         <v>0</v>
@@ -5619,10 +5677,10 @@
         <v>20500</v>
       </c>
       <c r="D90" s="9" t="s">
-        <v>36</v>
+        <v>289</v>
       </c>
       <c r="E90" s="10" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="F90" s="8">
         <v>20501</v>
@@ -5636,11 +5694,11 @@
       <c r="I90" s="11">
         <v>1</v>
       </c>
-      <c r="J90" s="12" t="s">
-        <v>78</v>
+      <c r="J90" s="12">
+        <v>1000000</v>
       </c>
       <c r="K90" s="11" t="s">
-        <v>79</v>
+        <v>313</v>
       </c>
       <c r="L90" s="11"/>
       <c r="M90" s="11">
@@ -5652,10 +5710,10 @@
         <v>20501</v>
       </c>
       <c r="D91" s="9" t="s">
-        <v>171</v>
+        <v>290</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>172</v>
+        <v>88</v>
       </c>
       <c r="F91" s="8">
         <v>20502</v>
@@ -5669,14 +5727,14 @@
       <c r="I91" s="11">
         <v>1</v>
       </c>
-      <c r="J91" s="12" t="s">
-        <v>78</v>
+      <c r="J91" s="12">
+        <v>2000000</v>
       </c>
       <c r="K91" s="11" t="s">
-        <v>80</v>
+        <v>332</v>
       </c>
       <c r="L91" s="11" t="s">
-        <v>289</v>
+        <v>185</v>
       </c>
       <c r="M91" s="11">
         <v>0</v>
@@ -5688,10 +5746,10 @@
         <v>20502</v>
       </c>
       <c r="D92" s="9" t="s">
-        <v>173</v>
+        <v>291</v>
       </c>
       <c r="E92" s="10" t="s">
-        <v>174</v>
+        <v>89</v>
       </c>
       <c r="F92" s="8">
         <v>20503</v>
@@ -5705,14 +5763,14 @@
       <c r="I92" s="11">
         <v>1</v>
       </c>
-      <c r="J92" s="12" t="s">
-        <v>78</v>
+      <c r="J92" s="12">
+        <v>3000000</v>
       </c>
       <c r="K92" s="11" t="s">
-        <v>81</v>
+        <v>314</v>
       </c>
       <c r="L92" s="11" t="s">
-        <v>290</v>
+        <v>186</v>
       </c>
       <c r="M92" s="11">
         <v>0</v>
@@ -5724,10 +5782,10 @@
         <v>20503</v>
       </c>
       <c r="D93" s="9" t="s">
-        <v>175</v>
+        <v>292</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>176</v>
+        <v>90</v>
       </c>
       <c r="F93" s="8">
         <v>20504</v>
@@ -5741,14 +5799,14 @@
       <c r="I93" s="11">
         <v>1</v>
       </c>
-      <c r="J93" s="12" t="s">
-        <v>78</v>
+      <c r="J93" s="12">
+        <v>4000000</v>
       </c>
       <c r="K93" s="11" t="s">
-        <v>82</v>
+        <v>315</v>
       </c>
       <c r="L93" s="11" t="s">
-        <v>291</v>
+        <v>187</v>
       </c>
       <c r="M93" s="11">
         <v>0</v>
@@ -5760,10 +5818,10 @@
         <v>20504</v>
       </c>
       <c r="D94" s="9" t="s">
-        <v>177</v>
+        <v>293</v>
       </c>
       <c r="E94" s="10" t="s">
-        <v>178</v>
+        <v>91</v>
       </c>
       <c r="F94" s="8">
         <v>20505</v>
@@ -5777,14 +5835,14 @@
       <c r="I94" s="11">
         <v>1</v>
       </c>
-      <c r="J94" s="12" t="s">
-        <v>78</v>
+      <c r="J94" s="12">
+        <v>5000000</v>
       </c>
       <c r="K94" s="11" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="L94" s="11" t="s">
-        <v>292</v>
+        <v>188</v>
       </c>
       <c r="M94" s="11">
         <v>0</v>
@@ -5796,10 +5854,10 @@
         <v>20505</v>
       </c>
       <c r="D95" s="9" t="s">
-        <v>179</v>
+        <v>294</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>180</v>
+        <v>92</v>
       </c>
       <c r="F95" s="8">
         <v>20506</v>
@@ -5813,14 +5871,14 @@
       <c r="I95" s="11">
         <v>1</v>
       </c>
-      <c r="J95" s="12" t="s">
-        <v>78</v>
+      <c r="J95" s="12">
+        <v>6000000</v>
       </c>
       <c r="K95" s="11" t="s">
-        <v>83</v>
+        <v>317</v>
       </c>
       <c r="L95" s="11" t="s">
-        <v>293</v>
+        <v>189</v>
       </c>
       <c r="M95" s="11">
         <v>0</v>
@@ -5832,10 +5890,10 @@
         <v>20506</v>
       </c>
       <c r="D96" s="9" t="s">
-        <v>181</v>
+        <v>295</v>
       </c>
       <c r="E96" s="10" t="s">
-        <v>182</v>
+        <v>93</v>
       </c>
       <c r="F96" s="8">
         <v>20507</v>
@@ -5849,14 +5907,14 @@
       <c r="I96" s="11">
         <v>1</v>
       </c>
-      <c r="J96" s="12" t="s">
-        <v>78</v>
+      <c r="J96" s="12">
+        <v>7000000</v>
       </c>
       <c r="K96" s="11" t="s">
-        <v>84</v>
+        <v>318</v>
       </c>
       <c r="L96" s="11" t="s">
-        <v>294</v>
+        <v>190</v>
       </c>
       <c r="M96" s="11">
         <v>0</v>
@@ -5868,10 +5926,10 @@
         <v>20507</v>
       </c>
       <c r="D97" s="9" t="s">
-        <v>183</v>
+        <v>296</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>184</v>
+        <v>94</v>
       </c>
       <c r="F97" s="8">
         <v>20508</v>
@@ -5885,14 +5943,14 @@
       <c r="I97" s="11">
         <v>1</v>
       </c>
-      <c r="J97" s="12" t="s">
-        <v>78</v>
+      <c r="J97" s="12">
+        <v>8000000</v>
       </c>
       <c r="K97" s="11" t="s">
-        <v>85</v>
+        <v>319</v>
       </c>
       <c r="L97" s="11" t="s">
-        <v>295</v>
+        <v>191</v>
       </c>
       <c r="M97" s="11">
         <v>0</v>
@@ -5904,10 +5962,10 @@
         <v>20508</v>
       </c>
       <c r="D98" s="9" t="s">
-        <v>185</v>
+        <v>297</v>
       </c>
       <c r="E98" s="10" t="s">
-        <v>186</v>
+        <v>95</v>
       </c>
       <c r="F98" s="8">
         <v>20509</v>
@@ -5921,14 +5979,14 @@
       <c r="I98" s="11">
         <v>1</v>
       </c>
-      <c r="J98" s="12" t="s">
-        <v>78</v>
+      <c r="J98" s="12">
+        <v>9000000</v>
       </c>
       <c r="K98" s="11" t="s">
-        <v>86</v>
+        <v>320</v>
       </c>
       <c r="L98" s="11" t="s">
-        <v>296</v>
+        <v>192</v>
       </c>
       <c r="M98" s="11">
         <v>0</v>
@@ -5940,10 +5998,10 @@
         <v>20509</v>
       </c>
       <c r="D99" s="9" t="s">
-        <v>187</v>
+        <v>298</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>188</v>
+        <v>96</v>
       </c>
       <c r="F99" s="8">
         <v>20510</v>
@@ -5957,14 +6015,14 @@
       <c r="I99" s="11">
         <v>1</v>
       </c>
-      <c r="J99" s="12" t="s">
-        <v>78</v>
+      <c r="J99" s="12">
+        <v>10000000</v>
       </c>
       <c r="K99" s="11" t="s">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="L99" s="11" t="s">
-        <v>297</v>
+        <v>193</v>
       </c>
       <c r="M99" s="11">
         <v>0</v>
@@ -5976,10 +6034,10 @@
         <v>20510</v>
       </c>
       <c r="D100" s="9" t="s">
-        <v>189</v>
+        <v>299</v>
       </c>
       <c r="E100" s="10" t="s">
-        <v>190</v>
+        <v>97</v>
       </c>
       <c r="F100" s="8">
         <v>20511</v>
@@ -5993,14 +6051,14 @@
       <c r="I100" s="11">
         <v>1</v>
       </c>
-      <c r="J100" s="12" t="s">
-        <v>78</v>
+      <c r="J100" s="12">
+        <v>12000000</v>
       </c>
       <c r="K100" s="11" t="s">
-        <v>87</v>
+        <v>322</v>
       </c>
       <c r="L100" s="11" t="s">
-        <v>298</v>
+        <v>194</v>
       </c>
       <c r="M100" s="11">
         <v>0</v>
@@ -6012,10 +6070,10 @@
         <v>20511</v>
       </c>
       <c r="D101" s="9" t="s">
-        <v>191</v>
+        <v>300</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>192</v>
+        <v>98</v>
       </c>
       <c r="F101" s="8">
         <v>20512</v>
@@ -6029,14 +6087,14 @@
       <c r="I101" s="11">
         <v>1</v>
       </c>
-      <c r="J101" s="12" t="s">
-        <v>78</v>
+      <c r="J101" s="12">
+        <v>14000000</v>
       </c>
       <c r="K101" s="11" t="s">
-        <v>88</v>
+        <v>323</v>
       </c>
       <c r="L101" s="11" t="s">
-        <v>299</v>
+        <v>195</v>
       </c>
       <c r="M101" s="11">
         <v>0</v>
@@ -6048,10 +6106,10 @@
         <v>20512</v>
       </c>
       <c r="D102" s="9" t="s">
-        <v>193</v>
+        <v>301</v>
       </c>
       <c r="E102" s="10" t="s">
-        <v>194</v>
+        <v>99</v>
       </c>
       <c r="F102" s="8">
         <v>20513</v>
@@ -6065,14 +6123,14 @@
       <c r="I102" s="11">
         <v>1</v>
       </c>
-      <c r="J102" s="12" t="s">
-        <v>78</v>
+      <c r="J102" s="12">
+        <v>16000000</v>
       </c>
       <c r="K102" s="11" t="s">
-        <v>89</v>
+        <v>324</v>
       </c>
       <c r="L102" s="11" t="s">
-        <v>300</v>
+        <v>196</v>
       </c>
       <c r="M102" s="11">
         <v>0</v>
@@ -6084,10 +6142,10 @@
         <v>20513</v>
       </c>
       <c r="D103" s="9" t="s">
-        <v>195</v>
+        <v>302</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>196</v>
+        <v>100</v>
       </c>
       <c r="F103" s="8">
         <v>20514</v>
@@ -6101,14 +6159,14 @@
       <c r="I103" s="11">
         <v>1</v>
       </c>
-      <c r="J103" s="12" t="s">
-        <v>78</v>
+      <c r="J103" s="12">
+        <v>18000000</v>
       </c>
       <c r="K103" s="11" t="s">
-        <v>90</v>
+        <v>325</v>
       </c>
       <c r="L103" s="11" t="s">
-        <v>301</v>
+        <v>197</v>
       </c>
       <c r="M103" s="11">
         <v>0</v>
@@ -6120,10 +6178,10 @@
         <v>20514</v>
       </c>
       <c r="D104" s="9" t="s">
-        <v>197</v>
+        <v>303</v>
       </c>
       <c r="E104" s="10" t="s">
-        <v>198</v>
+        <v>101</v>
       </c>
       <c r="F104" s="8">
         <v>20515</v>
@@ -6137,14 +6195,14 @@
       <c r="I104" s="11">
         <v>1</v>
       </c>
-      <c r="J104" s="12" t="s">
-        <v>78</v>
+      <c r="J104" s="12">
+        <v>20000000</v>
       </c>
       <c r="K104" s="11" t="s">
-        <v>311</v>
+        <v>326</v>
       </c>
       <c r="L104" s="11" t="s">
-        <v>302</v>
+        <v>198</v>
       </c>
       <c r="M104" s="11">
         <v>0</v>
@@ -6156,10 +6214,10 @@
         <v>20515</v>
       </c>
       <c r="D105" s="9" t="s">
-        <v>199</v>
+        <v>304</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>200</v>
+        <v>102</v>
       </c>
       <c r="F105" s="8">
         <v>20516</v>
@@ -6173,14 +6231,14 @@
       <c r="I105" s="11">
         <v>1</v>
       </c>
-      <c r="J105" s="12" t="s">
-        <v>78</v>
+      <c r="J105" s="12">
+        <v>22000000</v>
       </c>
       <c r="K105" s="11" t="s">
-        <v>91</v>
+        <v>327</v>
       </c>
       <c r="L105" s="11" t="s">
-        <v>303</v>
+        <v>199</v>
       </c>
       <c r="M105" s="11">
         <v>0</v>
@@ -6192,10 +6250,10 @@
         <v>20516</v>
       </c>
       <c r="D106" s="9" t="s">
-        <v>201</v>
+        <v>305</v>
       </c>
       <c r="E106" s="10" t="s">
-        <v>202</v>
+        <v>103</v>
       </c>
       <c r="F106" s="8">
         <v>20517</v>
@@ -6209,14 +6267,14 @@
       <c r="I106" s="11">
         <v>1</v>
       </c>
-      <c r="J106" s="12" t="s">
-        <v>78</v>
+      <c r="J106" s="12">
+        <v>24000000</v>
       </c>
       <c r="K106" s="11" t="s">
-        <v>92</v>
+        <v>328</v>
       </c>
       <c r="L106" s="11" t="s">
-        <v>304</v>
+        <v>200</v>
       </c>
       <c r="M106" s="11">
         <v>0</v>
@@ -6228,10 +6286,10 @@
         <v>20517</v>
       </c>
       <c r="D107" s="9" t="s">
-        <v>203</v>
+        <v>306</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>204</v>
+        <v>104</v>
       </c>
       <c r="F107" s="8">
         <v>20518</v>
@@ -6245,14 +6303,14 @@
       <c r="I107" s="11">
         <v>1</v>
       </c>
-      <c r="J107" s="12" t="s">
-        <v>78</v>
+      <c r="J107" s="12">
+        <v>26000000</v>
       </c>
       <c r="K107" s="11" t="s">
-        <v>93</v>
+        <v>329</v>
       </c>
       <c r="L107" s="11" t="s">
-        <v>305</v>
+        <v>201</v>
       </c>
       <c r="M107" s="11">
         <v>0</v>
@@ -6264,10 +6322,10 @@
         <v>20518</v>
       </c>
       <c r="D108" s="9" t="s">
-        <v>205</v>
+        <v>307</v>
       </c>
       <c r="E108" s="10" t="s">
-        <v>206</v>
+        <v>105</v>
       </c>
       <c r="F108" s="8">
         <v>20519</v>
@@ -6281,14 +6339,14 @@
       <c r="I108" s="11">
         <v>1</v>
       </c>
-      <c r="J108" s="12" t="s">
-        <v>78</v>
+      <c r="J108" s="12">
+        <v>28000000</v>
       </c>
       <c r="K108" s="11" t="s">
-        <v>94</v>
+        <v>330</v>
       </c>
       <c r="L108" s="11" t="s">
-        <v>306</v>
+        <v>202</v>
       </c>
       <c r="M108" s="11">
         <v>0</v>
@@ -6300,10 +6358,10 @@
         <v>20519</v>
       </c>
       <c r="D109" s="9" t="s">
-        <v>207</v>
+        <v>308</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>208</v>
+        <v>106</v>
       </c>
       <c r="F109" s="8">
         <v>20520</v>
@@ -6317,14 +6375,14 @@
       <c r="I109" s="11">
         <v>1</v>
       </c>
-      <c r="J109" s="12" t="s">
-        <v>78</v>
+      <c r="J109" s="12">
+        <v>30000000</v>
       </c>
       <c r="K109" s="11" t="s">
-        <v>312</v>
+        <v>331</v>
       </c>
       <c r="L109" s="11" t="s">
-        <v>307</v>
+        <v>203</v>
       </c>
       <c r="M109" s="11">
         <v>0</v>
@@ -6336,10 +6394,10 @@
         <v>20520</v>
       </c>
       <c r="D110" s="9" t="s">
-        <v>38</v>
+        <v>309</v>
       </c>
       <c r="E110" s="10" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="F110" s="8">
         <v>0</v>
@@ -6353,14 +6411,14 @@
       <c r="I110" s="11">
         <v>1</v>
       </c>
-      <c r="J110" s="12" t="s">
-        <v>78</v>
+      <c r="J110" s="12">
+        <v>30000000</v>
       </c>
       <c r="K110" s="11" t="s">
-        <v>312</v>
+        <v>331</v>
       </c>
       <c r="L110" s="11" t="s">
-        <v>308</v>
+        <v>204</v>
       </c>
       <c r="M110" s="11">
         <v>0</v>
